--- a/database/event/4680/event_4680_evp_summary.xlsx
+++ b/database/event/4680/event_4680_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5486</v>
+        <v>5.5324</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2091</v>
+        <v>1.2056</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8201</v>
+        <v>1.7602</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5486</v>
+        <v>5.5324</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4477</v>
+        <v>1.4315</v>
       </c>
       <c r="G2" t="n">
         <v>4.1009</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4477</v>
+        <v>1.4315</v>
       </c>
       <c r="I2" t="n">
         <v>1.468</v>
@@ -548,7 +548,7 @@
         <v>1.0501</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5255</v>
+        <v>1.4761</v>
       </c>
       <c r="E3" t="n">
         <v>4.8192</v>
@@ -594,7 +594,7 @@
         <v>0.9562</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3513</v>
+        <v>1.3043</v>
       </c>
       <c r="E4" t="n">
         <v>4.3881</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0028</v>
+        <v>3.9954</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8722</v>
+        <v>0.8706</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1957</v>
+        <v>1.1479</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0028</v>
+        <v>3.9954</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6574</v>
       </c>
       <c r="G5" t="n">
         <v>3.338</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6574</v>
       </c>
       <c r="I5" t="n">
         <v>0.6741</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7775</v>
+        <v>3.7641</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8232</v>
+        <v>0.8202</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1047</v>
+        <v>1.0557</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7775</v>
+        <v>3.7641</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1977</v>
+        <v>1.1843</v>
       </c>
       <c r="G6" t="n">
         <v>2.5798</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1977</v>
+        <v>1.1843</v>
       </c>
       <c r="I6" t="n">
         <v>1.2145</v>
@@ -732,7 +732,7 @@
         <v>0.8201000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.099</v>
+        <v>1.0554</v>
       </c>
       <c r="E7" t="n">
         <v>3.7634</v>
@@ -778,7 +778,7 @@
         <v>0.8070000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0748</v>
+        <v>1.0316</v>
       </c>
       <c r="E8" t="n">
         <v>3.7035</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0375</v>
+        <v>3.0199</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6619</v>
+        <v>0.6581</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8057</v>
+        <v>0.7592</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0375</v>
+        <v>3.0199</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3727</v>
+        <v>2.3551</v>
       </c>
       <c r="G9" t="n">
         <v>0.6647999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3727</v>
+        <v>2.3551</v>
       </c>
       <c r="I9" t="n">
         <v>2.3949</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7631</v>
+        <v>2.7528</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6021</v>
+        <v>0.5999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6949</v>
+        <v>0.6528</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7631</v>
+        <v>2.7528</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3763</v>
+        <v>1.366</v>
       </c>
       <c r="G10" t="n">
         <v>1.3868</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3763</v>
+        <v>1.366</v>
       </c>
       <c r="I10" t="n">
         <v>1.3891</v>
@@ -916,7 +916,7 @@
         <v>0.5532</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5675</v>
       </c>
       <c r="E11" t="n">
         <v>2.5388</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4898</v>
+        <v>2.4828</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5425</v>
+        <v>0.541</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5845</v>
+        <v>0.5452</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4898</v>
+        <v>2.4828</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9355</v>
+        <v>0.9285</v>
       </c>
       <c r="G12" t="n">
         <v>1.5543</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9355</v>
+        <v>0.9285</v>
       </c>
       <c r="I12" t="n">
         <v>0.9442</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3384</v>
+        <v>2.3269</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.5071</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5233</v>
+        <v>0.4831</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3384</v>
+        <v>2.3269</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5354</v>
+        <v>1.5239</v>
       </c>
       <c r="G13" t="n">
         <v>0.803</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5354</v>
+        <v>1.5239</v>
       </c>
       <c r="I13" t="n">
         <v>1.5497</v>
@@ -1054,7 +1054,7 @@
         <v>0.463</v>
       </c>
       <c r="D14" t="n">
-        <v>0.437</v>
+        <v>0.4026</v>
       </c>
       <c r="E14" t="n">
         <v>2.1248</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9981</v>
+        <v>1.9858</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4354</v>
+        <v>0.4327</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3858</v>
+        <v>0.3472</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9981</v>
+        <v>1.9858</v>
       </c>
       <c r="F15" t="n">
-        <v>1.654</v>
+        <v>1.6417</v>
       </c>
       <c r="G15" t="n">
         <v>0.3441</v>
       </c>
       <c r="H15" t="n">
-        <v>1.654</v>
+        <v>1.6417</v>
       </c>
       <c r="I15" t="n">
         <v>1.6695</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7552</v>
+        <v>1.7433</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3825</v>
+        <v>0.3799</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2877</v>
+        <v>0.2506</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7552</v>
+        <v>1.7433</v>
       </c>
       <c r="F16" t="n">
-        <v>1.601</v>
+        <v>1.5891</v>
       </c>
       <c r="G16" t="n">
         <v>0.1542</v>
       </c>
       <c r="H16" t="n">
-        <v>1.601</v>
+        <v>1.5891</v>
       </c>
       <c r="I16" t="n">
         <v>1.616</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6734</v>
+        <v>1.6645</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3646</v>
+        <v>0.3627</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2547</v>
+        <v>0.2192</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6734</v>
+        <v>1.6645</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1909</v>
+        <v>1.182</v>
       </c>
       <c r="G17" t="n">
         <v>0.4825</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1909</v>
+        <v>1.182</v>
       </c>
       <c r="I17" t="n">
         <v>1.202</v>
@@ -1238,7 +1238,7 @@
         <v>0.3523</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2317</v>
+        <v>0.2002</v>
       </c>
       <c r="E18" t="n">
         <v>1.6167</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3807</v>
+        <v>1.3755</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3009</v>
+        <v>0.2997</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1364</v>
+        <v>0.1041</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3807</v>
+        <v>1.3755</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3807</v>
+        <v>1.3755</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3807</v>
+        <v>1.3755</v>
       </c>
       <c r="I19" t="n">
         <v>1.3871</v>
@@ -1330,7 +1330,7 @@
         <v>0.2244</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0053</v>
+        <v>-0.0336</v>
       </c>
       <c r="E20" t="n">
         <v>1.0298</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8438</v>
+        <v>0.8359</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1839</v>
+        <v>0.1821</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0805</v>
+        <v>-0.1109</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8438</v>
+        <v>0.8359</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0603</v>
+        <v>1.0524</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2165</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0603</v>
+        <v>1.0524</v>
       </c>
       <c r="I21" t="n">
         <v>1.0702</v>
@@ -1422,7 +1422,7 @@
         <v>0.1556</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1329</v>
+        <v>-0.1594</v>
       </c>
       <c r="E22" t="n">
         <v>0.7141</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6481</v>
+        <v>0.6455</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1412</v>
+        <v>0.1407</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1595</v>
+        <v>-0.1867</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6481</v>
+        <v>0.6455</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3507</v>
+        <v>0.3481</v>
       </c>
       <c r="G23" t="n">
         <v>0.2974</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3507</v>
+        <v>0.3481</v>
       </c>
       <c r="I23" t="n">
         <v>0.354</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5657</v>
+        <v>0.5636</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1233</v>
+        <v>0.1228</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1928</v>
+        <v>-0.2194</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5657</v>
+        <v>0.5636</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5657</v>
+        <v>0.5636</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5657</v>
+        <v>0.5636</v>
       </c>
       <c r="I24" t="n">
         <v>0.5683</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5079</v>
+        <v>0.499</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1107</v>
+        <v>0.1087</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2162</v>
+        <v>-0.2451</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5079</v>
+        <v>0.499</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1959</v>
+        <v>1.187</v>
       </c>
       <c r="G25" t="n">
         <v>-0.6879999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1959</v>
+        <v>1.187</v>
       </c>
       <c r="I25" t="n">
         <v>1.207</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1925</v>
+        <v>0.1918</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0419</v>
+        <v>0.0418</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3436</v>
+        <v>-0.3675</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1925</v>
+        <v>0.1918</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1925</v>
+        <v>0.1918</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1925</v>
+        <v>0.1918</v>
       </c>
       <c r="I26" t="n">
         <v>0.1934</v>
@@ -1652,7 +1652,7 @@
         <v>0.0036</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4146</v>
+        <v>-0.4373</v>
       </c>
       <c r="E27" t="n">
         <v>0.0167</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4386</v>
+        <v>-0.4369</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0956</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5985</v>
+        <v>-0.618</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4386</v>
+        <v>-0.4369</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4386</v>
+        <v>-0.4369</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4386</v>
+        <v>-0.4369</v>
       </c>
       <c r="I28" t="n">
         <v>-0.4406</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4698</v>
+        <v>-0.4697</v>
       </c>
       <c r="C29" t="n">
         <v>-0.1024</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6112</v>
+        <v>-0.631</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4698</v>
+        <v>-0.4697</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0134</v>
+        <v>-0.0133</v>
       </c>
       <c r="G29" t="n">
         <v>-0.4564</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0134</v>
+        <v>-0.0133</v>
       </c>
       <c r="I29" t="n">
         <v>-0.0135</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4767</v>
+        <v>-0.4788</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1039</v>
+        <v>-0.1043</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6139</v>
+        <v>-0.6347</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4767</v>
+        <v>-0.4788</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2822</v>
+        <v>0.2801</v>
       </c>
       <c r="G30" t="n">
         <v>-0.7589</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2822</v>
+        <v>0.2801</v>
       </c>
       <c r="I30" t="n">
         <v>0.2848</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5295</v>
+        <v>-0.5276</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1154</v>
+        <v>-0.115</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6353</v>
+        <v>-0.6541</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5295</v>
+        <v>-0.5276</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5295</v>
+        <v>-0.5276</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5295</v>
+        <v>-0.5276</v>
       </c>
       <c r="I31" t="n">
         <v>-0.532</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5735</v>
+        <v>-0.5557</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.125</v>
+        <v>-0.1211</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.653</v>
+        <v>-0.6653</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5735</v>
+        <v>-0.5557</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.5965</v>
+        <v>-1.5787</v>
       </c>
       <c r="G32" t="n">
         <v>1.023</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.5965</v>
+        <v>-1.5787</v>
       </c>
       <c r="I32" t="n">
         <v>-1.6189</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7016</v>
+        <v>-0.6963</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1529</v>
+        <v>-0.1517</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7048</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7016</v>
+        <v>-0.6963</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7016</v>
+        <v>-0.6963</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7016</v>
+        <v>-0.6963</v>
       </c>
       <c r="I33" t="n">
         <v>-0.7081</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7351</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1602</v>
+        <v>-0.1605</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7183</v>
+        <v>-0.7373</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7351</v>
+        <v>-0.7364000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1788</v>
+        <v>0.1775</v>
       </c>
       <c r="G34" t="n">
         <v>-0.9139</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1788</v>
+        <v>0.1775</v>
       </c>
       <c r="I34" t="n">
         <v>0.1805</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7507</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1642</v>
+        <v>-0.1636</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7258</v>
+        <v>-0.743</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7507</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7507</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.7507</v>
       </c>
       <c r="I35" t="n">
         <v>-0.757</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1898</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7733</v>
+        <v>-0.791</v>
       </c>
       <c r="E36" t="n">
         <v>-0.8711</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9643</v>
+        <v>-0.9607</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2101</v>
+        <v>-0.2093</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8109</v>
+        <v>-0.8267</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9643</v>
+        <v>-0.9607</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9643</v>
+        <v>-0.9607</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9643</v>
+        <v>-0.9607</v>
       </c>
       <c r="I37" t="n">
         <v>-0.9688</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1591</v>
+        <v>-1.1547</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2526</v>
+        <v>-0.2516</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.9039</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1591</v>
+        <v>-1.1547</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3972</v>
+        <v>-0.3928</v>
       </c>
       <c r="G38" t="n">
         <v>-0.7619</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3972</v>
+        <v>-0.3928</v>
       </c>
       <c r="I38" t="n">
         <v>-0.4028</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5156</v>
+        <v>-1.51</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3303</v>
+        <v>-0.329</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0336</v>
+        <v>-1.0455</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5156</v>
+        <v>-1.51</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5156</v>
+        <v>-1.51</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5156</v>
+        <v>-1.51</v>
       </c>
       <c r="I39" t="n">
         <v>-1.5227</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9794</v>
+        <v>-1.9721</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4313</v>
+        <v>-0.4297</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.221</v>
+        <v>-1.2296</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9794</v>
+        <v>-1.9721</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9794</v>
+        <v>-0.9721</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9794</v>
+        <v>-0.9721</v>
       </c>
       <c r="I40" t="n">
         <v>-0.9885</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4338</v>
+        <v>-0.4322</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2256</v>
+        <v>-1.2341</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="I41" t="n">
         <v>-2</v>
@@ -2342,7 +2342,7 @@
         <v>-0.5229</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3907</v>
+        <v>-1.3998</v>
       </c>
       <c r="E42" t="n">
         <v>-2.3994</v>

--- a/database/event/4680/event_4680_evp_summary.xlsx
+++ b/database/event/4680/event_4680_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5324</v>
+        <v>5.2277</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2056</v>
+        <v>1.1392</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7602</v>
+        <v>1.722</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5324</v>
+        <v>5.2277</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4315</v>
+        <v>1.4935</v>
       </c>
       <c r="G2" t="n">
-        <v>4.1009</v>
+        <v>3.7342</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4315</v>
+        <v>1.4935</v>
       </c>
       <c r="I2" t="n">
-        <v>1.468</v>
+        <v>1.6854</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1009</v>
+        <v>3.7342</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>196</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5689</v>
+        <v>5.4196</v>
       </c>
       <c r="N2" t="n">
         <v>328</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8192</v>
+        <v>4.2001</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0501</v>
+        <v>0.9152</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4761</v>
+        <v>1.2581</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8192</v>
+        <v>4.2001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.769</v>
+        <v>3.2237</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0502</v>
+        <v>0.9764</v>
       </c>
       <c r="H3" t="n">
-        <v>3.769</v>
+        <v>5.8719</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0549</v>
+        <v>3.0531</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0502</v>
+        <v>0.9764</v>
       </c>
       <c r="K3" t="n">
         <v>112</v>
@@ -575,7 +575,7 @@
         <v>88</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1051</v>
+        <v>4.029500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>200</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3881</v>
+        <v>4.0491</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9562</v>
+        <v>0.8823</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3043</v>
+        <v>1.19</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3881</v>
+        <v>4.0491</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4317</v>
+        <v>2.4699</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9564</v>
+        <v>1.5792</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4317</v>
+        <v>3.2161</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7814</v>
+        <v>1.6722</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9564</v>
+        <v>1.5792</v>
       </c>
       <c r="K4" t="n">
         <v>112</v>
@@ -621,7 +621,7 @@
         <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7378</v>
+        <v>3.2514</v>
       </c>
       <c r="N4" t="n">
         <v>200</v>
@@ -630,81 +630,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9954</v>
+        <v>3.8219</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8706</v>
+        <v>0.8328</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1479</v>
+        <v>1.0874</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9954</v>
+        <v>3.8219</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6574</v>
+        <v>3.0223</v>
       </c>
       <c r="G5" t="n">
-        <v>3.338</v>
+        <v>0.7996</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6574</v>
+        <v>5.1624</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6741</v>
+        <v>2.6842</v>
       </c>
       <c r="J5" t="n">
-        <v>3.338</v>
+        <v>0.7996</v>
       </c>
       <c r="K5" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="L5" t="n">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0121</v>
+        <v>3.4838</v>
       </c>
       <c r="N5" t="n">
-        <v>328</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7641</v>
+        <v>3.5662</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8202</v>
+        <v>0.7771</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0557</v>
+        <v>0.9719</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7641</v>
+        <v>3.5662</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1843</v>
+        <v>0.7653</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5798</v>
+        <v>2.8008</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1843</v>
+        <v>0.7653</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2145</v>
+        <v>0.8637</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5798</v>
+        <v>2.8008</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>196</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7943</v>
+        <v>3.6645</v>
       </c>
       <c r="N6" t="n">
         <v>328</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7634</v>
+        <v>3.5514</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.7739</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0554</v>
+        <v>0.9653</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7634</v>
+        <v>3.5514</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0329</v>
+        <v>2.8286</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7305</v>
+        <v>0.7228</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0329</v>
+        <v>4.48</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4582</v>
+        <v>2.3294</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7305</v>
+        <v>0.7228</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>136</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1887</v>
+        <v>3.0522</v>
       </c>
       <c r="N7" t="n">
         <v>262</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7035</v>
+        <v>3.4635</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.7547</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0316</v>
+        <v>0.9256</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7035</v>
+        <v>3.4635</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0061</v>
+        <v>1.3902</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6974</v>
+        <v>2.0733</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0061</v>
+        <v>1.3902</v>
       </c>
       <c r="I8" t="n">
-        <v>1.626</v>
+        <v>1.5689</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6974</v>
+        <v>2.0733</v>
       </c>
       <c r="K8" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="L8" t="n">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3234</v>
+        <v>3.6422</v>
       </c>
       <c r="N8" t="n">
-        <v>200</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0199</v>
+        <v>3.4384</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6581</v>
+        <v>0.7493</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7592</v>
+        <v>0.9143</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0199</v>
+        <v>3.4384</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3551</v>
+        <v>2.7726</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3551</v>
+        <v>2.7726</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3949</v>
+        <v>3.0053</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0597</v>
+        <v>3.6711</v>
       </c>
       <c r="N9" t="n">
         <v>231</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7528</v>
+        <v>2.7082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5999</v>
+        <v>0.5901</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6528</v>
+        <v>0.5846</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7528</v>
+        <v>2.7082</v>
       </c>
       <c r="F10" t="n">
-        <v>1.366</v>
+        <v>1.4049</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3868</v>
+        <v>1.3033</v>
       </c>
       <c r="H10" t="n">
-        <v>1.366</v>
+        <v>1.4049</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3891</v>
+        <v>1.5228</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3868</v>
+        <v>1.3033</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>87</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7759</v>
+        <v>2.8261</v>
       </c>
       <c r="N10" t="n">
         <v>231</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5388</v>
+        <v>2.6626</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5532</v>
+        <v>0.5802</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5675</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5388</v>
+        <v>2.6626</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8194</v>
+        <v>1.8786</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2806</v>
+        <v>0.784</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8194</v>
+        <v>1.8786</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0957</v>
+        <v>0.9768</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2806</v>
+        <v>0.784</v>
       </c>
       <c r="K11" t="n">
         <v>126</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8151</v>
+        <v>1.7608</v>
       </c>
       <c r="N11" t="n">
         <v>262</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4828</v>
+        <v>2.4698</v>
       </c>
       <c r="C12" t="n">
-        <v>0.541</v>
+        <v>0.5382</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5452</v>
+        <v>0.477</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4828</v>
+        <v>2.4698</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9285</v>
+        <v>2.686</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5543</v>
+        <v>-0.2162</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9285</v>
+        <v>3.9775</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9442</v>
+        <v>2.0681</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5543</v>
+        <v>-0.2162</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L12" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4985</v>
+        <v>1.8519</v>
       </c>
       <c r="N12" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3269</v>
+        <v>2.4077</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5071</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4831</v>
+        <v>0.4489</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3269</v>
+        <v>2.4077</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5239</v>
+        <v>1.0475</v>
       </c>
       <c r="G13" t="n">
-        <v>0.803</v>
+        <v>1.3602</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5239</v>
+        <v>1.0475</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5497</v>
+        <v>1.1354</v>
       </c>
       <c r="J13" t="n">
-        <v>0.803</v>
+        <v>1.3602</v>
       </c>
       <c r="K13" t="n">
         <v>111</v>
@@ -1035,7 +1035,7 @@
         <v>170</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3527</v>
+        <v>2.4956</v>
       </c>
       <c r="N13" t="n">
         <v>281</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1248</v>
+        <v>2.3375</v>
       </c>
       <c r="C14" t="n">
-        <v>0.463</v>
+        <v>0.5094</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4026</v>
+        <v>0.4173</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1248</v>
+        <v>2.3375</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6035</v>
+        <v>3.2007</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4787</v>
+        <v>-0.8632</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6035</v>
+        <v>5.7909</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1102</v>
+        <v>3.011</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4787</v>
+        <v>-0.8632</v>
       </c>
       <c r="K14" t="n">
         <v>126</v>
@@ -1081,7 +1081,7 @@
         <v>136</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6315</v>
+        <v>2.1478</v>
       </c>
       <c r="N14" t="n">
         <v>262</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9858</v>
+        <v>2.2486</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4327</v>
+        <v>0.49</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3472</v>
+        <v>0.3771</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9858</v>
+        <v>2.2486</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6417</v>
+        <v>1.398</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3441</v>
+        <v>0.8506</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6417</v>
+        <v>1.398</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6695</v>
+        <v>1.5154</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3441</v>
+        <v>0.8506</v>
       </c>
       <c r="K15" t="n">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="L15" t="n">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0136</v>
+        <v>2.366</v>
       </c>
       <c r="N15" t="n">
-        <v>231</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7433</v>
+        <v>2.2341</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3799</v>
+        <v>0.4868</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2506</v>
+        <v>0.3706</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7433</v>
+        <v>2.2341</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5891</v>
+        <v>2.0699</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1542</v>
+        <v>0.1642</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5891</v>
+        <v>2.0699</v>
       </c>
       <c r="I16" t="n">
-        <v>1.616</v>
+        <v>2.2437</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1542</v>
+        <v>0.1642</v>
       </c>
       <c r="K16" t="n">
         <v>118</v>
@@ -1173,7 +1173,7 @@
         <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7702</v>
+        <v>2.4079</v>
       </c>
       <c r="N16" t="n">
         <v>173</v>
@@ -1182,277 +1182,277 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6645</v>
+        <v>2.0049</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3627</v>
+        <v>0.4369</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2192</v>
+        <v>0.2671</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6645</v>
+        <v>2.0049</v>
       </c>
       <c r="F17" t="n">
-        <v>1.182</v>
+        <v>1.7184</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4825</v>
+        <v>0.2865</v>
       </c>
       <c r="H17" t="n">
-        <v>1.182</v>
+        <v>1.7184</v>
       </c>
       <c r="I17" t="n">
-        <v>1.202</v>
+        <v>1.8627</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4825</v>
+        <v>0.2865</v>
       </c>
       <c r="K17" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6845</v>
+        <v>2.1492</v>
       </c>
       <c r="N17" t="n">
-        <v>173</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6167</v>
+        <v>1.9265</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3523</v>
+        <v>0.4198</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2002</v>
+        <v>0.2317</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6167</v>
+        <v>1.9265</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1119</v>
+        <v>1.4792</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5048</v>
+        <v>0.4473</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1119</v>
+        <v>1.4792</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9012</v>
+        <v>1.6034</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5048</v>
+        <v>0.4473</v>
       </c>
       <c r="K18" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="L18" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>1.406</v>
+        <v>2.0507</v>
       </c>
       <c r="N18" t="n">
-        <v>262</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3755</v>
+        <v>1.7215</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2997</v>
+        <v>0.3751</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1041</v>
+        <v>0.1392</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3755</v>
+        <v>1.7215</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3755</v>
+        <v>0.851</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3755</v>
+        <v>0.851</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3871</v>
+        <v>0.4425</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3871</v>
+        <v>1.313</v>
       </c>
       <c r="N19" t="n">
-        <v>138</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0298</v>
+        <v>1.4273</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2244</v>
+        <v>0.311</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0336</v>
+        <v>0.0063</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0298</v>
+        <v>1.4273</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2862</v>
+        <v>1.4273</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7436</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2862</v>
+        <v>1.4273</v>
       </c>
       <c r="I20" t="n">
-        <v>0.232</v>
+        <v>1.486</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7436</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9756</v>
+        <v>1.486</v>
       </c>
       <c r="N20" t="n">
-        <v>262</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8359</v>
+        <v>1.329</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1821</v>
+        <v>0.2896</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1109</v>
+        <v>-0.038</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8359</v>
+        <v>1.329</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0524</v>
+        <v>1.1463</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2165</v>
+        <v>0.1827</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0524</v>
+        <v>1.1463</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0702</v>
+        <v>0.596</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2165</v>
+        <v>0.1827</v>
       </c>
       <c r="K21" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L21" t="n">
-        <v>170</v>
+        <v>88</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8537</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>281</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7141</v>
+        <v>1.2619</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1556</v>
+        <v>0.275</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1594</v>
+        <v>-0.0683</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7141</v>
+        <v>1.2619</v>
       </c>
       <c r="F22" t="n">
-        <v>0.57</v>
+        <v>1.3187</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1441</v>
+        <v>-0.0568</v>
       </c>
       <c r="H22" t="n">
-        <v>0.57</v>
+        <v>1.3187</v>
       </c>
       <c r="I22" t="n">
-        <v>0.462</v>
+        <v>1.4294</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1441</v>
+        <v>-0.0568</v>
       </c>
       <c r="K22" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L22" t="n">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6061000000000001</v>
+        <v>1.3726</v>
       </c>
       <c r="N22" t="n">
-        <v>200</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6455</v>
+        <v>0.9217</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1407</v>
+        <v>0.2008</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1867</v>
+        <v>-0.2219</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6455</v>
+        <v>0.9217</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3481</v>
+        <v>0.511</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2974</v>
+        <v>0.4107</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3481</v>
+        <v>0.511</v>
       </c>
       <c r="I23" t="n">
-        <v>0.354</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2974</v>
+        <v>0.4107</v>
       </c>
       <c r="K23" t="n">
         <v>111</v>
@@ -1495,7 +1495,7 @@
         <v>170</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6514</v>
+        <v>0.9645999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>281</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5636</v>
+        <v>0.7478</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1228</v>
+        <v>0.163</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2194</v>
+        <v>-0.3004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5636</v>
+        <v>0.7478</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5636</v>
+        <v>1.2184</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.4706</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5636</v>
+        <v>1.2184</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5683</v>
+        <v>1.3207</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.4706</v>
       </c>
       <c r="K24" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5683</v>
+        <v>0.8501</v>
       </c>
       <c r="N24" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.499</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1087</v>
+        <v>0.1536</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2451</v>
+        <v>-0.3197</v>
       </c>
       <c r="E25" t="n">
-        <v>0.499</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>1.187</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6879999999999999</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.187</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.207</v>
+        <v>0.7341</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6879999999999999</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5190000000000001</v>
+        <v>0.7341</v>
       </c>
       <c r="N25" t="n">
-        <v>173</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1918</v>
+        <v>0.4935</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0418</v>
+        <v>0.1075</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3675</v>
+        <v>-0.4152</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1918</v>
+        <v>0.4935</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1918</v>
+        <v>0.4935</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1918</v>
+        <v>0.4935</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1934</v>
+        <v>0.5138</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1934</v>
+        <v>0.5138</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0167</v>
+        <v>0.2909</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0036</v>
+        <v>0.0634</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4373</v>
+        <v>-0.5067</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0167</v>
+        <v>0.2909</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0167</v>
+        <v>0.2909</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0167</v>
+        <v>0.2909</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0168</v>
+        <v>0.3029</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0168</v>
+        <v>0.3029</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1688,323 +1688,323 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4369</v>
+        <v>0.103</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.0224</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.618</v>
+        <v>-0.5915</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4369</v>
+        <v>0.103</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4369</v>
+        <v>0.5875</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.4845</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4369</v>
+        <v>0.5875</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4406</v>
+        <v>0.6368</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.4845</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4406</v>
+        <v>0.1523</v>
       </c>
       <c r="N28" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4697</v>
+        <v>0.0583</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1024</v>
+        <v>0.0127</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.631</v>
+        <v>-0.6117</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4697</v>
+        <v>0.0583</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0133</v>
+        <v>0.0583</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4564</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0133</v>
+        <v>0.0583</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0135</v>
+        <v>0.0607</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4564</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="L29" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4699</v>
+        <v>0.0607</v>
       </c>
       <c r="N29" t="n">
-        <v>173</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4788</v>
+        <v>-0.0636</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1043</v>
+        <v>-0.0139</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6347</v>
+        <v>-0.6667</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4788</v>
+        <v>-0.0636</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2801</v>
+        <v>-1.064</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7589</v>
+        <v>1.0004</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2801</v>
+        <v>-1.064</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2848</v>
+        <v>-1.2008</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7589</v>
+        <v>1.0004</v>
       </c>
       <c r="K30" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L30" t="n">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4741</v>
+        <v>-0.2004000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>173</v>
+        <v>328</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5276</v>
+        <v>-0.0888</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.115</v>
+        <v>-0.0194</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6541</v>
+        <v>-0.6781</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5276</v>
+        <v>-0.0888</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5276</v>
+        <v>0.1957</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.2845</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5276</v>
+        <v>0.1957</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.532</v>
+        <v>0.2121</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.2845</v>
       </c>
       <c r="K31" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.532</v>
+        <v>-0.07239999999999996</v>
       </c>
       <c r="N31" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5557</v>
+        <v>-0.1007</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1211</v>
+        <v>-0.0219</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6653</v>
+        <v>-0.6835</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5557</v>
+        <v>-0.1007</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.5787</v>
+        <v>0.4158</v>
       </c>
       <c r="G32" t="n">
-        <v>1.023</v>
+        <v>-0.5165</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.5787</v>
+        <v>0.4158</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.6189</v>
+        <v>0.4507</v>
       </c>
       <c r="J32" t="n">
-        <v>1.023</v>
+        <v>-0.5165</v>
       </c>
       <c r="K32" t="n">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="L32" t="n">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5959000000000001</v>
+        <v>-0.06579999999999997</v>
       </c>
       <c r="N32" t="n">
-        <v>328</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6963</v>
+        <v>-0.1436</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1517</v>
+        <v>-0.0313</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.7028</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6963</v>
+        <v>-0.1436</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6963</v>
+        <v>-0.1436</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6963</v>
+        <v>-0.1436</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7081</v>
+        <v>-0.1495</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7081</v>
+        <v>-0.1495</v>
       </c>
       <c r="N33" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.2352</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1605</v>
+        <v>-0.0513</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7373</v>
+        <v>-0.7442</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.2352</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1775</v>
+        <v>-0.2352</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.9139</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1775</v>
+        <v>-0.2352</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1805</v>
+        <v>-0.2549</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9139</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="L34" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.2549</v>
       </c>
       <c r="N34" t="n">
-        <v>281</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7507</v>
+        <v>-0.3055</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1636</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.743</v>
+        <v>-0.7759</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7507</v>
+        <v>-0.3055</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7507</v>
+        <v>-0.3055</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7507</v>
+        <v>-0.3055</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.757</v>
+        <v>-0.3181</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.757</v>
+        <v>-0.3181</v>
       </c>
       <c r="N35" t="n">
         <v>119</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8711</v>
+        <v>-0.4875</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1898</v>
+        <v>-0.1062</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.791</v>
+        <v>-0.8581</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8711</v>
+        <v>-0.4875</v>
       </c>
       <c r="F36" t="n">
+        <v>-0.4875</v>
+      </c>
+      <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="G36" t="n">
-        <v>-0.8711</v>
-      </c>
       <c r="H36" t="n">
+        <v>-0.4875</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.5075</v>
+      </c>
+      <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
+        <v>119</v>
+      </c>
+      <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="n">
-        <v>-0.8711</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>87</v>
-      </c>
       <c r="M36" t="n">
-        <v>-0.8711</v>
+        <v>-0.5075</v>
       </c>
       <c r="N36" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9607</v>
+        <v>-0.5226</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2093</v>
+        <v>-0.1139</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8267</v>
+        <v>-0.8739</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9607</v>
+        <v>-0.5226</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9607</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
+        <v>-0.5226</v>
+      </c>
+      <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="n">
-        <v>-0.9607</v>
-      </c>
       <c r="I37" t="n">
-        <v>-0.9688</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
+        <v>-0.5226</v>
+      </c>
+      <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="K37" t="n">
-        <v>119</v>
-      </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9688</v>
+        <v>-0.5226</v>
       </c>
       <c r="N37" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1547</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2516</v>
+        <v>-0.1402</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9039</v>
+        <v>-0.9286</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1547</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.3928</v>
+        <v>-0.1692</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7619</v>
+        <v>-0.4744</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3928</v>
+        <v>-0.1692</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4028</v>
+        <v>-0.191</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7619</v>
+        <v>-0.4744</v>
       </c>
       <c r="K38" t="n">
         <v>132</v>
@@ -2185,7 +2185,7 @@
         <v>196</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.1647</v>
+        <v>-0.6654</v>
       </c>
       <c r="N38" t="n">
         <v>328</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.51</v>
+        <v>-1.0031</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.329</v>
+        <v>-0.2186</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0455</v>
+        <v>-1.0909</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.51</v>
+        <v>-1.0031</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.51</v>
+        <v>-1.0031</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.51</v>
+        <v>-1.0031</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5227</v>
+        <v>-1.0444</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5227</v>
+        <v>-1.0444</v>
       </c>
       <c r="N39" t="n">
         <v>138</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9721</v>
+        <v>-1.1432</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.4297</v>
+        <v>-0.2491</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2296</v>
+        <v>-1.1541</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9721</v>
+        <v>-1.1432</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9721</v>
+        <v>-0.49</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.6532</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9721</v>
+        <v>-0.49</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9885</v>
+        <v>-0.5311</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.6532</v>
       </c>
       <c r="K40" t="n">
         <v>144</v>
@@ -2277,7 +2277,7 @@
         <v>87</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9885</v>
+        <v>-1.1843</v>
       </c>
       <c r="N40" t="n">
         <v>231</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9833</v>
+        <v>-1.7332</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4322</v>
+        <v>-0.3777</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2341</v>
+        <v>-1.4205</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9833</v>
+        <v>-1.7332</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9833</v>
+        <v>-1.7332</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9833</v>
+        <v>-1.7332</v>
       </c>
       <c r="I41" t="n">
-        <v>-2</v>
+        <v>-1.8045</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2</v>
+        <v>-1.8045</v>
       </c>
       <c r="N41" t="n">
         <v>138</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.3994</v>
+        <v>-2.7998</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.5229</v>
+        <v>-0.6101</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.3998</v>
+        <v>-1.902</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.3994</v>
+        <v>-2.7998</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.7837</v>
+        <v>-2.5012</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.6157</v>
+        <v>-0.2986</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.7837</v>
+        <v>-2.5012</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.4457</v>
+        <v>-1.3005</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6157</v>
+        <v>-0.2986</v>
       </c>
       <c r="K42" t="n">
         <v>112</v>
@@ -2369,7 +2369,7 @@
         <v>88</v>
       </c>
       <c r="M42" t="n">
-        <v>-2.0614</v>
+        <v>-1.5991</v>
       </c>
       <c r="N42" t="n">
         <v>200</v>
@@ -2475,10 +2475,10 @@
         <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4074</v>
+        <v>0.4589</v>
       </c>
       <c r="J2" t="n">
-        <v>10.5924</v>
+        <v>11.9314</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2703</v>
+        <v>-0.1818</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.0278</v>
+        <v>-4.7268</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3226</v>
+        <v>-0.2115</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.387600000000001</v>
+        <v>-5.499</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3549</v>
+        <v>-0.2313</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.227399999999999</v>
+        <v>-6.0138</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5423</v>
+        <v>-0.3563</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.0998</v>
+        <v>-9.2638</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9556</v>
+        <v>0.9605</v>
       </c>
       <c r="J7" t="n">
-        <v>24.8456</v>
+        <v>24.973</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8889</v>
+        <v>0.8979</v>
       </c>
       <c r="J8" t="n">
-        <v>23.1114</v>
+        <v>23.3454</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4135</v>
+        <v>0.4814</v>
       </c>
       <c r="J9" t="n">
-        <v>10.751</v>
+        <v>12.5164</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3867</v>
+        <v>0.456</v>
       </c>
       <c r="J10" t="n">
-        <v>10.0542</v>
+        <v>11.856</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2214</v>
+        <v>0.295</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7564</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6168</v>
+        <v>0.7484</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6536</v>
+        <v>20.2068</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1778</v>
+        <v>-0.1329</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.8006</v>
+        <v>-3.5883</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.78</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3773</v>
+        <v>-0.2434</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.1871</v>
+        <v>-6.5718</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4219</v>
+        <v>-0.2727</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.3913</v>
+        <v>-7.3629</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6117</v>
+        <v>-0.4055</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.5159</v>
+        <v>-10.9485</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.36</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9425</v>
+        <v>0.9372</v>
       </c>
       <c r="J17" t="n">
-        <v>25.4475</v>
+        <v>25.3044</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8529</v>
+        <v>0.8474</v>
       </c>
       <c r="J18" t="n">
-        <v>23.0283</v>
+        <v>22.8798</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.18</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4964</v>
+        <v>0.5159</v>
       </c>
       <c r="J19" t="n">
-        <v>13.4028</v>
+        <v>13.9293</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0545</v>
+        <v>0.0129</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4715</v>
+        <v>0.3483</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1133</v>
+        <v>-0.042</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.0591</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.59</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7459</v>
+        <v>0.5389</v>
       </c>
       <c r="J22" t="n">
-        <v>16.4098</v>
+        <v>11.8558</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7119</v>
+        <v>0.521</v>
       </c>
       <c r="J23" t="n">
-        <v>15.6618</v>
+        <v>11.462</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6042</v>
+        <v>0.4667</v>
       </c>
       <c r="J24" t="n">
-        <v>13.2924</v>
+        <v>10.2674</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.34</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4218</v>
+        <v>0.3867</v>
       </c>
       <c r="J25" t="n">
-        <v>9.2796</v>
+        <v>8.507400000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>1.12</v>
       </c>
       <c r="I26" t="n">
-        <v>0.122</v>
+        <v>0.1554</v>
       </c>
       <c r="J26" t="n">
-        <v>2.684</v>
+        <v>3.4188</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0.407</v>
+        <v>0.344</v>
       </c>
       <c r="J27" t="n">
-        <v>8.954000000000001</v>
+        <v>7.568</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2661</v>
+        <v>-0.2096</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.8542</v>
+        <v>-4.6112</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.7</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4487</v>
+        <v>-0.3034</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.8714</v>
+        <v>-6.6748</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.64</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.538</v>
+        <v>-0.3597</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.836</v>
+        <v>-7.9134</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.774</v>
+        <v>-0.5275</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.028</v>
+        <v>-11.605</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5264</v>
+        <v>0.505</v>
       </c>
       <c r="J32" t="n">
-        <v>18.9504</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1999</v>
+        <v>0.2093</v>
       </c>
       <c r="J33" t="n">
-        <v>7.1964</v>
+        <v>7.5348</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1009</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6324</v>
+        <v>3.4272</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4361</v>
+        <v>-0.2765</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.6996</v>
+        <v>-9.954000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4635</v>
+        <v>-0.2959</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.686</v>
+        <v>-10.6524</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2108</v>
+        <v>0.8548</v>
       </c>
       <c r="J37" t="n">
-        <v>43.5888</v>
+        <v>30.7728</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3786</v>
+        <v>0.3586</v>
       </c>
       <c r="J38" t="n">
-        <v>13.6296</v>
+        <v>12.9096</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.345</v>
+        <v>0.3419</v>
       </c>
       <c r="J39" t="n">
-        <v>12.42</v>
+        <v>12.3084</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1327</v>
+        <v>0.1757</v>
       </c>
       <c r="J40" t="n">
-        <v>4.7772</v>
+        <v>6.3252</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7753</v>
+        <v>-0.7278</v>
       </c>
       <c r="J41" t="n">
-        <v>-27.9108</v>
+        <v>-26.2008</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7492</v>
+        <v>0.6875</v>
       </c>
       <c r="J42" t="n">
-        <v>22.476</v>
+        <v>20.625</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2461</v>
+        <v>0.3004</v>
       </c>
       <c r="J43" t="n">
-        <v>7.383</v>
+        <v>9.012</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1096</v>
+        <v>0.1655</v>
       </c>
       <c r="J44" t="n">
-        <v>3.288</v>
+        <v>4.965</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1317</v>
+        <v>-0.0618</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.951</v>
+        <v>-1.854</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2742</v>
+        <v>-0.1581</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.226000000000001</v>
+        <v>-4.743</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.57</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4846</v>
+        <v>1.0411</v>
       </c>
       <c r="J47" t="n">
-        <v>44.538</v>
+        <v>31.233</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.95</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2111</v>
+        <v>-0.19</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.333</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.89</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4088</v>
+        <v>-0.3688</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.264</v>
+        <v>-11.064</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8257</v>
+        <v>-0.7903</v>
       </c>
       <c r="J50" t="n">
-        <v>-24.771</v>
+        <v>-23.709</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8723</v>
+        <v>-0.8401</v>
       </c>
       <c r="J51" t="n">
-        <v>-26.169</v>
+        <v>-25.203</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3438</v>
+        <v>0.2958</v>
       </c>
       <c r="J52" t="n">
-        <v>10.314</v>
+        <v>8.874000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3287</v>
+        <v>0.2813</v>
       </c>
       <c r="J53" t="n">
-        <v>9.861000000000001</v>
+        <v>8.439</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2577</v>
+        <v>-0.1548</v>
       </c>
       <c r="J54" t="n">
-        <v>-7.731</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2577</v>
+        <v>-0.1548</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.731</v>
+        <v>-4.644</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3058</v>
+        <v>-0.1866</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.173999999999999</v>
+        <v>-5.598</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.55</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8085</v>
+        <v>0.5636</v>
       </c>
       <c r="J57" t="n">
-        <v>24.255</v>
+        <v>16.908</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>0.97</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1071</v>
+        <v>-0.0535</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.213</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2042</v>
+        <v>-0.1156</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.126</v>
+        <v>-3.468</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2551</v>
+        <v>-0.1493</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.653</v>
+        <v>-4.479</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.85</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3181</v>
+        <v>-0.1921</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.542999999999999</v>
+        <v>-5.763</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9426</v>
+        <v>0.6822</v>
       </c>
       <c r="J62" t="n">
-        <v>25.4502</v>
+        <v>18.4194</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.25</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7356</v>
+        <v>0.5553</v>
       </c>
       <c r="J63" t="n">
-        <v>19.8612</v>
+        <v>14.9931</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.04</v>
       </c>
       <c r="I64" t="n">
-        <v>0.105</v>
+        <v>0.1458</v>
       </c>
       <c r="J64" t="n">
-        <v>2.835</v>
+        <v>3.9366</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1785</v>
+        <v>-0.1166</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.8195</v>
+        <v>-3.1482</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5748</v>
+        <v>-0.515</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.5196</v>
+        <v>-13.905</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5225</v>
+        <v>0.5062</v>
       </c>
       <c r="J67" t="n">
-        <v>14.1075</v>
+        <v>13.6674</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3288</v>
+        <v>0.3625</v>
       </c>
       <c r="J68" t="n">
-        <v>8.877599999999999</v>
+        <v>9.7875</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0235</v>
+        <v>0.0562</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6345</v>
+        <v>1.5174</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1783</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.8141</v>
+        <v>-2.5839</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2478</v>
+        <v>-0.1422</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.6906</v>
+        <v>-3.8394</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6574</v>
+        <v>0.5101</v>
       </c>
       <c r="J72" t="n">
-        <v>17.0924</v>
+        <v>13.2626</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.443</v>
+        <v>0.3902</v>
       </c>
       <c r="J73" t="n">
-        <v>11.518</v>
+        <v>10.1452</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3111</v>
+        <v>0.3215</v>
       </c>
       <c r="J74" t="n">
-        <v>8.0886</v>
+        <v>8.359</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.09</v>
       </c>
       <c r="I75" t="n">
-        <v>0.272</v>
+        <v>0.2958</v>
       </c>
       <c r="J75" t="n">
-        <v>7.072</v>
+        <v>7.6908</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2905</v>
+        <v>-0.2242</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.553</v>
+        <v>-5.8292</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2217</v>
+        <v>0.2254</v>
       </c>
       <c r="J77" t="n">
-        <v>5.7642</v>
+        <v>5.8604</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0528</v>
       </c>
       <c r="J78" t="n">
-        <v>1.9968</v>
+        <v>1.3728</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0528</v>
       </c>
       <c r="J79" t="n">
-        <v>1.9968</v>
+        <v>1.3728</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.86</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2694</v>
+        <v>-0.1689</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.0044</v>
+        <v>-4.3914</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.67</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.545</v>
+        <v>-0.3559</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.17</v>
+        <v>-9.253399999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.08</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2286</v>
+        <v>0.2314</v>
       </c>
       <c r="J82" t="n">
-        <v>5.9436</v>
+        <v>6.0164</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.02</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1097</v>
+        <v>0.0872</v>
       </c>
       <c r="J83" t="n">
-        <v>2.8522</v>
+        <v>2.2672</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0495</v>
+        <v>0.0185</v>
       </c>
       <c r="J84" t="n">
-        <v>1.287</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3431</v>
+        <v>-0.2179</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.9206</v>
+        <v>-5.6654</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.63</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5931</v>
+        <v>-0.3911</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.4206</v>
+        <v>-10.1686</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.61</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3901</v>
+        <v>0.9823</v>
       </c>
       <c r="J87" t="n">
-        <v>36.1426</v>
+        <v>25.5398</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1745</v>
+        <v>0.8466</v>
       </c>
       <c r="J88" t="n">
-        <v>30.537</v>
+        <v>22.0116</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4571</v>
+        <v>0.4566</v>
       </c>
       <c r="J89" t="n">
-        <v>11.8846</v>
+        <v>11.8716</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4319</v>
+        <v>0.442</v>
       </c>
       <c r="J90" t="n">
-        <v>11.2294</v>
+        <v>11.492</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2131</v>
+        <v>-0.1273</v>
       </c>
       <c r="J91" t="n">
-        <v>-5.5406</v>
+        <v>-3.3098</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.433</v>
+        <v>0.4288</v>
       </c>
       <c r="J92" t="n">
-        <v>12.557</v>
+        <v>12.4352</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0672</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.1576</v>
+        <v>-1.9488</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0949</v>
+        <v>-0.0795</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.7521</v>
+        <v>-2.3055</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4158</v>
+        <v>-0.2666</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.0582</v>
+        <v>-7.7314</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5661</v>
+        <v>-0.3717</v>
       </c>
       <c r="J96" t="n">
-        <v>-16.4169</v>
+        <v>-10.7793</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.52</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2532</v>
+        <v>0.8888</v>
       </c>
       <c r="J97" t="n">
-        <v>36.3428</v>
+        <v>25.7752</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6828</v>
+        <v>0.5478</v>
       </c>
       <c r="J98" t="n">
-        <v>19.8012</v>
+        <v>15.8862</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>0.602</v>
+        <v>0.5069</v>
       </c>
       <c r="J99" t="n">
-        <v>17.458</v>
+        <v>14.7001</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.12</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2843</v>
+        <v>0.345</v>
       </c>
       <c r="J100" t="n">
-        <v>8.2447</v>
+        <v>10.005</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3016</v>
+        <v>-0.2215</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.7464</v>
+        <v>-6.4235</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.7286</v>
+        <v>0.5453</v>
       </c>
       <c r="J102" t="n">
-        <v>18.215</v>
+        <v>13.6325</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.236</v>
+        <v>0.1869</v>
       </c>
       <c r="J103" t="n">
-        <v>5.9</v>
+        <v>4.6725</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.75</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4387</v>
+        <v>-0.2804</v>
       </c>
       <c r="J104" t="n">
-        <v>-10.9675</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4665</v>
+        <v>-0.2997</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.6625</v>
+        <v>-7.4925</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5725</v>
+        <v>-0.3756</v>
       </c>
       <c r="J106" t="n">
-        <v>-14.3125</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.56</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7894</v>
+        <v>0.5526</v>
       </c>
       <c r="J107" t="n">
-        <v>19.735</v>
+        <v>13.815</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.14</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2368</v>
+        <v>0.2126</v>
       </c>
       <c r="J108" t="n">
-        <v>5.92</v>
+        <v>5.315</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1221</v>
+        <v>0.1309</v>
       </c>
       <c r="J109" t="n">
-        <v>3.0525</v>
+        <v>3.2725</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0553</v>
+        <v>-0.0122</v>
       </c>
       <c r="J110" t="n">
-        <v>-1.3825</v>
+        <v>-0.305</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2774</v>
+        <v>-0.1598</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.935</v>
+        <v>-3.995</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.37</v>
       </c>
       <c r="I112" t="n">
-        <v>1.0268</v>
+        <v>0.7332</v>
       </c>
       <c r="J112" t="n">
-        <v>28.7504</v>
+        <v>20.5296</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.15</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5006</v>
+        <v>0.4127</v>
       </c>
       <c r="J113" t="n">
-        <v>14.0168</v>
+        <v>11.5556</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1192</v>
       </c>
       <c r="J114" t="n">
-        <v>2.5704</v>
+        <v>3.3376</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3959</v>
+        <v>-0.3363</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.0852</v>
+        <v>-9.416399999999999</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.614</v>
+        <v>-0.5592</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.192</v>
+        <v>-15.6576</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.46</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7114</v>
+        <v>0.6552</v>
       </c>
       <c r="J117" t="n">
-        <v>19.9192</v>
+        <v>18.3456</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0232</v>
+        <v>0.0359</v>
       </c>
       <c r="J118" t="n">
-        <v>0.6496</v>
+        <v>1.0052</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.91</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2163</v>
+        <v>-0.125</v>
       </c>
       <c r="J119" t="n">
-        <v>-6.0564</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.88</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2665</v>
+        <v>-0.1582</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.462</v>
+        <v>-4.4296</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.83</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3439</v>
+        <v>-0.2107</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.629200000000001</v>
+        <v>-5.8996</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6272</v>
+        <v>0.494</v>
       </c>
       <c r="J122" t="n">
-        <v>21.3248</v>
+        <v>16.796</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.4497</v>
       </c>
       <c r="J123" t="n">
-        <v>18.6626</v>
+        <v>15.2898</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3746</v>
+        <v>0.3582</v>
       </c>
       <c r="J124" t="n">
-        <v>12.7364</v>
+        <v>12.1788</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1301</v>
+        <v>0.1748</v>
       </c>
       <c r="J125" t="n">
-        <v>4.4234</v>
+        <v>5.9432</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.98</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1863</v>
+        <v>-0.1209</v>
       </c>
       <c r="J126" t="n">
-        <v>-6.3342</v>
+        <v>-4.1106</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5195</v>
+        <v>0.499</v>
       </c>
       <c r="J127" t="n">
-        <v>17.663</v>
+        <v>16.966</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4386</v>
+        <v>0.4355</v>
       </c>
       <c r="J128" t="n">
-        <v>14.9124</v>
+        <v>14.807</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1788</v>
+        <v>-0.1079</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.0792</v>
+        <v>-3.6686</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2498</v>
+        <v>-0.1521</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.4932</v>
+        <v>-5.1714</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.5</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7595</v>
+        <v>-0.516</v>
       </c>
       <c r="J131" t="n">
-        <v>-25.823</v>
+        <v>-17.544</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.48</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7015</v>
+        <v>0.6188</v>
       </c>
       <c r="J132" t="n">
-        <v>25.254</v>
+        <v>22.2768</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.36</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.4818</v>
       </c>
       <c r="J133" t="n">
-        <v>20.052</v>
+        <v>17.3448</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4259</v>
+        <v>0.3634</v>
       </c>
       <c r="J134" t="n">
-        <v>15.3324</v>
+        <v>13.0824</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.79</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4217</v>
+        <v>-0.2624</v>
       </c>
       <c r="J135" t="n">
-        <v>-15.1812</v>
+        <v>-9.446400000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.73</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5014</v>
+        <v>-0.3206</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.0504</v>
+        <v>-11.5416</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.18</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3787</v>
+        <v>0.3254</v>
       </c>
       <c r="J137" t="n">
-        <v>13.6332</v>
+        <v>11.7144</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1637</v>
+        <v>0.1194</v>
       </c>
       <c r="J138" t="n">
-        <v>5.8932</v>
+        <v>4.2984</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2549</v>
+        <v>-0.1591</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.176399999999999</v>
+        <v>-5.7276</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3355</v>
+        <v>-0.2107</v>
       </c>
       <c r="J140" t="n">
-        <v>-12.078</v>
+        <v>-7.5852</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4522</v>
+        <v>-0.2898</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.2792</v>
+        <v>-10.4328</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.445</v>
+        <v>0.5098</v>
       </c>
       <c r="J142" t="n">
-        <v>12.46</v>
+        <v>14.2744</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0434</v>
+        <v>-0.0568</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.2152</v>
+        <v>-1.5904</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2482</v>
+        <v>-0.1802</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.9496</v>
+        <v>-5.0456</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5365</v>
+        <v>-0.3532</v>
       </c>
       <c r="J145" t="n">
-        <v>-15.022</v>
+        <v>-9.8896</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7164</v>
+        <v>-0.4834</v>
       </c>
       <c r="J146" t="n">
-        <v>-20.0592</v>
+        <v>-13.5352</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.55</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3093</v>
+        <v>1.199</v>
       </c>
       <c r="J147" t="n">
-        <v>36.6604</v>
+        <v>33.572</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.45</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1085</v>
+        <v>1.0718</v>
       </c>
       <c r="J148" t="n">
-        <v>31.038</v>
+        <v>30.0104</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6785</v>
+        <v>0.6956</v>
       </c>
       <c r="J149" t="n">
-        <v>18.998</v>
+        <v>19.4768</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0736</v>
+        <v>0.0003</v>
       </c>
       <c r="J150" t="n">
-        <v>-2.0608</v>
+        <v>0.008399999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6141</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.1948</v>
+        <v>-15.3692</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.06</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2105</v>
+        <v>0.2032</v>
       </c>
       <c r="J152" t="n">
-        <v>5.473</v>
+        <v>5.2832</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1916</v>
+        <v>0.1795</v>
       </c>
       <c r="J153" t="n">
-        <v>4.9816</v>
+        <v>4.667</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.095</v>
+        <v>-0.0863</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.47</v>
+        <v>-2.2438</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.85</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2552</v>
+        <v>-0.1724</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.6352</v>
+        <v>-4.4824</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.42</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.5775</v>
       </c>
       <c r="J156" t="n">
-        <v>-21.8192</v>
+        <v>-15.015</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8762</v>
       </c>
       <c r="J157" t="n">
-        <v>22.5524</v>
+        <v>22.7812</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.29</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7497</v>
+        <v>0.763</v>
       </c>
       <c r="J158" t="n">
-        <v>19.4922</v>
+        <v>19.838</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.24</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6192</v>
+        <v>0.6486</v>
       </c>
       <c r="J159" t="n">
-        <v>16.0992</v>
+        <v>16.8636</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4147</v>
+        <v>0.4818</v>
       </c>
       <c r="J160" t="n">
-        <v>10.7822</v>
+        <v>12.5268</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>1.11</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2506</v>
+        <v>0.3235</v>
       </c>
       <c r="J161" t="n">
-        <v>6.5156</v>
+        <v>8.411</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.69</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5421</v>
+        <v>1.3545</v>
       </c>
       <c r="J162" t="n">
-        <v>37.0104</v>
+        <v>32.508</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5104</v>
+        <v>0.5917</v>
       </c>
       <c r="J163" t="n">
-        <v>12.2496</v>
+        <v>14.2008</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4852</v>
+        <v>0.5676</v>
       </c>
       <c r="J164" t="n">
-        <v>11.6448</v>
+        <v>13.6224</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3837</v>
+        <v>0.4683</v>
       </c>
       <c r="J165" t="n">
-        <v>9.2088</v>
+        <v>11.2392</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.3837</v>
+        <v>0.4683</v>
       </c>
       <c r="J166" t="n">
-        <v>9.2088</v>
+        <v>11.2392</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7315</v>
+        <v>0.9207</v>
       </c>
       <c r="J167" t="n">
-        <v>17.556</v>
+        <v>22.0968</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.3642</v>
+        <v>-0.2445</v>
       </c>
       <c r="J168" t="n">
-        <v>-8.7408</v>
+        <v>-5.868</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.72</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4425</v>
+        <v>-0.2923</v>
       </c>
       <c r="J169" t="n">
-        <v>-10.62</v>
+        <v>-7.0152</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.67</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5145</v>
+        <v>-0.3398</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.348</v>
+        <v>-8.155200000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.46</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7841</v>
+        <v>-0.5349</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.8184</v>
+        <v>-12.8376</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1916</v>
+        <v>0.1423</v>
       </c>
       <c r="J172" t="n">
-        <v>5.1732</v>
+        <v>3.8421</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.05</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1725</v>
+        <v>0.1245</v>
       </c>
       <c r="J173" t="n">
-        <v>4.6575</v>
+        <v>3.3615</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2275</v>
+        <v>-0.1462</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.1425</v>
+        <v>-3.9474</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2454</v>
+        <v>-0.1567</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.6258</v>
+        <v>-4.2309</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5151</v>
+        <v>-0.335</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.9077</v>
+        <v>-9.045</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.32</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5048</v>
+        <v>0.4343</v>
       </c>
       <c r="J177" t="n">
-        <v>13.6296</v>
+        <v>11.7261</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.25</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4107</v>
+        <v>0.3506</v>
       </c>
       <c r="J178" t="n">
-        <v>11.0889</v>
+        <v>9.466200000000001</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1426</v>
+        <v>0.1461</v>
       </c>
       <c r="J179" t="n">
-        <v>3.8502</v>
+        <v>3.9447</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0872</v>
+        <v>0.1014</v>
       </c>
       <c r="J180" t="n">
-        <v>2.3544</v>
+        <v>2.7378</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2271</v>
+        <v>-0.1253</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.1317</v>
+        <v>-3.3831</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.29</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8456</v>
+        <v>0.8181</v>
       </c>
       <c r="J182" t="n">
-        <v>22.8312</v>
+        <v>22.0887</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7756</v>
+        <v>0.745</v>
       </c>
       <c r="J183" t="n">
-        <v>20.9412</v>
+        <v>20.115</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1258</v>
+        <v>0.152</v>
       </c>
       <c r="J184" t="n">
-        <v>3.3966</v>
+        <v>4.104</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1198</v>
+        <v>-0.0683</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.2346</v>
+        <v>-1.8441</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8334</v>
+        <v>-0.7927</v>
       </c>
       <c r="J186" t="n">
-        <v>-22.5018</v>
+        <v>-21.4029</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.6186</v>
+        <v>0.7522</v>
       </c>
       <c r="J187" t="n">
-        <v>16.7022</v>
+        <v>20.3094</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2602</v>
+        <v>0.2949</v>
       </c>
       <c r="J188" t="n">
-        <v>7.0254</v>
+        <v>7.9623</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2436</v>
+        <v>0.2756</v>
       </c>
       <c r="J189" t="n">
-        <v>6.5772</v>
+        <v>7.4412</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0624</v>
+        <v>-0.0245</v>
       </c>
       <c r="J190" t="n">
-        <v>-1.6848</v>
+        <v>-0.6615</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.6</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6521</v>
+        <v>-0.4338</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.6067</v>
+        <v>-11.7126</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.77</v>
       </c>
       <c r="I192" t="n">
-        <v>0.9341</v>
+        <v>0.859</v>
       </c>
       <c r="J192" t="n">
-        <v>19.6161</v>
+        <v>18.039</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.48</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6107</v>
+        <v>0.5677</v>
       </c>
       <c r="J193" t="n">
-        <v>12.8247</v>
+        <v>11.9217</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.45</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5709</v>
+        <v>0.5372</v>
       </c>
       <c r="J194" t="n">
-        <v>11.9889</v>
+        <v>11.2812</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>1.25</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>0.3187</v>
       </c>
       <c r="J195" t="n">
-        <v>6.3</v>
+        <v>6.6927</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>1.22</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2601</v>
+        <v>0.2825</v>
       </c>
       <c r="J196" t="n">
-        <v>5.4621</v>
+        <v>5.9325</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>0.85</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1301</v>
+        <v>-0.1295</v>
       </c>
       <c r="J197" t="n">
-        <v>-2.7321</v>
+        <v>-2.7195</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>0.73</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3199</v>
+        <v>-0.2594</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.7179</v>
+        <v>-5.4474</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.6</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.5501</v>
+        <v>-0.38</v>
       </c>
       <c r="J199" t="n">
-        <v>-11.5521</v>
+        <v>-7.98</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.581</v>
+        <v>-0.3984</v>
       </c>
       <c r="J200" t="n">
-        <v>-12.201</v>
+        <v>-8.366400000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.46</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7486</v>
+        <v>-0.5109</v>
       </c>
       <c r="J201" t="n">
-        <v>-15.7206</v>
+        <v>-10.7289</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>0.92</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0689</v>
+        <v>-0.0801</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.4469</v>
+        <v>-1.6821</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.8</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2742</v>
+        <v>-0.2117</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.7582</v>
+        <v>-4.4457</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.74</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.391</v>
+        <v>-0.2678</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.211</v>
+        <v>-5.6238</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.71</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4398</v>
+        <v>-0.296</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.235799999999999</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5288</v>
+        <v>-0.3525</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.1048</v>
+        <v>-7.4025</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>1.8938</v>
+        <v>1.5965</v>
       </c>
       <c r="J207" t="n">
-        <v>39.7698</v>
+        <v>33.5265</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0403</v>
+        <v>1.048</v>
       </c>
       <c r="J208" t="n">
-        <v>21.8463</v>
+        <v>22.008</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.35</v>
       </c>
       <c r="I209" t="n">
-        <v>0.795</v>
+        <v>0.8728</v>
       </c>
       <c r="J209" t="n">
-        <v>16.695</v>
+        <v>18.3288</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.3577</v>
+        <v>0.4538</v>
       </c>
       <c r="J210" t="n">
-        <v>7.5117</v>
+        <v>9.5298</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4887</v>
+        <v>-0.4106</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.2627</v>
+        <v>-8.6226</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>0.88</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.123</v>
+        <v>-0.1194</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.583</v>
+        <v>-2.5074</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.87</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1399</v>
+        <v>-0.1308</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.9379</v>
+        <v>-2.7468</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.86</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1566</v>
+        <v>-0.1421</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.2886</v>
+        <v>-2.9841</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5732</v>
+        <v>-0.3847</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.0372</v>
+        <v>-8.0787</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.43</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.8068</v>
+        <v>-0.5525</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.9428</v>
+        <v>-11.6025</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>1.8422</v>
+        <v>1.5633</v>
       </c>
       <c r="J217" t="n">
-        <v>38.6862</v>
+        <v>32.8293</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.6</v>
       </c>
       <c r="I218" t="n">
-        <v>1.279</v>
+        <v>1.2099</v>
       </c>
       <c r="J218" t="n">
-        <v>26.859</v>
+        <v>25.4079</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.52</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1106</v>
+        <v>1.1171</v>
       </c>
       <c r="J219" t="n">
-        <v>23.3226</v>
+        <v>23.4591</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.4</v>
       </c>
       <c r="I220" t="n">
-        <v>0.8293</v>
+        <v>0.9527</v>
       </c>
       <c r="J220" t="n">
-        <v>17.4153</v>
+        <v>20.0067</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0263</v>
+        <v>0.1177</v>
       </c>
       <c r="J221" t="n">
-        <v>0.5523</v>
+        <v>2.4717</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.33</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9248</v>
+        <v>0.9048</v>
       </c>
       <c r="J222" t="n">
-        <v>25.8944</v>
+        <v>25.3344</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.21</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6419</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J223" t="n">
-        <v>17.9732</v>
+        <v>17.1752</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4549</v>
+        <v>0.4334</v>
       </c>
       <c r="J224" t="n">
-        <v>12.7372</v>
+        <v>12.1352</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>1.05</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1466</v>
+        <v>0.1802</v>
       </c>
       <c r="J225" t="n">
-        <v>4.1048</v>
+        <v>5.0456</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9512</v>
+        <v>-0.9213</v>
       </c>
       <c r="J226" t="n">
-        <v>-26.6336</v>
+        <v>-25.7964</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7218</v>
+        <v>0.8942</v>
       </c>
       <c r="J227" t="n">
-        <v>20.2104</v>
+        <v>25.0376</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0033</v>
+        <v>0.0298</v>
       </c>
       <c r="J228" t="n">
-        <v>0.0924</v>
+        <v>0.8344</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.98</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.092</v>
+        <v>-0.0414</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.576</v>
+        <v>-1.1592</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1926</v>
+        <v>-0.1062</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.3928</v>
+        <v>-2.9736</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.89</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2607</v>
+        <v>-0.1517</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.2996</v>
+        <v>-4.2476</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.8</v>
       </c>
       <c r="I232" t="n">
-        <v>1.775</v>
+        <v>1.5096</v>
       </c>
       <c r="J232" t="n">
-        <v>49.7</v>
+        <v>42.2688</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.29</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7585</v>
+        <v>0.7663</v>
       </c>
       <c r="J233" t="n">
-        <v>21.238</v>
+        <v>21.4564</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.17</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4232</v>
+        <v>0.4846</v>
       </c>
       <c r="J234" t="n">
-        <v>11.8496</v>
+        <v>13.5688</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.365</v>
+        <v>-0.2867</v>
       </c>
       <c r="J235" t="n">
-        <v>-10.22</v>
+        <v>-8.0276</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.4644</v>
       </c>
       <c r="J236" t="n">
-        <v>-14.9744</v>
+        <v>-13.0032</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.04</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1501</v>
+        <v>0.1368</v>
       </c>
       <c r="J237" t="n">
-        <v>4.2028</v>
+        <v>3.8304</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.02</v>
       </c>
       <c r="I238" t="n">
-        <v>0.1064</v>
+        <v>0.0849</v>
       </c>
       <c r="J238" t="n">
-        <v>2.9792</v>
+        <v>2.3772</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2121</v>
+        <v>-0.1362</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.9388</v>
+        <v>-3.8136</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2985</v>
+        <v>-0.1884</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.358000000000001</v>
+        <v>-5.2752</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.376</v>
+        <v>-0.2388</v>
       </c>
       <c r="J241" t="n">
-        <v>-10.528</v>
+        <v>-6.6864</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2371</v>
+        <v>0.2527</v>
       </c>
       <c r="J242" t="n">
-        <v>6.4017</v>
+        <v>6.8229</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.05</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1458</v>
+        <v>0.1445</v>
       </c>
       <c r="J243" t="n">
-        <v>3.9366</v>
+        <v>3.9015</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1253</v>
+        <v>0.121</v>
       </c>
       <c r="J244" t="n">
-        <v>3.3831</v>
+        <v>3.267</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1037</v>
+        <v>0.0965</v>
       </c>
       <c r="J245" t="n">
-        <v>2.7999</v>
+        <v>2.6055</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.66</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5675</v>
+        <v>-0.3712</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.3225</v>
+        <v>-10.0224</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.7</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6664</v>
+        <v>1.437</v>
       </c>
       <c r="J247" t="n">
-        <v>44.9928</v>
+        <v>38.799</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3048</v>
+        <v>0.2988</v>
       </c>
       <c r="J248" t="n">
-        <v>8.2296</v>
+        <v>8.067600000000001</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4336</v>
+        <v>-0.3711</v>
       </c>
       <c r="J249" t="n">
-        <v>-11.7072</v>
+        <v>-10.0197</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.87</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.5168</v>
+        <v>-0.4562</v>
       </c>
       <c r="J250" t="n">
-        <v>-13.9536</v>
+        <v>-12.3174</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.83</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6211</v>
+        <v>-0.5649</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.7697</v>
+        <v>-15.2523</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.21</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4063</v>
+        <v>0.4652</v>
       </c>
       <c r="J252" t="n">
-        <v>10.9701</v>
+        <v>12.5604</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0179</v>
+        <v>0.0032</v>
       </c>
       <c r="J253" t="n">
-        <v>0.4833</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0477</v>
+        <v>-0.0344</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.2879</v>
+        <v>-0.9288</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1245</v>
+        <v>-0.0736</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.3615</v>
+        <v>-1.9872</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.74</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4622</v>
+        <v>-0.2952</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.4794</v>
+        <v>-7.9704</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9679</v>
+        <v>0.9484</v>
       </c>
       <c r="J257" t="n">
-        <v>26.1333</v>
+        <v>25.6068</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.14</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4534</v>
+        <v>0.4328</v>
       </c>
       <c r="J258" t="n">
-        <v>12.2418</v>
+        <v>11.6856</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1451</v>
+        <v>0.1798</v>
       </c>
       <c r="J259" t="n">
-        <v>3.9177</v>
+        <v>4.8546</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1755</v>
+        <v>-0.115</v>
       </c>
       <c r="J260" t="n">
-        <v>-4.7385</v>
+        <v>-3.105</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.408</v>
+        <v>-0.3441</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.016</v>
+        <v>-9.290699999999999</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.09</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3509</v>
+        <v>0.3127</v>
       </c>
       <c r="J262" t="n">
-        <v>10.1761</v>
+        <v>9.068300000000001</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1795</v>
+        <v>0.1591</v>
       </c>
       <c r="J263" t="n">
-        <v>5.2055</v>
+        <v>4.6139</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0358</v>
+        <v>0.0501</v>
       </c>
       <c r="J264" t="n">
-        <v>1.0382</v>
+        <v>1.4529</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.99</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0911</v>
+        <v>-0.058</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.6419</v>
+        <v>-1.682</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.98</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1366</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-3.9614</v>
+        <v>-2.8594</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.4</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6263</v>
+        <v>0.7634</v>
       </c>
       <c r="J267" t="n">
-        <v>18.1627</v>
+        <v>22.1386</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.37</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5895</v>
+        <v>0.7138</v>
       </c>
       <c r="J268" t="n">
-        <v>17.0955</v>
+        <v>20.7002</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2109</v>
+        <v>-0.1181</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.1161</v>
+        <v>-3.4249</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3822</v>
+        <v>-0.2357</v>
       </c>
       <c r="J270" t="n">
-        <v>-11.0838</v>
+        <v>-6.8353</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3964</v>
+        <v>-0.2458</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.4956</v>
+        <v>-7.1282</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.8</v>
       </c>
       <c r="I272" t="n">
-        <v>1.6451</v>
+        <v>1.4362</v>
       </c>
       <c r="J272" t="n">
-        <v>31.2569</v>
+        <v>27.2878</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.7</v>
       </c>
       <c r="I273" t="n">
-        <v>1.4633</v>
+        <v>1.3226</v>
       </c>
       <c r="J273" t="n">
-        <v>27.8027</v>
+        <v>25.1294</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.67</v>
       </c>
       <c r="I274" t="n">
-        <v>1.4068</v>
+        <v>1.2883</v>
       </c>
       <c r="J274" t="n">
-        <v>26.7292</v>
+        <v>24.4777</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>1.61</v>
       </c>
       <c r="I275" t="n">
-        <v>1.2901</v>
+        <v>1.2193</v>
       </c>
       <c r="J275" t="n">
-        <v>24.5119</v>
+        <v>23.1667</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.8</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7877</v>
+        <v>-0.7373</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.9663</v>
+        <v>-14.0087</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2599</v>
+        <v>0.296</v>
       </c>
       <c r="J277" t="n">
-        <v>4.9381</v>
+        <v>5.624</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.77</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2012</v>
+        <v>-0.1836</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.8228</v>
+        <v>-3.4884</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.38</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.8247</v>
+        <v>-0.5688</v>
       </c>
       <c r="J279" t="n">
-        <v>-15.6693</v>
+        <v>-10.8072</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.36</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.8515</v>
+        <v>-0.5883</v>
       </c>
       <c r="J280" t="n">
-        <v>-16.1785</v>
+        <v>-11.1777</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.21</v>
       </c>
       <c r="I281" t="n">
-        <v>-1.0415</v>
+        <v>-0.7363</v>
       </c>
       <c r="J281" t="n">
-        <v>-19.7885</v>
+        <v>-13.9897</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.01</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0794</v>
+        <v>0.0544</v>
       </c>
       <c r="J282" t="n">
-        <v>2.3026</v>
+        <v>1.5776</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.99</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0092</v>
+        <v>-0.0129</v>
       </c>
       <c r="J283" t="n">
-        <v>0.2668</v>
+        <v>-0.3741</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0837</v>
+        <v>-0.0692</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.4273</v>
+        <v>-2.0068</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.743</v>
+        <v>-4.8778</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.79</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3772</v>
+        <v>-0.2393</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.9388</v>
+        <v>-6.9397</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3027</v>
+        <v>1.1911</v>
       </c>
       <c r="J287" t="n">
-        <v>37.7783</v>
+        <v>34.5419</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.2</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5675</v>
       </c>
       <c r="J288" t="n">
-        <v>16.472</v>
+        <v>16.4575</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.229</v>
+        <v>0.2838</v>
       </c>
       <c r="J289" t="n">
-        <v>6.641</v>
+        <v>8.2302</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.02</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0053</v>
+        <v>0.058</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.1537</v>
+        <v>1.682</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.95</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3139</v>
+        <v>-0.2397</v>
       </c>
       <c r="J291" t="n">
-        <v>-9.1031</v>
+        <v>-6.9513</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.05</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1804</v>
+        <v>0.1693</v>
       </c>
       <c r="J292" t="n">
-        <v>4.6904</v>
+        <v>4.4018</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1606</v>
+        <v>0.145</v>
       </c>
       <c r="J293" t="n">
-        <v>4.1756</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.88</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2156</v>
+        <v>-0.1443</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.6056</v>
+        <v>-3.7518</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2156</v>
+        <v>-0.1443</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.6056</v>
+        <v>-3.7518</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.6</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.6276</v>
+        <v>-0.4168</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.3176</v>
+        <v>-10.8368</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.38</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9608</v>
+        <v>0.9633</v>
       </c>
       <c r="J297" t="n">
-        <v>24.9808</v>
+        <v>25.0458</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.33</v>
       </c>
       <c r="I298" t="n">
-        <v>0.849</v>
+        <v>0.8558</v>
       </c>
       <c r="J298" t="n">
-        <v>22.074</v>
+        <v>22.2508</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.25</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6538</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="J299" t="n">
-        <v>16.9988</v>
+        <v>17.4954</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.08</v>
       </c>
       <c r="I300" t="n">
-        <v>0.1675</v>
+        <v>0.2395</v>
       </c>
       <c r="J300" t="n">
-        <v>4.355</v>
+        <v>6.227</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>1.07</v>
       </c>
       <c r="I301" t="n">
-        <v>0.1373</v>
+        <v>0.2096</v>
       </c>
       <c r="J301" t="n">
-        <v>3.5698</v>
+        <v>5.4496</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.12</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2748</v>
+        <v>0.2968</v>
       </c>
       <c r="J302" t="n">
-        <v>8.244</v>
+        <v>8.904</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>0.95</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1178</v>
+        <v>-0.0726</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.534</v>
+        <v>-2.178</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1393</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.179</v>
+        <v>-2.538</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.92</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1788</v>
+        <v>-0.1079</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.364</v>
+        <v>-3.237</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2328</v>
+        <v>-0.1412</v>
       </c>
       <c r="J306" t="n">
-        <v>-6.984</v>
+        <v>-4.236</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8733</v>
+        <v>0.8525</v>
       </c>
       <c r="J307" t="n">
-        <v>26.199</v>
+        <v>25.575</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.17</v>
       </c>
       <c r="I308" t="n">
-        <v>0.53</v>
+        <v>0.5082</v>
       </c>
       <c r="J308" t="n">
-        <v>15.9</v>
+        <v>15.246</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4166</v>
+        <v>0.4039</v>
       </c>
       <c r="J309" t="n">
-        <v>12.498</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.07</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2069</v>
+        <v>0.2391</v>
       </c>
       <c r="J310" t="n">
-        <v>6.207</v>
+        <v>7.173</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.7014</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="J311" t="n">
-        <v>-21.042</v>
+        <v>-19.461</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.22</v>
       </c>
       <c r="I312" t="n">
-        <v>0.431</v>
+        <v>0.4949</v>
       </c>
       <c r="J312" t="n">
-        <v>11.206</v>
+        <v>12.8674</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3439</v>
+        <v>0.3816</v>
       </c>
       <c r="J313" t="n">
-        <v>8.9414</v>
+        <v>9.9216</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>0.89</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2259</v>
+        <v>-0.1393</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.8734</v>
+        <v>-3.6218</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>0.87</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2602</v>
+        <v>-0.1607</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.7652</v>
+        <v>-4.1782</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.59</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6498</v>
+        <v>-0.4326</v>
       </c>
       <c r="J316" t="n">
-        <v>-16.8948</v>
+        <v>-11.2476</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.33</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8811</v>
+        <v>0.8738</v>
       </c>
       <c r="J317" t="n">
-        <v>22.9086</v>
+        <v>22.7188</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1.27</v>
       </c>
       <c r="I318" t="n">
-        <v>0.7417</v>
+        <v>0.7339</v>
       </c>
       <c r="J318" t="n">
-        <v>19.2842</v>
+        <v>19.0814</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>1.21</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5906</v>
+        <v>0.5905</v>
       </c>
       <c r="J319" t="n">
-        <v>15.3556</v>
+        <v>15.353</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>1.17</v>
       </c>
       <c r="I320" t="n">
-        <v>0.4758</v>
+        <v>0.493</v>
       </c>
       <c r="J320" t="n">
-        <v>12.3708</v>
+        <v>12.818</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.84</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.623</v>
+        <v>-0.5611</v>
       </c>
       <c r="J321" t="n">
-        <v>-16.198</v>
+        <v>-14.5886</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4680/event_4680_evp_summary.xlsx
+++ b/database/event/4680/event_4680_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2277</v>
+        <v>5.3434</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1392</v>
+        <v>1.1644</v>
       </c>
       <c r="D2" t="n">
-        <v>1.722</v>
+        <v>1.8082</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2277</v>
+        <v>5.3434</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4935</v>
+        <v>1.5198</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7342</v>
+        <v>3.8236</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4935</v>
+        <v>1.5198</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6854</v>
+        <v>1.6403</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7342</v>
+        <v>3.8236</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>196</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4196</v>
+        <v>5.4639</v>
       </c>
       <c r="N2" t="n">
         <v>328</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2001</v>
+        <v>4.1656</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9152</v>
+        <v>0.9077</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2581</v>
+        <v>1.2721</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2001</v>
+        <v>4.1656</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2237</v>
+        <v>3.1041</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9764</v>
+        <v>1.0615</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8719</v>
+        <v>5.3475</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0531</v>
+        <v>2.8876</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9764</v>
+        <v>1.0615</v>
       </c>
       <c r="K3" t="n">
         <v>112</v>
@@ -575,7 +575,7 @@
         <v>88</v>
       </c>
       <c r="M3" t="n">
-        <v>4.029500000000001</v>
+        <v>3.9491</v>
       </c>
       <c r="N3" t="n">
         <v>200</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0491</v>
+        <v>4.1494</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8823</v>
+        <v>0.9042</v>
       </c>
       <c r="D4" t="n">
-        <v>1.19</v>
+        <v>1.2647</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0491</v>
+        <v>4.1494</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4699</v>
+        <v>2.3801</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5792</v>
+        <v>1.7693</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2161</v>
+        <v>2.9586</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6722</v>
+        <v>1.5976</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5792</v>
+        <v>1.7693</v>
       </c>
       <c r="K4" t="n">
         <v>112</v>
@@ -621,7 +621,7 @@
         <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2514</v>
+        <v>3.3669</v>
       </c>
       <c r="N4" t="n">
         <v>200</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8219</v>
+        <v>3.8753</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8328</v>
+        <v>0.8445</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0874</v>
+        <v>1.1399</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8219</v>
+        <v>3.8753</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0223</v>
+        <v>2.973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7996</v>
+        <v>0.9023</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1624</v>
+        <v>4.9147</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6842</v>
+        <v>2.6539</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7996</v>
+        <v>0.9023</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -667,7 +667,7 @@
         <v>88</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4838</v>
+        <v>3.5562</v>
       </c>
       <c r="N5" t="n">
         <v>200</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5662</v>
+        <v>3.6846</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7771</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9719</v>
+        <v>1.0531</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5662</v>
+        <v>3.6846</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7653</v>
+        <v>0.7572</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8008</v>
+        <v>2.9273</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7653</v>
+        <v>0.7572</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8637</v>
+        <v>0.8173</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8008</v>
+        <v>2.9273</v>
       </c>
       <c r="K6" t="n">
         <v>132</v>
@@ -713,7 +713,7 @@
         <v>196</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6645</v>
+        <v>3.7446</v>
       </c>
       <c r="N6" t="n">
         <v>328</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5514</v>
+        <v>3.6553</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7739</v>
+        <v>0.7965</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9653</v>
+        <v>1.0398</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5514</v>
+        <v>3.6553</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8286</v>
+        <v>1.3986</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7228</v>
+        <v>2.2567</v>
       </c>
       <c r="H7" t="n">
-        <v>4.48</v>
+        <v>1.3986</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3294</v>
+        <v>1.5095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7228</v>
+        <v>2.2567</v>
       </c>
       <c r="K7" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="M7" t="n">
-        <v>3.0522</v>
+        <v>3.7662</v>
       </c>
       <c r="N7" t="n">
-        <v>262</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4635</v>
+        <v>3.5496</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7547</v>
+        <v>0.7735</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9256</v>
+        <v>0.9916</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4635</v>
+        <v>3.5496</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3902</v>
+        <v>2.7668</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0733</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3902</v>
+        <v>4.2345</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5689</v>
+        <v>2.2866</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0733</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L8" t="n">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6422</v>
+        <v>3.0694</v>
       </c>
       <c r="N8" t="n">
-        <v>328</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4384</v>
+        <v>3.2602</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7493</v>
+        <v>0.7104</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9143</v>
+        <v>0.8599</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4384</v>
+        <v>3.2602</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7726</v>
+        <v>2.5193</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.7409</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7726</v>
+        <v>2.789</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0053</v>
+        <v>2.9346</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.7409</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6711</v>
+        <v>3.6755</v>
       </c>
       <c r="N9" t="n">
         <v>231</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7082</v>
+        <v>2.7987</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5901</v>
+        <v>0.6099</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5846</v>
+        <v>0.6498</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7082</v>
+        <v>2.7987</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4049</v>
+        <v>1.3592</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3033</v>
+        <v>1.4395</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4049</v>
+        <v>1.3592</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5228</v>
+        <v>1.4302</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3033</v>
+        <v>1.4395</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>87</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8261</v>
+        <v>2.8697</v>
       </c>
       <c r="N10" t="n">
         <v>231</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6626</v>
+        <v>2.611</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5802</v>
+        <v>0.569</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5644</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6626</v>
+        <v>2.611</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8786</v>
+        <v>1.8658</v>
       </c>
       <c r="G11" t="n">
-        <v>0.784</v>
+        <v>0.7452</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8786</v>
+        <v>1.8658</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9768</v>
+        <v>1.0075</v>
       </c>
       <c r="J11" t="n">
-        <v>0.784</v>
+        <v>0.7452</v>
       </c>
       <c r="K11" t="n">
         <v>126</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7608</v>
+        <v>1.7527</v>
       </c>
       <c r="N11" t="n">
         <v>262</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4698</v>
+        <v>2.5376</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5382</v>
+        <v>0.553</v>
       </c>
       <c r="D12" t="n">
-        <v>0.477</v>
+        <v>0.531</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4698</v>
+        <v>2.5376</v>
       </c>
       <c r="F12" t="n">
-        <v>2.686</v>
+        <v>0.9928</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2162</v>
+        <v>1.5448</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9775</v>
+        <v>0.9928</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0681</v>
+        <v>1.0446</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2162</v>
+        <v>1.5448</v>
       </c>
       <c r="K12" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L12" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8519</v>
+        <v>2.5894</v>
       </c>
       <c r="N12" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4077</v>
+        <v>2.4245</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5283</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4489</v>
+        <v>0.4795</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4077</v>
+        <v>2.4245</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0475</v>
+        <v>2.635</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3602</v>
+        <v>-0.2105</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0475</v>
+        <v>3.7997</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1354</v>
+        <v>2.0518</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3602</v>
+        <v>-0.2105</v>
       </c>
       <c r="K13" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L13" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4956</v>
+        <v>1.8413</v>
       </c>
       <c r="N13" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3375</v>
+        <v>2.3188</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5094</v>
+        <v>0.5053</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4173</v>
+        <v>0.4314</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3375</v>
+        <v>2.3188</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2007</v>
+        <v>1.4304</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8632</v>
+        <v>0.8884</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7909</v>
+        <v>1.4304</v>
       </c>
       <c r="I14" t="n">
-        <v>3.011</v>
+        <v>1.5051</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8632</v>
+        <v>0.8884</v>
       </c>
       <c r="K14" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L14" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1478</v>
+        <v>2.3935</v>
       </c>
       <c r="N14" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2486</v>
+        <v>2.2549</v>
       </c>
       <c r="C15" t="n">
-        <v>0.49</v>
+        <v>0.4914</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3771</v>
+        <v>0.4023</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2486</v>
+        <v>2.2549</v>
       </c>
       <c r="F15" t="n">
-        <v>1.398</v>
+        <v>3.1308</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8506</v>
+        <v>-0.8759</v>
       </c>
       <c r="H15" t="n">
-        <v>1.398</v>
+        <v>5.4355</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5154</v>
+        <v>2.9351</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8506</v>
+        <v>-0.8759</v>
       </c>
       <c r="K15" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L15" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="M15" t="n">
-        <v>2.366</v>
+        <v>2.0592</v>
       </c>
       <c r="N15" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2341</v>
+        <v>2.2219</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4868</v>
+        <v>0.4842</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3706</v>
+        <v>0.3873</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2341</v>
+        <v>2.2219</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0699</v>
+        <v>2.0696</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1642</v>
+        <v>0.1523</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0699</v>
+        <v>2.0696</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2437</v>
+        <v>2.1776</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1642</v>
+        <v>0.1523</v>
       </c>
       <c r="K16" t="n">
         <v>118</v>
@@ -1173,7 +1173,7 @@
         <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4079</v>
+        <v>2.3299</v>
       </c>
       <c r="N16" t="n">
         <v>173</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0049</v>
+        <v>2.0475</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4369</v>
+        <v>0.4462</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2671</v>
+        <v>0.3079</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0049</v>
+        <v>2.0475</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7184</v>
+        <v>1.7085</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2865</v>
+        <v>0.339</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7184</v>
+        <v>1.7085</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8627</v>
+        <v>1.7977</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2865</v>
+        <v>0.339</v>
       </c>
       <c r="K17" t="n">
         <v>144</v>
@@ -1219,7 +1219,7 @@
         <v>87</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1492</v>
+        <v>2.1367</v>
       </c>
       <c r="N17" t="n">
         <v>231</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.9265</v>
+        <v>1.8885</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4198</v>
+        <v>0.4115</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2317</v>
+        <v>0.2355</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9265</v>
+        <v>1.8885</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4792</v>
+        <v>1.4072</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4473</v>
+        <v>0.4813</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4792</v>
+        <v>1.4072</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6034</v>
+        <v>1.4807</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4473</v>
+        <v>0.4813</v>
       </c>
       <c r="K18" t="n">
         <v>118</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0507</v>
+        <v>1.962</v>
       </c>
       <c r="N18" t="n">
         <v>173</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7215</v>
+        <v>1.7274</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3751</v>
+        <v>0.3764</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1392</v>
+        <v>0.1621</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7215</v>
+        <v>1.7274</v>
       </c>
       <c r="F19" t="n">
-        <v>0.851</v>
+        <v>0.828</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8994</v>
       </c>
       <c r="H19" t="n">
-        <v>0.851</v>
+        <v>0.828</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4425</v>
+        <v>0.4471</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8994</v>
       </c>
       <c r="K19" t="n">
         <v>126</v>
@@ -1311,7 +1311,7 @@
         <v>136</v>
       </c>
       <c r="M19" t="n">
-        <v>1.313</v>
+        <v>1.3465</v>
       </c>
       <c r="N19" t="n">
         <v>262</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4273</v>
+        <v>1.3961</v>
       </c>
       <c r="C20" t="n">
-        <v>0.311</v>
+        <v>0.3042</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0063</v>
+        <v>0.0113</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4273</v>
+        <v>1.3961</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4273</v>
+        <v>1.153</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.2431</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4273</v>
+        <v>1.153</v>
       </c>
       <c r="I20" t="n">
-        <v>1.486</v>
+        <v>0.6226</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.2431</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M20" t="n">
-        <v>1.486</v>
+        <v>0.8657</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.329</v>
+        <v>1.3517</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2896</v>
+        <v>0.2945</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.038</v>
+        <v>-0.0089</v>
       </c>
       <c r="E21" t="n">
-        <v>1.329</v>
+        <v>1.3517</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1463</v>
+        <v>1.3517</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1827</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1463</v>
+        <v>1.3517</v>
       </c>
       <c r="I21" t="n">
-        <v>0.596</v>
+        <v>1.3865</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1827</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7786999999999999</v>
+        <v>1.3865</v>
       </c>
       <c r="N21" t="n">
-        <v>200</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2619</v>
+        <v>1.2912</v>
       </c>
       <c r="C22" t="n">
-        <v>0.275</v>
+        <v>0.2814</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0683</v>
+        <v>-0.0364</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2619</v>
+        <v>1.2912</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3187</v>
+        <v>1.257</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0568</v>
+        <v>0.0342</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3187</v>
+        <v>1.257</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4294</v>
+        <v>1.3226</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0568</v>
+        <v>0.0342</v>
       </c>
       <c r="K22" t="n">
         <v>111</v>
@@ -1449,7 +1449,7 @@
         <v>170</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3726</v>
+        <v>1.3568</v>
       </c>
       <c r="N22" t="n">
         <v>281</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9217</v>
+        <v>1.0365</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2008</v>
+        <v>0.2259</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2219</v>
+        <v>-0.1524</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9217</v>
+        <v>1.0365</v>
       </c>
       <c r="F23" t="n">
-        <v>0.511</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4107</v>
+        <v>0.4977</v>
       </c>
       <c r="H23" t="n">
-        <v>0.511</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5669</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4107</v>
+        <v>0.4977</v>
       </c>
       <c r="K23" t="n">
         <v>111</v>
@@ -1495,7 +1495,7 @@
         <v>170</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9645999999999999</v>
+        <v>1.0646</v>
       </c>
       <c r="N23" t="n">
         <v>281</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7478</v>
+        <v>0.6903</v>
       </c>
       <c r="C24" t="n">
-        <v>0.163</v>
+        <v>0.1504</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3004</v>
+        <v>-0.31</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7478</v>
+        <v>0.6903</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2184</v>
+        <v>1.1853</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4706</v>
+        <v>-0.495</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2184</v>
+        <v>1.1853</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3207</v>
+        <v>1.2472</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4706</v>
+        <v>-0.495</v>
       </c>
       <c r="K24" t="n">
         <v>118</v>
@@ -1541,7 +1541,7 @@
         <v>55</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8501</v>
+        <v>0.7522000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>173</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1536</v>
+        <v>0.1416</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3197</v>
+        <v>-0.3283</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7341</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7341</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>119</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4935</v>
+        <v>0.443</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1075</v>
+        <v>0.0965</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4152</v>
+        <v>-0.4225</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4935</v>
+        <v>0.443</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4935</v>
+        <v>0.443</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4935</v>
+        <v>0.443</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5138</v>
+        <v>0.4544</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5138</v>
+        <v>0.4544</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2909</v>
+        <v>0.254</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0634</v>
+        <v>0.0553</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5067</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2909</v>
+        <v>0.254</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2909</v>
+        <v>0.254</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2909</v>
+        <v>0.254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3029</v>
+        <v>0.2605</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3029</v>
+        <v>0.2605</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.103</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0224</v>
+        <v>0.014</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5915</v>
+        <v>-0.595</v>
       </c>
       <c r="E28" t="n">
-        <v>0.103</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5875</v>
+        <v>-1.0851</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4845</v>
+        <v>1.1493</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5875</v>
+        <v>-1.0851</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6368</v>
+        <v>-1.1712</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4845</v>
+        <v>1.1493</v>
       </c>
       <c r="K28" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L28" t="n">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1523</v>
+        <v>-0.02190000000000003</v>
       </c>
       <c r="N28" t="n">
-        <v>173</v>
+        <v>328</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0583</v>
+        <v>0.0453</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0127</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6117</v>
+        <v>-0.6036</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0583</v>
+        <v>0.0453</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0583</v>
+        <v>0.5611</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.5158</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0583</v>
+        <v>0.5611</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0607</v>
+        <v>0.5904</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.5158</v>
       </c>
       <c r="K29" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0607</v>
+        <v>0.0746</v>
       </c>
       <c r="N29" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0636</v>
+        <v>0.0421</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0139</v>
+        <v>0.0092</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6667</v>
+        <v>-0.605</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0636</v>
+        <v>0.0421</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.064</v>
+        <v>0.0421</v>
       </c>
       <c r="G30" t="n">
-        <v>1.0004</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.064</v>
+        <v>0.0421</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.2008</v>
+        <v>0.0432</v>
       </c>
       <c r="J30" t="n">
-        <v>1.0004</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L30" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2004000000000001</v>
+        <v>0.0432</v>
       </c>
       <c r="N30" t="n">
-        <v>328</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0888</v>
+        <v>-0.0897</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0194</v>
+        <v>-0.0195</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6781</v>
+        <v>-0.665</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0888</v>
+        <v>-0.0897</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1957</v>
+        <v>0.2057</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2845</v>
+        <v>-0.2954</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1957</v>
+        <v>0.2057</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2121</v>
+        <v>0.2164</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2845</v>
+        <v>-0.2954</v>
       </c>
       <c r="K31" t="n">
         <v>118</v>
@@ -1863,7 +1863,7 @@
         <v>55</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07239999999999996</v>
+        <v>-0.07899999999999999</v>
       </c>
       <c r="N31" t="n">
         <v>173</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1007</v>
+        <v>-0.1275</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0219</v>
+        <v>-0.0278</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6835</v>
+        <v>-0.6822</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1007</v>
+        <v>-0.1275</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4158</v>
+        <v>0.4001</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5165</v>
+        <v>-0.5276</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4158</v>
+        <v>0.4001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4507</v>
+        <v>0.421</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5165</v>
+        <v>-0.5276</v>
       </c>
       <c r="K32" t="n">
         <v>111</v>
@@ -1909,7 +1909,7 @@
         <v>170</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.06579999999999997</v>
+        <v>-0.1066</v>
       </c>
       <c r="N32" t="n">
         <v>281</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1436</v>
+        <v>-0.1977</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0313</v>
+        <v>-0.0431</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7028</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1436</v>
+        <v>-0.1977</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1436</v>
+        <v>-0.1977</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1436</v>
+        <v>-0.1977</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1495</v>
+        <v>-0.2028</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1495</v>
+        <v>-0.2028</v>
       </c>
       <c r="N33" t="n">
         <v>119</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2352</v>
+        <v>-0.24</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0513</v>
+        <v>-0.0523</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7442</v>
+        <v>-0.7335</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2352</v>
+        <v>-0.24</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2352</v>
+        <v>-0.24</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2352</v>
+        <v>-0.24</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2549</v>
+        <v>-0.2525</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2549</v>
+        <v>-0.2525</v>
       </c>
       <c r="N34" t="n">
         <v>144</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3055</v>
+        <v>-0.3292</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0717</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7759</v>
+        <v>-0.7741</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3055</v>
+        <v>-0.3292</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3055</v>
+        <v>-0.3292</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3055</v>
+        <v>-0.3292</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3181</v>
+        <v>-0.3377</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3181</v>
+        <v>-0.3377</v>
       </c>
       <c r="N35" t="n">
         <v>119</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4875</v>
+        <v>-0.5347</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1062</v>
+        <v>-0.1165</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8581</v>
+        <v>-0.8676</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4875</v>
+        <v>-0.5347</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4875</v>
+        <v>-0.5347</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4875</v>
+        <v>-0.5347</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5075</v>
+        <v>-0.5485</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5075</v>
+        <v>-0.5485</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5226</v>
+        <v>-0.5594</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1139</v>
+        <v>-0.1219</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8739</v>
+        <v>-0.8789</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5226</v>
+        <v>-0.5594</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.5226</v>
+        <v>-0.5594</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5226</v>
+        <v>-0.5594</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>87</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.5226</v>
+        <v>-0.5594</v>
       </c>
       <c r="N37" t="n">
         <v>87</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5877</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1402</v>
+        <v>-0.1281</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9286</v>
+        <v>-0.8917</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.5877</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1692</v>
+        <v>-0.1718</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4744</v>
+        <v>-0.4159</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1692</v>
+        <v>-0.1718</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.191</v>
+        <v>-0.1854</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4744</v>
+        <v>-0.4159</v>
       </c>
       <c r="K38" t="n">
         <v>132</v>
@@ -2185,7 +2185,7 @@
         <v>196</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6654</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>328</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0031</v>
+        <v>-1.1049</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2186</v>
+        <v>-0.2408</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0909</v>
+        <v>-1.1272</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0031</v>
+        <v>-1.1049</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0031</v>
+        <v>-1.1049</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0031</v>
+        <v>-1.1049</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0444</v>
+        <v>-1.1334</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0444</v>
+        <v>-1.1334</v>
       </c>
       <c r="N39" t="n">
         <v>138</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1432</v>
+        <v>-1.1606</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2491</v>
+        <v>-0.2529</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1541</v>
+        <v>-1.1525</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1432</v>
+        <v>-1.1606</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.49</v>
+        <v>-0.494</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6532</v>
+        <v>-0.6666</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.49</v>
+        <v>-0.494</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5311</v>
+        <v>-0.5198</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6532</v>
+        <v>-0.6666</v>
       </c>
       <c r="K40" t="n">
         <v>144</v>
@@ -2277,7 +2277,7 @@
         <v>87</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1843</v>
+        <v>-1.1864</v>
       </c>
       <c r="N40" t="n">
         <v>231</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7332</v>
+        <v>-1.7797</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3777</v>
+        <v>-0.3878</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4205</v>
+        <v>-1.4344</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7332</v>
+        <v>-1.7797</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7332</v>
+        <v>-1.7797</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7332</v>
+        <v>-1.7797</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8045</v>
+        <v>-1.8256</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8045</v>
+        <v>-1.8256</v>
       </c>
       <c r="N41" t="n">
         <v>138</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.7998</v>
+        <v>-2.5012</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.6101</v>
+        <v>-0.545</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.902</v>
+        <v>-1.7628</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.7998</v>
+        <v>-2.5012</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.5012</v>
+        <v>-2.2037</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2986</v>
+        <v>-0.2975</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.5012</v>
+        <v>-2.2037</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.3005</v>
+        <v>-1.19</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2986</v>
+        <v>-0.2975</v>
       </c>
       <c r="K42" t="n">
         <v>112</v>
@@ -2369,7 +2369,7 @@
         <v>88</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.5991</v>
+        <v>-1.4875</v>
       </c>
       <c r="N42" t="n">
         <v>200</v>
@@ -2475,10 +2475,10 @@
         <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4589</v>
+        <v>0.4414</v>
       </c>
       <c r="J2" t="n">
-        <v>11.9314</v>
+        <v>11.4764</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1818</v>
+        <v>-0.1991</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.7268</v>
+        <v>-5.1766</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2115</v>
+        <v>-0.2289</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.499</v>
+        <v>-5.9514</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2313</v>
+        <v>-0.2485</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.0138</v>
+        <v>-6.461</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3563</v>
+        <v>-0.3702</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.2638</v>
+        <v>-9.6252</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9605</v>
+        <v>0.9044</v>
       </c>
       <c r="J7" t="n">
-        <v>24.973</v>
+        <v>23.5144</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8979</v>
+        <v>0.8462</v>
       </c>
       <c r="J8" t="n">
-        <v>23.3454</v>
+        <v>22.0012</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4814</v>
+        <v>0.4752</v>
       </c>
       <c r="J9" t="n">
-        <v>12.5164</v>
+        <v>12.3552</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.456</v>
+        <v>0.4522</v>
       </c>
       <c r="J10" t="n">
-        <v>11.856</v>
+        <v>11.7572</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.295</v>
+        <v>0.305</v>
       </c>
       <c r="J11" t="n">
-        <v>7.67</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7484</v>
+        <v>0.7059</v>
       </c>
       <c r="J12" t="n">
-        <v>20.2068</v>
+        <v>19.0593</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1329</v>
+        <v>-0.1488</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.5883</v>
+        <v>-4.0176</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.78</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2434</v>
+        <v>-0.26</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.5718</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2727</v>
+        <v>-0.2887</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.3629</v>
+        <v>-7.7949</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4055</v>
+        <v>-0.4169</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.9485</v>
+        <v>-11.2563</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.36</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9372</v>
+        <v>0.8786</v>
       </c>
       <c r="J17" t="n">
-        <v>25.3044</v>
+        <v>23.7222</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8474</v>
+        <v>0.7988</v>
       </c>
       <c r="J18" t="n">
-        <v>22.8798</v>
+        <v>21.5676</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.18</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5159</v>
+        <v>0.5043</v>
       </c>
       <c r="J19" t="n">
-        <v>13.9293</v>
+        <v>13.6161</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0129</v>
+        <v>0.0308</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3483</v>
+        <v>0.8316</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.042</v>
+        <v>-0.029</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.134</v>
+        <v>-0.783</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.59</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5389</v>
+        <v>0.6212</v>
       </c>
       <c r="J22" t="n">
-        <v>11.8558</v>
+        <v>13.6664</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.521</v>
+        <v>0.6002</v>
       </c>
       <c r="J23" t="n">
-        <v>11.462</v>
+        <v>13.2044</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4667</v>
+        <v>0.5361</v>
       </c>
       <c r="J24" t="n">
-        <v>10.2674</v>
+        <v>11.7942</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.34</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3867</v>
+        <v>0.4377</v>
       </c>
       <c r="J25" t="n">
-        <v>8.507400000000001</v>
+        <v>9.6294</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>1.12</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1554</v>
+        <v>0.1795</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4188</v>
+        <v>3.949</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0.344</v>
+        <v>0.3377</v>
       </c>
       <c r="J27" t="n">
-        <v>7.568</v>
+        <v>7.4294</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2096</v>
+        <v>-0.2297</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.6112</v>
+        <v>-5.0534</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.7</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3034</v>
+        <v>-0.3221</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.6748</v>
+        <v>-7.0862</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.64</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3597</v>
+        <v>-0.3763</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.9134</v>
+        <v>-8.278600000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5275</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.605</v>
+        <v>-11.7656</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.505</v>
+        <v>0.5599</v>
       </c>
       <c r="J32" t="n">
-        <v>18.18</v>
+        <v>20.1564</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2093</v>
+        <v>0.2156</v>
       </c>
       <c r="J33" t="n">
-        <v>7.5348</v>
+        <v>7.7616</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1024</v>
       </c>
       <c r="J34" t="n">
-        <v>3.4272</v>
+        <v>3.6864</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2765</v>
+        <v>-0.2898</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.954000000000001</v>
+        <v>-10.4328</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2959</v>
+        <v>-0.3088</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.6524</v>
+        <v>-11.1168</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8548</v>
+        <v>0.9382</v>
       </c>
       <c r="J37" t="n">
-        <v>30.7728</v>
+        <v>33.7752</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3586</v>
+        <v>0.3733</v>
       </c>
       <c r="J38" t="n">
-        <v>12.9096</v>
+        <v>13.4388</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3419</v>
+        <v>0.3488</v>
       </c>
       <c r="J39" t="n">
-        <v>12.3084</v>
+        <v>12.5568</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1757</v>
+        <v>0.1857</v>
       </c>
       <c r="J40" t="n">
-        <v>6.3252</v>
+        <v>6.6852</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7278</v>
+        <v>-0.6764</v>
       </c>
       <c r="J41" t="n">
-        <v>-26.2008</v>
+        <v>-24.3504</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6875</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>20.625</v>
+        <v>23.151</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3004</v>
+        <v>0.3098</v>
       </c>
       <c r="J43" t="n">
-        <v>9.012</v>
+        <v>9.294</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1655</v>
+        <v>0.1787</v>
       </c>
       <c r="J44" t="n">
-        <v>4.965</v>
+        <v>5.361</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0618</v>
+        <v>-0.0673</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.854</v>
+        <v>-2.019</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1581</v>
+        <v>-0.1682</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.743</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.57</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0411</v>
+        <v>1.1271</v>
       </c>
       <c r="J47" t="n">
-        <v>31.233</v>
+        <v>33.813</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.95</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.19</v>
+        <v>-0.1953</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.7</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.89</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3688</v>
+        <v>-0.3622</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.064</v>
+        <v>-10.866</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7903</v>
+        <v>-0.7379</v>
       </c>
       <c r="J50" t="n">
-        <v>-23.709</v>
+        <v>-22.137</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8401</v>
+        <v>-0.7813</v>
       </c>
       <c r="J51" t="n">
-        <v>-25.203</v>
+        <v>-23.439</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2958</v>
+        <v>0.3012</v>
       </c>
       <c r="J52" t="n">
-        <v>8.874000000000001</v>
+        <v>9.036</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2813</v>
+        <v>0.2872</v>
       </c>
       <c r="J53" t="n">
-        <v>8.439</v>
+        <v>8.616</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1548</v>
+        <v>-0.1682</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.644</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1548</v>
+        <v>-0.1682</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.644</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1866</v>
+        <v>-0.2004</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.598</v>
+        <v>-6.012</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.55</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5636</v>
+        <v>0.64</v>
       </c>
       <c r="J57" t="n">
-        <v>16.908</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>0.97</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0535</v>
+        <v>-0.0608</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.605</v>
+        <v>-1.824</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1156</v>
+        <v>-0.1266</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.468</v>
+        <v>-3.798</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1493</v>
+        <v>-0.1614</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.479</v>
+        <v>-4.842</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.85</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1921</v>
+        <v>-0.2047</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.763</v>
+        <v>-6.141</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6822</v>
+        <v>0.751</v>
       </c>
       <c r="J62" t="n">
-        <v>18.4194</v>
+        <v>20.277</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.25</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5553</v>
+        <v>0.6116</v>
       </c>
       <c r="J63" t="n">
-        <v>14.9931</v>
+        <v>16.5132</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.04</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1458</v>
+        <v>0.1562</v>
       </c>
       <c r="J64" t="n">
-        <v>3.9366</v>
+        <v>4.2174</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1166</v>
+        <v>-0.1153</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.1482</v>
+        <v>-3.1131</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.515</v>
+        <v>-0.4875</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.905</v>
+        <v>-13.1625</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5062</v>
+        <v>0.5653</v>
       </c>
       <c r="J67" t="n">
-        <v>13.6674</v>
+        <v>15.2631</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3625</v>
+        <v>0.3852</v>
       </c>
       <c r="J68" t="n">
-        <v>9.7875</v>
+        <v>10.4004</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0562</v>
+        <v>0.0664</v>
       </c>
       <c r="J69" t="n">
-        <v>1.5174</v>
+        <v>1.7928</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1049</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.5839</v>
+        <v>-2.8323</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1422</v>
+        <v>-0.1531</v>
       </c>
       <c r="J71" t="n">
-        <v>-3.8394</v>
+        <v>-4.1337</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5101</v>
+        <v>0.5619</v>
       </c>
       <c r="J72" t="n">
-        <v>13.2626</v>
+        <v>14.6094</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3902</v>
+        <v>0.4212</v>
       </c>
       <c r="J73" t="n">
-        <v>10.1452</v>
+        <v>10.9512</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3215</v>
+        <v>0.3243</v>
       </c>
       <c r="J74" t="n">
-        <v>8.359</v>
+        <v>8.431800000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.09</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2958</v>
+        <v>0.2988</v>
       </c>
       <c r="J75" t="n">
-        <v>7.6908</v>
+        <v>7.7688</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2242</v>
+        <v>-0.219</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.8292</v>
+        <v>-5.694</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2254</v>
+        <v>0.2273</v>
       </c>
       <c r="J77" t="n">
-        <v>5.8604</v>
+        <v>5.9098</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0528</v>
+        <v>0.0542</v>
       </c>
       <c r="J78" t="n">
-        <v>1.3728</v>
+        <v>1.4092</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0528</v>
+        <v>0.0542</v>
       </c>
       <c r="J79" t="n">
-        <v>1.3728</v>
+        <v>1.4092</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.86</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1689</v>
+        <v>-0.1843</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.3914</v>
+        <v>-4.7918</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.67</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3559</v>
+        <v>-0.3682</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.253399999999999</v>
+        <v>-9.5732</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.08</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2314</v>
+        <v>0.2317</v>
       </c>
       <c r="J82" t="n">
-        <v>6.0164</v>
+        <v>6.0242</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.02</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0872</v>
+        <v>0.0886</v>
       </c>
       <c r="J83" t="n">
-        <v>2.2672</v>
+        <v>2.3036</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0185</v>
+        <v>0.0133</v>
       </c>
       <c r="J84" t="n">
-        <v>0.481</v>
+        <v>0.3458</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2179</v>
+        <v>-0.2338</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.6654</v>
+        <v>-6.0788</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.63</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3911</v>
+        <v>-0.4025</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.1686</v>
+        <v>-10.465</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.61</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9823</v>
+        <v>1.0838</v>
       </c>
       <c r="J87" t="n">
-        <v>25.5398</v>
+        <v>28.1788</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8466</v>
+        <v>0.9384</v>
       </c>
       <c r="J88" t="n">
-        <v>22.0116</v>
+        <v>24.3984</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4566</v>
+        <v>0.5082</v>
       </c>
       <c r="J89" t="n">
-        <v>11.8716</v>
+        <v>13.2132</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.442</v>
+        <v>0.4918</v>
       </c>
       <c r="J90" t="n">
-        <v>11.492</v>
+        <v>12.7868</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1273</v>
+        <v>-0.11</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.3098</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4288</v>
+        <v>0.468</v>
       </c>
       <c r="J92" t="n">
-        <v>12.4352</v>
+        <v>13.572</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0672</v>
+        <v>-0.0794</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.9488</v>
+        <v>-2.3026</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0795</v>
+        <v>-0.0925</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.3055</v>
+        <v>-2.6825</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2666</v>
+        <v>-0.282</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.7314</v>
+        <v>-8.178000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3717</v>
+        <v>-0.384</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.7793</v>
+        <v>-11.136</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.52</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8888</v>
+        <v>0.9804</v>
       </c>
       <c r="J97" t="n">
-        <v>25.7752</v>
+        <v>28.4316</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5478</v>
+        <v>0.6085</v>
       </c>
       <c r="J98" t="n">
-        <v>15.8862</v>
+        <v>17.6465</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5069</v>
+        <v>0.5627</v>
       </c>
       <c r="J99" t="n">
-        <v>14.7001</v>
+        <v>16.3183</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.12</v>
       </c>
       <c r="I100" t="n">
-        <v>0.345</v>
+        <v>0.3583</v>
       </c>
       <c r="J100" t="n">
-        <v>10.005</v>
+        <v>10.3907</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2215</v>
+        <v>-0.2085</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.4235</v>
+        <v>-6.0465</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5453</v>
+        <v>0.6071</v>
       </c>
       <c r="J102" t="n">
-        <v>13.6325</v>
+        <v>15.1775</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1869</v>
+        <v>0.1928</v>
       </c>
       <c r="J103" t="n">
-        <v>4.6725</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.75</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2804</v>
+        <v>-0.2947</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.01</v>
+        <v>-7.3675</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2997</v>
+        <v>-0.3136</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.4925</v>
+        <v>-7.84</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3756</v>
+        <v>-0.3871</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.6775</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.56</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5526</v>
+        <v>0.6306</v>
       </c>
       <c r="J107" t="n">
-        <v>13.815</v>
+        <v>15.765</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.14</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2126</v>
+        <v>0.2292</v>
       </c>
       <c r="J108" t="n">
-        <v>5.315</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1309</v>
+        <v>0.1467</v>
       </c>
       <c r="J109" t="n">
-        <v>3.2725</v>
+        <v>3.6675</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0122</v>
+        <v>-0.0094</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.305</v>
+        <v>-0.235</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1598</v>
+        <v>-0.1695</v>
       </c>
       <c r="J111" t="n">
-        <v>-3.995</v>
+        <v>-4.2375</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.37</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7332</v>
+        <v>0.8045</v>
       </c>
       <c r="J112" t="n">
-        <v>20.5296</v>
+        <v>22.526</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.15</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4127</v>
+        <v>0.449</v>
       </c>
       <c r="J113" t="n">
-        <v>11.5556</v>
+        <v>12.572</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1192</v>
+        <v>0.1282</v>
       </c>
       <c r="J114" t="n">
-        <v>3.3376</v>
+        <v>3.5896</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3363</v>
+        <v>-0.3266</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.416399999999999</v>
+        <v>-9.1448</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5592</v>
+        <v>-0.529</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.6576</v>
+        <v>-14.812</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.46</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6552</v>
+        <v>0.731</v>
       </c>
       <c r="J117" t="n">
-        <v>18.3456</v>
+        <v>20.468</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0359</v>
+        <v>0.0421</v>
       </c>
       <c r="J118" t="n">
-        <v>1.0052</v>
+        <v>1.1788</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.91</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.125</v>
+        <v>-0.1369</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.5</v>
+        <v>-3.8332</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.88</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1582</v>
+        <v>-0.1709</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.4296</v>
+        <v>-4.7852</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.83</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2107</v>
+        <v>-0.2238</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.8996</v>
+        <v>-6.2664</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.494</v>
+        <v>0.5442</v>
       </c>
       <c r="J122" t="n">
-        <v>16.796</v>
+        <v>18.5028</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4497</v>
+        <v>0.4944</v>
       </c>
       <c r="J123" t="n">
-        <v>15.2898</v>
+        <v>16.8096</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3582</v>
+        <v>0.3729</v>
       </c>
       <c r="J124" t="n">
-        <v>12.1788</v>
+        <v>12.6786</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1748</v>
+        <v>0.185</v>
       </c>
       <c r="J125" t="n">
-        <v>5.9432</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.98</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1209</v>
+        <v>-0.1182</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.1106</v>
+        <v>-4.0188</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.499</v>
+        <v>0.5521</v>
       </c>
       <c r="J127" t="n">
-        <v>16.966</v>
+        <v>18.7714</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4355</v>
+        <v>0.4793</v>
       </c>
       <c r="J128" t="n">
-        <v>14.807</v>
+        <v>16.2962</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1079</v>
+        <v>-0.1207</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.6686</v>
+        <v>-4.1038</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1521</v>
+        <v>-0.1661</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.1714</v>
+        <v>-5.6474</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.5</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.516</v>
+        <v>-0.5203</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.544</v>
+        <v>-17.6902</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.48</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6188</v>
+        <v>0.6178</v>
       </c>
       <c r="J132" t="n">
-        <v>22.2768</v>
+        <v>22.2408</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.36</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4818</v>
+        <v>0.4893</v>
       </c>
       <c r="J133" t="n">
-        <v>17.3448</v>
+        <v>17.6148</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3634</v>
+        <v>0.3765</v>
       </c>
       <c r="J134" t="n">
-        <v>13.0824</v>
+        <v>13.554</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.79</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2624</v>
+        <v>-0.2728</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.446400000000001</v>
+        <v>-9.8208</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.73</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3206</v>
+        <v>-0.3301</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.5416</v>
+        <v>-11.8836</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.18</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3254</v>
+        <v>0.3263</v>
       </c>
       <c r="J137" t="n">
-        <v>11.7144</v>
+        <v>11.7468</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1194</v>
+        <v>0.1253</v>
       </c>
       <c r="J138" t="n">
-        <v>4.2984</v>
+        <v>4.5108</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1591</v>
+        <v>-0.1742</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.7276</v>
+        <v>-6.2712</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2107</v>
+        <v>-0.2261</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.5852</v>
+        <v>-8.1396</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2898</v>
+        <v>-0.304</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.4328</v>
+        <v>-10.944</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5098</v>
+        <v>0.4861</v>
       </c>
       <c r="J142" t="n">
-        <v>14.2744</v>
+        <v>13.6108</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0568</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.5904</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1802</v>
+        <v>-0.1979</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.0456</v>
+        <v>-5.5412</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3532</v>
+        <v>-0.3679</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.8896</v>
+        <v>-10.3012</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4834</v>
+        <v>-0.4917</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.5352</v>
+        <v>-13.7676</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.55</v>
       </c>
       <c r="I147" t="n">
-        <v>1.199</v>
+        <v>1.167</v>
       </c>
       <c r="J147" t="n">
-        <v>33.572</v>
+        <v>32.676</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.45</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0718</v>
+        <v>1.0276</v>
       </c>
       <c r="J148" t="n">
-        <v>30.0104</v>
+        <v>28.7728</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6956</v>
+        <v>0.6675</v>
       </c>
       <c r="J149" t="n">
-        <v>19.4768</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0003</v>
+        <v>0.0221</v>
       </c>
       <c r="J150" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.6188</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.5113</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.3692</v>
+        <v>-14.3164</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.06</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2032</v>
+        <v>0.2003</v>
       </c>
       <c r="J152" t="n">
-        <v>5.2832</v>
+        <v>5.2078</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1795</v>
+        <v>0.1771</v>
       </c>
       <c r="J153" t="n">
-        <v>4.667</v>
+        <v>4.6046</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0863</v>
+        <v>-0.101</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.2438</v>
+        <v>-2.626</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.85</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1724</v>
+        <v>-0.1895</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.4824</v>
+        <v>-4.927</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.42</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5775</v>
+        <v>-0.5796</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.015</v>
+        <v>-15.0696</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8762</v>
+        <v>0.8269</v>
       </c>
       <c r="J157" t="n">
-        <v>22.7812</v>
+        <v>21.4994</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.29</v>
       </c>
       <c r="I158" t="n">
-        <v>0.763</v>
+        <v>0.7275</v>
       </c>
       <c r="J158" t="n">
-        <v>19.838</v>
+        <v>18.915</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.24</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6486</v>
+        <v>0.6258</v>
       </c>
       <c r="J159" t="n">
-        <v>16.8636</v>
+        <v>16.2708</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4818</v>
+        <v>0.4755</v>
       </c>
       <c r="J160" t="n">
-        <v>12.5268</v>
+        <v>12.363</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>1.11</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3235</v>
+        <v>0.3312</v>
       </c>
       <c r="J161" t="n">
-        <v>8.411</v>
+        <v>8.6112</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.69</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3545</v>
+        <v>1.3355</v>
       </c>
       <c r="J162" t="n">
-        <v>32.508</v>
+        <v>32.052</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5917</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="J163" t="n">
-        <v>14.2008</v>
+        <v>13.8504</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5676</v>
+        <v>0.5556</v>
       </c>
       <c r="J164" t="n">
-        <v>13.6224</v>
+        <v>13.3344</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4683</v>
+        <v>0.4663</v>
       </c>
       <c r="J165" t="n">
-        <v>11.2392</v>
+        <v>11.1912</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4683</v>
+        <v>0.4663</v>
       </c>
       <c r="J166" t="n">
-        <v>11.2392</v>
+        <v>11.1912</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.9207</v>
+        <v>0.8531</v>
       </c>
       <c r="J167" t="n">
-        <v>22.0968</v>
+        <v>20.4744</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2445</v>
+        <v>-0.2629</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.868</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.72</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2923</v>
+        <v>-0.3097</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.0152</v>
+        <v>-7.4328</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.67</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3398</v>
+        <v>-0.3557</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.155200000000001</v>
+        <v>-8.536799999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.46</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5349</v>
+        <v>-0.5406</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.8376</v>
+        <v>-12.9744</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.1423</v>
+        <v>0.147</v>
       </c>
       <c r="J172" t="n">
-        <v>3.8421</v>
+        <v>3.969</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.05</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1245</v>
+        <v>0.1291</v>
       </c>
       <c r="J173" t="n">
-        <v>3.3615</v>
+        <v>3.4857</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1462</v>
+        <v>-0.1616</v>
       </c>
       <c r="J174" t="n">
-        <v>-3.9474</v>
+        <v>-4.3632</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1567</v>
+        <v>-0.1723</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.2309</v>
+        <v>-4.6521</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.335</v>
+        <v>-0.3484</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.045</v>
+        <v>-9.4068</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.32</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4343</v>
+        <v>0.4444</v>
       </c>
       <c r="J177" t="n">
-        <v>11.7261</v>
+        <v>11.9988</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.25</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3506</v>
+        <v>0.3643</v>
       </c>
       <c r="J178" t="n">
-        <v>9.466200000000001</v>
+        <v>9.8361</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1461</v>
+        <v>0.1619</v>
       </c>
       <c r="J179" t="n">
-        <v>3.9447</v>
+        <v>4.3713</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1014</v>
+        <v>0.1162</v>
       </c>
       <c r="J180" t="n">
-        <v>2.7378</v>
+        <v>3.1374</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1253</v>
+        <v>-0.1343</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.3831</v>
+        <v>-3.6261</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.29</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8181</v>
+        <v>0.7659</v>
       </c>
       <c r="J182" t="n">
-        <v>22.0887</v>
+        <v>20.6793</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.745</v>
+        <v>0.7018</v>
       </c>
       <c r="J183" t="n">
-        <v>20.115</v>
+        <v>18.9486</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.152</v>
+        <v>0.1604</v>
       </c>
       <c r="J184" t="n">
-        <v>4.104</v>
+        <v>4.3308</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0683</v>
+        <v>-0.0689</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.8441</v>
+        <v>-1.8603</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7927</v>
+        <v>-0.7353</v>
       </c>
       <c r="J186" t="n">
-        <v>-21.4029</v>
+        <v>-19.8531</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7522</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>20.3094</v>
+        <v>19.5021</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2949</v>
+        <v>0.3014</v>
       </c>
       <c r="J188" t="n">
-        <v>7.9623</v>
+        <v>8.1378</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2756</v>
+        <v>0.2829</v>
       </c>
       <c r="J189" t="n">
-        <v>7.4412</v>
+        <v>7.6383</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0245</v>
+        <v>-0.0283</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.6615</v>
+        <v>-0.7641</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.6</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4338</v>
+        <v>-0.4408</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.7126</v>
+        <v>-11.9016</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.77</v>
       </c>
       <c r="I192" t="n">
-        <v>0.859</v>
+        <v>0.85</v>
       </c>
       <c r="J192" t="n">
-        <v>18.039</v>
+        <v>17.85</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.48</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5677</v>
+        <v>0.5789</v>
       </c>
       <c r="J193" t="n">
-        <v>11.9217</v>
+        <v>12.1569</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.45</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5372</v>
+        <v>0.55</v>
       </c>
       <c r="J194" t="n">
-        <v>11.2812</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>1.25</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3187</v>
+        <v>0.3403</v>
       </c>
       <c r="J195" t="n">
-        <v>6.6927</v>
+        <v>7.1463</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>1.22</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2825</v>
+        <v>0.3053</v>
       </c>
       <c r="J196" t="n">
-        <v>5.9325</v>
+        <v>6.4113</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>0.85</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1295</v>
+        <v>-0.1561</v>
       </c>
       <c r="J197" t="n">
-        <v>-2.7195</v>
+        <v>-3.2781</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>0.73</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2594</v>
+        <v>-0.2825</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.4474</v>
+        <v>-5.9325</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.6</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.38</v>
+        <v>-0.3986</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.98</v>
+        <v>-8.3706</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3984</v>
+        <v>-0.4161</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.366400000000001</v>
+        <v>-8.738099999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.46</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5109</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.7289</v>
+        <v>-10.9557</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>0.92</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0801</v>
+        <v>-0.0993</v>
       </c>
       <c r="J202" t="n">
-        <v>-1.6821</v>
+        <v>-2.0853</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.8</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2117</v>
+        <v>-0.2313</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.4457</v>
+        <v>-4.8573</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.74</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2678</v>
+        <v>-0.287</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.6238</v>
+        <v>-6.027</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.71</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.296</v>
+        <v>-0.3145</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.216</v>
+        <v>-6.6045</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3525</v>
+        <v>-0.369</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.4025</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5965</v>
+        <v>1.5931</v>
       </c>
       <c r="J207" t="n">
-        <v>33.5265</v>
+        <v>33.4551</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.048</v>
+        <v>1.0047</v>
       </c>
       <c r="J208" t="n">
-        <v>22.008</v>
+        <v>21.0987</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.35</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8728</v>
+        <v>0.8289</v>
       </c>
       <c r="J209" t="n">
-        <v>18.3288</v>
+        <v>17.4069</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4538</v>
+        <v>0.4561</v>
       </c>
       <c r="J210" t="n">
-        <v>9.5298</v>
+        <v>9.578099999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4106</v>
+        <v>-0.3787</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.6226</v>
+        <v>-7.9527</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>0.88</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1194</v>
+        <v>-0.141</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.5074</v>
+        <v>-2.961</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.87</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1308</v>
+        <v>-0.1524</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.7468</v>
+        <v>-3.2004</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.86</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1421</v>
+        <v>-0.1637</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.9841</v>
+        <v>-3.4377</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3847</v>
+        <v>-0.4007</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.0787</v>
+        <v>-8.4147</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.43</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5525</v>
+        <v>-0.5585</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.6025</v>
+        <v>-11.7285</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5633</v>
+        <v>1.5636</v>
       </c>
       <c r="J217" t="n">
-        <v>32.8293</v>
+        <v>32.8356</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.6</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2099</v>
+        <v>1.1884</v>
       </c>
       <c r="J218" t="n">
-        <v>25.4079</v>
+        <v>24.9564</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.52</v>
       </c>
       <c r="I219" t="n">
-        <v>1.1171</v>
+        <v>1.088</v>
       </c>
       <c r="J219" t="n">
-        <v>23.4591</v>
+        <v>22.848</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.4</v>
       </c>
       <c r="I220" t="n">
-        <v>0.9527</v>
+        <v>0.9062</v>
       </c>
       <c r="J220" t="n">
-        <v>20.0067</v>
+        <v>19.0302</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1177</v>
+        <v>0.1531</v>
       </c>
       <c r="J221" t="n">
-        <v>2.4717</v>
+        <v>3.2151</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.33</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9048</v>
+        <v>0.8431</v>
       </c>
       <c r="J222" t="n">
-        <v>25.3344</v>
+        <v>23.6068</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.21</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.5869</v>
       </c>
       <c r="J223" t="n">
-        <v>17.1752</v>
+        <v>16.4332</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.4334</v>
+        <v>0.425</v>
       </c>
       <c r="J224" t="n">
-        <v>12.1352</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>1.05</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1802</v>
+        <v>0.1888</v>
       </c>
       <c r="J225" t="n">
-        <v>5.0456</v>
+        <v>5.2864</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.9213</v>
+        <v>-0.8466</v>
       </c>
       <c r="J226" t="n">
-        <v>-25.7964</v>
+        <v>-23.7048</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8942</v>
+        <v>0.8501</v>
       </c>
       <c r="J227" t="n">
-        <v>25.0376</v>
+        <v>23.8028</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0298</v>
+        <v>0.0378</v>
       </c>
       <c r="J228" t="n">
-        <v>0.8344</v>
+        <v>1.0584</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.98</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0414</v>
+        <v>-0.0469</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.1592</v>
+        <v>-1.3132</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1062</v>
+        <v>-0.1163</v>
       </c>
       <c r="J230" t="n">
-        <v>-2.9736</v>
+        <v>-3.2564</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.89</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1517</v>
+        <v>-0.1632</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.2476</v>
+        <v>-4.5696</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.8</v>
       </c>
       <c r="I232" t="n">
-        <v>1.5096</v>
+        <v>1.4952</v>
       </c>
       <c r="J232" t="n">
-        <v>42.2688</v>
+        <v>41.8656</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.29</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7663</v>
+        <v>0.7298</v>
       </c>
       <c r="J233" t="n">
-        <v>21.4564</v>
+        <v>20.4344</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.17</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4846</v>
+        <v>0.4775</v>
       </c>
       <c r="J234" t="n">
-        <v>13.5688</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2867</v>
+        <v>-0.2706</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.0276</v>
+        <v>-7.5768</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4644</v>
+        <v>-0.4351</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.0032</v>
+        <v>-12.1828</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.04</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1368</v>
+        <v>0.1396</v>
       </c>
       <c r="J237" t="n">
-        <v>3.8304</v>
+        <v>3.9088</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.02</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0849</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>2.3772</v>
+        <v>2.436</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1362</v>
+        <v>-0.1512</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.8136</v>
+        <v>-4.2336</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1884</v>
+        <v>-0.2042</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.2752</v>
+        <v>-5.7176</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2388</v>
+        <v>-0.2544</v>
       </c>
       <c r="J241" t="n">
-        <v>-6.6864</v>
+        <v>-7.1232</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2527</v>
+        <v>0.2571</v>
       </c>
       <c r="J242" t="n">
-        <v>6.8229</v>
+        <v>6.9417</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.05</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1445</v>
+        <v>0.1516</v>
       </c>
       <c r="J243" t="n">
-        <v>3.9015</v>
+        <v>4.0932</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.121</v>
+        <v>0.1282</v>
       </c>
       <c r="J244" t="n">
-        <v>3.267</v>
+        <v>3.4614</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0965</v>
+        <v>0.1033</v>
       </c>
       <c r="J245" t="n">
-        <v>2.6055</v>
+        <v>2.7891</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.66</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3712</v>
+        <v>-0.3819</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.0224</v>
+        <v>-10.3113</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.7</v>
       </c>
       <c r="I247" t="n">
-        <v>1.437</v>
+        <v>1.4109</v>
       </c>
       <c r="J247" t="n">
-        <v>38.799</v>
+        <v>38.0943</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2988</v>
+        <v>0.3008</v>
       </c>
       <c r="J248" t="n">
-        <v>8.067600000000001</v>
+        <v>8.121600000000001</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3711</v>
+        <v>-0.3575</v>
       </c>
       <c r="J249" t="n">
-        <v>-10.0197</v>
+        <v>-9.6525</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.87</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4562</v>
+        <v>-0.4351</v>
       </c>
       <c r="J250" t="n">
-        <v>-12.3174</v>
+        <v>-11.7477</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.83</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5649</v>
+        <v>-0.533</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.2523</v>
+        <v>-14.391</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.21</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4652</v>
+        <v>0.4567</v>
       </c>
       <c r="J252" t="n">
-        <v>12.5604</v>
+        <v>12.3309</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0032</v>
+        <v>0.0022</v>
       </c>
       <c r="J253" t="n">
-        <v>0.0864</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0344</v>
+        <v>-0.0416</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.9288</v>
+        <v>-1.1232</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0736</v>
+        <v>-0.0843</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.9872</v>
+        <v>-2.2761</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.74</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2952</v>
+        <v>-0.3082</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.9704</v>
+        <v>-8.321400000000001</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9484</v>
+        <v>0.8833</v>
       </c>
       <c r="J257" t="n">
-        <v>25.6068</v>
+        <v>23.8491</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.14</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4328</v>
+        <v>0.4247</v>
       </c>
       <c r="J258" t="n">
-        <v>11.6856</v>
+        <v>11.4669</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1798</v>
+        <v>0.1885</v>
       </c>
       <c r="J259" t="n">
-        <v>4.8546</v>
+        <v>5.0895</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.115</v>
+        <v>-0.1142</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.105</v>
+        <v>-3.0834</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3441</v>
+        <v>-0.3321</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.290699999999999</v>
+        <v>-8.966699999999999</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.09</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3127</v>
+        <v>0.3103</v>
       </c>
       <c r="J262" t="n">
-        <v>9.068300000000001</v>
+        <v>8.998699999999999</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1591</v>
+        <v>0.1652</v>
       </c>
       <c r="J263" t="n">
-        <v>4.6139</v>
+        <v>4.7908</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0501</v>
+        <v>0.0565</v>
       </c>
       <c r="J264" t="n">
-        <v>1.4529</v>
+        <v>1.6385</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.99</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.058</v>
+        <v>-0.0618</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.682</v>
+        <v>-1.7922</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.98</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1028</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.8594</v>
+        <v>-2.9812</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.4</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7634</v>
+        <v>0.7332</v>
       </c>
       <c r="J267" t="n">
-        <v>22.1386</v>
+        <v>21.2628</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.37</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7138</v>
+        <v>0.6886</v>
       </c>
       <c r="J268" t="n">
-        <v>20.7002</v>
+        <v>19.9694</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1181</v>
+        <v>-0.1287</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.4249</v>
+        <v>-3.7323</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2357</v>
+        <v>-0.2478</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.8353</v>
+        <v>-7.1862</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2458</v>
+        <v>-0.2577</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.1282</v>
+        <v>-7.4733</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.8</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4362</v>
+        <v>1.4302</v>
       </c>
       <c r="J272" t="n">
-        <v>27.2878</v>
+        <v>27.1738</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.7</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3226</v>
+        <v>1.3095</v>
       </c>
       <c r="J273" t="n">
-        <v>25.1294</v>
+        <v>24.8805</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.67</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2883</v>
+        <v>1.2729</v>
       </c>
       <c r="J274" t="n">
-        <v>24.4777</v>
+        <v>24.1851</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>1.61</v>
       </c>
       <c r="I275" t="n">
-        <v>1.2193</v>
+        <v>1.1989</v>
       </c>
       <c r="J275" t="n">
-        <v>23.1667</v>
+        <v>22.7791</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.8</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7373</v>
+        <v>-0.6693</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.0087</v>
+        <v>-12.7167</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.296</v>
+        <v>0.2342</v>
       </c>
       <c r="J277" t="n">
-        <v>5.624</v>
+        <v>4.4498</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.77</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1836</v>
+        <v>-0.2155</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.4884</v>
+        <v>-4.0945</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.38</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5688</v>
+        <v>-0.5778</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.8072</v>
+        <v>-10.9782</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.36</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5883</v>
+        <v>-0.5957</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.1777</v>
+        <v>-11.3183</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.21</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7363</v>
+        <v>-0.7305</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.9897</v>
+        <v>-13.8795</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.01</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0544</v>
+        <v>0.0553</v>
       </c>
       <c r="J282" t="n">
-        <v>1.5776</v>
+        <v>1.6037</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.99</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0129</v>
+        <v>-0.0194</v>
       </c>
       <c r="J283" t="n">
-        <v>-0.3741</v>
+        <v>-0.5626</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0692</v>
+        <v>-0.081</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.0068</v>
+        <v>-2.349</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.8778</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.79</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2393</v>
+        <v>-0.2547</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.9397</v>
+        <v>-7.3863</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1911</v>
+        <v>1.1553</v>
       </c>
       <c r="J287" t="n">
-        <v>34.5419</v>
+        <v>33.5037</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.2</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5675</v>
+        <v>0.5502</v>
       </c>
       <c r="J288" t="n">
-        <v>16.4575</v>
+        <v>15.9558</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2838</v>
+        <v>0.2906</v>
       </c>
       <c r="J289" t="n">
-        <v>8.2302</v>
+        <v>8.4274</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.02</v>
       </c>
       <c r="I290" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="J290" t="n">
-        <v>1.682</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.95</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2397</v>
+        <v>-0.2297</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.9513</v>
+        <v>-6.6613</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.05</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1693</v>
+        <v>0.1697</v>
       </c>
       <c r="J292" t="n">
-        <v>4.4018</v>
+        <v>4.4122</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.145</v>
+        <v>0.1456</v>
       </c>
       <c r="J293" t="n">
-        <v>3.77</v>
+        <v>3.7856</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.88</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1443</v>
+        <v>-0.1602</v>
       </c>
       <c r="J294" t="n">
-        <v>-3.7518</v>
+        <v>-4.1652</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1443</v>
+        <v>-0.1602</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.7518</v>
+        <v>-4.1652</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.6</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4168</v>
+        <v>-0.4274</v>
       </c>
       <c r="J296" t="n">
-        <v>-10.8368</v>
+        <v>-11.1124</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.38</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9633</v>
+        <v>0.9064</v>
       </c>
       <c r="J297" t="n">
-        <v>25.0458</v>
+        <v>23.5664</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.33</v>
       </c>
       <c r="I298" t="n">
-        <v>0.8558</v>
+        <v>0.8088</v>
       </c>
       <c r="J298" t="n">
-        <v>22.2508</v>
+        <v>21.0288</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.25</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6473</v>
       </c>
       <c r="J299" t="n">
-        <v>17.4954</v>
+        <v>16.8298</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.08</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2395</v>
+        <v>0.253</v>
       </c>
       <c r="J300" t="n">
-        <v>6.227</v>
+        <v>6.578</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>1.07</v>
       </c>
       <c r="I301" t="n">
-        <v>0.2096</v>
+        <v>0.225</v>
       </c>
       <c r="J301" t="n">
-        <v>5.4496</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.12</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2968</v>
+        <v>0.2984</v>
       </c>
       <c r="J302" t="n">
-        <v>8.904</v>
+        <v>8.952</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>0.95</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0726</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.178</v>
+        <v>-2.508</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.08459999999999999</v>
+        <v>-0.0963</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.538</v>
+        <v>-2.889</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.92</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1079</v>
+        <v>-0.1207</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.237</v>
+        <v>-3.621</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1412</v>
+        <v>-0.1551</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.236</v>
+        <v>-4.653</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.8525</v>
+        <v>0.7982</v>
       </c>
       <c r="J307" t="n">
-        <v>25.575</v>
+        <v>23.946</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.17</v>
       </c>
       <c r="I308" t="n">
-        <v>0.5082</v>
+        <v>0.4935</v>
       </c>
       <c r="J308" t="n">
-        <v>15.246</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4039</v>
+        <v>0.3988</v>
       </c>
       <c r="J309" t="n">
-        <v>12.117</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.07</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2391</v>
+        <v>0.2453</v>
       </c>
       <c r="J310" t="n">
-        <v>7.173</v>
+        <v>7.359</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.6068</v>
       </c>
       <c r="J311" t="n">
-        <v>-19.461</v>
+        <v>-18.204</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.22</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4949</v>
+        <v>0.482</v>
       </c>
       <c r="J312" t="n">
-        <v>12.8674</v>
+        <v>12.532</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3816</v>
+        <v>0.3769</v>
       </c>
       <c r="J313" t="n">
-        <v>9.9216</v>
+        <v>9.7994</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>0.89</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1393</v>
+        <v>-0.1536</v>
       </c>
       <c r="J314" t="n">
-        <v>-3.6218</v>
+        <v>-3.9936</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>0.87</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1607</v>
+        <v>-0.1754</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.1782</v>
+        <v>-4.5604</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.59</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4326</v>
+        <v>-0.4414</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.2476</v>
+        <v>-11.4764</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.33</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8738</v>
+        <v>0.8212</v>
       </c>
       <c r="J317" t="n">
-        <v>22.7188</v>
+        <v>21.3512</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1.27</v>
       </c>
       <c r="I318" t="n">
-        <v>0.7339</v>
+        <v>0.6985</v>
       </c>
       <c r="J318" t="n">
-        <v>19.0814</v>
+        <v>18.161</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>1.21</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5905</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J319" t="n">
-        <v>15.353</v>
+        <v>14.8486</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>1.17</v>
       </c>
       <c r="I320" t="n">
-        <v>0.493</v>
+        <v>0.4831</v>
       </c>
       <c r="J320" t="n">
-        <v>12.818</v>
+        <v>12.5606</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.84</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5611</v>
+        <v>-0.5252</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.5886</v>
+        <v>-13.6552</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4680/event_4680_evp_summary.xlsx
+++ b/database/event/4680/event_4680_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3434</v>
+        <v>5.2191</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1644</v>
+        <v>1.1373</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8082</v>
+        <v>1.7718</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3434</v>
+        <v>5.2191</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5198</v>
+        <v>1.4801</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8236</v>
+        <v>3.739</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5198</v>
+        <v>1.4801</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6403</v>
+        <v>1.6019</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8236</v>
+        <v>3.739</v>
       </c>
       <c r="K2" t="n">
         <v>132</v>
@@ -529,7 +529,7 @@
         <v>196</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4639</v>
+        <v>5.3409</v>
       </c>
       <c r="N2" t="n">
         <v>328</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.1656</v>
+        <v>4.0934</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9077</v>
+        <v>0.892</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2721</v>
+        <v>1.259</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1656</v>
+        <v>4.0934</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1041</v>
+        <v>2.4437</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0615</v>
+        <v>1.6497</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3475</v>
+        <v>2.7319</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8876</v>
+        <v>1.5339</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0615</v>
+        <v>1.6497</v>
       </c>
       <c r="K3" t="n">
         <v>112</v>
@@ -575,7 +575,7 @@
         <v>88</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9491</v>
+        <v>3.1836</v>
       </c>
       <c r="N3" t="n">
         <v>200</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1494</v>
+        <v>3.9664</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9042</v>
+        <v>0.8643</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2647</v>
+        <v>1.2011</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1494</v>
+        <v>3.9664</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3801</v>
+        <v>3.0314</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7693</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9586</v>
+        <v>4.9387</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5976</v>
+        <v>2.7729</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7693</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>112</v>
@@ -621,7 +621,7 @@
         <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3669</v>
+        <v>3.7079</v>
       </c>
       <c r="N4" t="n">
         <v>200</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8753</v>
+        <v>3.7444</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8445</v>
+        <v>0.8159</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1399</v>
+        <v>1.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8753</v>
+        <v>3.7444</v>
       </c>
       <c r="F5" t="n">
-        <v>2.973</v>
+        <v>2.9419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9023</v>
+        <v>0.8025</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9147</v>
+        <v>4.6026</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6539</v>
+        <v>2.5842</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9023</v>
+        <v>0.8025</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -667,7 +667,7 @@
         <v>88</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5562</v>
+        <v>3.3867</v>
       </c>
       <c r="N5" t="n">
         <v>200</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6846</v>
+        <v>3.6041</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7854</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0531</v>
+        <v>1.0361</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6846</v>
+        <v>3.6041</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7572</v>
+        <v>2.8485</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9273</v>
+        <v>0.7556</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7572</v>
+        <v>4.2519</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8173</v>
+        <v>2.3873</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9273</v>
+        <v>0.7556</v>
       </c>
       <c r="K6" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7446</v>
+        <v>3.1429</v>
       </c>
       <c r="N6" t="n">
-        <v>328</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6553</v>
+        <v>3.574</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7965</v>
+        <v>0.7788</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0398</v>
+        <v>1.0223</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6553</v>
+        <v>3.574</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3986</v>
+        <v>0.6884</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2567</v>
+        <v>2.8856</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3986</v>
+        <v>0.6884</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5095</v>
+        <v>0.745</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2567</v>
+        <v>2.8856</v>
       </c>
       <c r="K7" t="n">
         <v>132</v>
@@ -759,7 +759,7 @@
         <v>196</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7662</v>
+        <v>3.6306</v>
       </c>
       <c r="N7" t="n">
         <v>328</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5496</v>
+        <v>3.5477</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7735</v>
+        <v>0.7731</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9916</v>
+        <v>1.0104</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5496</v>
+        <v>3.5477</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7668</v>
+        <v>1.2742</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7828000000000001</v>
+        <v>2.2735</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2345</v>
+        <v>1.2742</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2866</v>
+        <v>1.3791</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7828000000000001</v>
+        <v>2.2735</v>
       </c>
       <c r="K8" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="L8" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0694</v>
+        <v>3.6526</v>
       </c>
       <c r="N8" t="n">
-        <v>262</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2602</v>
+        <v>3.1114</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7104</v>
+        <v>0.678</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8599</v>
+        <v>0.8116</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2602</v>
+        <v>3.1114</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5193</v>
+        <v>2.4474</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7409</v>
+        <v>0.664</v>
       </c>
       <c r="H9" t="n">
-        <v>2.789</v>
+        <v>2.6585</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9346</v>
+        <v>2.8025</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7409</v>
+        <v>0.664</v>
       </c>
       <c r="K9" t="n">
         <v>144</v>
@@ -851,7 +851,7 @@
         <v>87</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6755</v>
+        <v>3.4665</v>
       </c>
       <c r="N9" t="n">
         <v>231</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7987</v>
+        <v>2.6092</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6099</v>
+        <v>0.5686</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6498</v>
+        <v>0.5828</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7987</v>
+        <v>2.6092</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3592</v>
+        <v>1.3022</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4395</v>
+        <v>1.307</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3592</v>
+        <v>1.3022</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4302</v>
+        <v>1.3727</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4395</v>
+        <v>1.307</v>
       </c>
       <c r="K10" t="n">
         <v>144</v>
@@ -897,7 +897,7 @@
         <v>87</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8697</v>
+        <v>2.6797</v>
       </c>
       <c r="N10" t="n">
         <v>231</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.611</v>
+        <v>2.5398</v>
       </c>
       <c r="C11" t="n">
-        <v>0.569</v>
+        <v>0.5534</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5644</v>
+        <v>0.5512</v>
       </c>
       <c r="E11" t="n">
-        <v>2.611</v>
+        <v>2.5398</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8658</v>
+        <v>2.6761</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7452</v>
+        <v>-0.1363</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8658</v>
+        <v>3.6047</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0075</v>
+        <v>2.0239</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7452</v>
+        <v>-0.1363</v>
       </c>
       <c r="K11" t="n">
         <v>126</v>
@@ -943,7 +943,7 @@
         <v>136</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7527</v>
+        <v>1.8876</v>
       </c>
       <c r="N11" t="n">
         <v>262</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5376</v>
+        <v>2.5225</v>
       </c>
       <c r="C12" t="n">
-        <v>0.553</v>
+        <v>0.5497</v>
       </c>
       <c r="D12" t="n">
-        <v>0.531</v>
+        <v>0.5433</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5376</v>
+        <v>2.5225</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9928</v>
+        <v>1.8079</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5448</v>
+        <v>0.7146</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9928</v>
+        <v>1.8079</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0446</v>
+        <v>1.0151</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5448</v>
+        <v>0.7146</v>
       </c>
       <c r="K12" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="L12" t="n">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5894</v>
+        <v>1.7297</v>
       </c>
       <c r="N12" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4245</v>
+        <v>2.4032</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5283</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4795</v>
+        <v>0.489</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4245</v>
+        <v>2.4032</v>
       </c>
       <c r="F13" t="n">
-        <v>2.635</v>
+        <v>0.9715</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2105</v>
+        <v>1.4318</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7997</v>
+        <v>0.9715</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0518</v>
+        <v>1.0241</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2105</v>
+        <v>1.4318</v>
       </c>
       <c r="K13" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="L13" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8413</v>
+        <v>2.4559</v>
       </c>
       <c r="N13" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3188</v>
+        <v>2.2491</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5053</v>
+        <v>0.4901</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4314</v>
+        <v>0.4188</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3188</v>
+        <v>2.2491</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4304</v>
+        <v>2.1292</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8884</v>
+        <v>0.1199</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4304</v>
+        <v>2.1292</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5051</v>
+        <v>2.2445</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8884</v>
+        <v>0.1199</v>
       </c>
       <c r="K14" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L14" t="n">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.3935</v>
+        <v>2.3644</v>
       </c>
       <c r="N14" t="n">
-        <v>281</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2549</v>
+        <v>2.2418</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4914</v>
+        <v>0.4885</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4023</v>
+        <v>0.4155</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2549</v>
+        <v>2.2418</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1308</v>
+        <v>3.0606</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8759</v>
+        <v>-0.8188</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4355</v>
+        <v>5.0484</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9351</v>
+        <v>2.8345</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8759</v>
+        <v>-0.8188</v>
       </c>
       <c r="K15" t="n">
         <v>126</v>
@@ -1127,7 +1127,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="n">
-        <v>2.0592</v>
+        <v>2.0157</v>
       </c>
       <c r="N15" t="n">
         <v>262</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2219</v>
+        <v>2.1712</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4842</v>
+        <v>0.4731</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3873</v>
+        <v>0.3833</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2219</v>
+        <v>2.1712</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0696</v>
+        <v>1.3782</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1523</v>
+        <v>0.793</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0696</v>
+        <v>1.3782</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1776</v>
+        <v>1.4529</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1523</v>
+        <v>0.793</v>
       </c>
       <c r="K16" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3299</v>
+        <v>2.2459</v>
       </c>
       <c r="N16" t="n">
-        <v>173</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0475</v>
+        <v>1.9863</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4462</v>
+        <v>0.4328</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3079</v>
+        <v>0.2991</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0475</v>
+        <v>1.9863</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7085</v>
+        <v>1.6507</v>
       </c>
       <c r="G17" t="n">
-        <v>0.339</v>
+        <v>0.3357</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7085</v>
+        <v>1.6507</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7977</v>
+        <v>1.7401</v>
       </c>
       <c r="J17" t="n">
-        <v>0.339</v>
+        <v>0.3357</v>
       </c>
       <c r="K17" t="n">
         <v>144</v>
@@ -1219,7 +1219,7 @@
         <v>87</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1367</v>
+        <v>2.0758</v>
       </c>
       <c r="N17" t="n">
         <v>231</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8885</v>
+        <v>1.8239</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4115</v>
+        <v>0.3974</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2355</v>
+        <v>0.2251</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8885</v>
+        <v>1.8239</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4072</v>
+        <v>1.3952</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4813</v>
+        <v>0.4286</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4072</v>
+        <v>1.3952</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4807</v>
+        <v>1.4708</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4813</v>
+        <v>0.4286</v>
       </c>
       <c r="K18" t="n">
         <v>118</v>
@@ -1265,7 +1265,7 @@
         <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>1.962</v>
+        <v>1.8994</v>
       </c>
       <c r="N18" t="n">
         <v>173</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7274</v>
+        <v>1.5577</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3764</v>
+        <v>0.3394</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1621</v>
+        <v>0.1038</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7274</v>
+        <v>1.5577</v>
       </c>
       <c r="F19" t="n">
-        <v>0.828</v>
+        <v>0.7341</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8994</v>
+        <v>0.8236</v>
       </c>
       <c r="H19" t="n">
-        <v>0.828</v>
+        <v>0.7341</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4471</v>
+        <v>0.4122</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8994</v>
+        <v>0.8236</v>
       </c>
       <c r="K19" t="n">
         <v>126</v>
@@ -1311,7 +1311,7 @@
         <v>136</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3465</v>
+        <v>1.2358</v>
       </c>
       <c r="N19" t="n">
         <v>262</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Freeman</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3961</v>
+        <v>1.367</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3042</v>
+        <v>0.2979</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0113</v>
+        <v>0.0169</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3961</v>
+        <v>1.367</v>
       </c>
       <c r="F20" t="n">
-        <v>1.153</v>
+        <v>1.2411</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2431</v>
+        <v>0.1259</v>
       </c>
       <c r="H20" t="n">
-        <v>1.153</v>
+        <v>1.2411</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6226</v>
+        <v>1.3084</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2431</v>
+        <v>0.1259</v>
       </c>
       <c r="K20" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8657</v>
+        <v>1.4343</v>
       </c>
       <c r="N20" t="n">
-        <v>200</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3517</v>
+        <v>1.2285</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2945</v>
+        <v>0.2677</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0089</v>
+        <v>-0.0461</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3517</v>
+        <v>1.2285</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3517</v>
+        <v>1.2285</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3517</v>
+        <v>1.2285</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3865</v>
+        <v>1.2613</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.3865</v>
+        <v>1.2613</v>
       </c>
       <c r="N21" t="n">
         <v>138</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Freeman</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2912</v>
+        <v>1.2276</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2814</v>
+        <v>0.2675</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0364</v>
+        <v>-0.0466</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2912</v>
+        <v>1.2276</v>
       </c>
       <c r="F22" t="n">
-        <v>1.257</v>
+        <v>0.9878</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0342</v>
+        <v>0.2398</v>
       </c>
       <c r="H22" t="n">
-        <v>1.257</v>
+        <v>0.9878</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3226</v>
+        <v>0.5546</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0342</v>
+        <v>0.2398</v>
       </c>
       <c r="K22" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L22" t="n">
-        <v>170</v>
+        <v>88</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3568</v>
+        <v>0.7944</v>
       </c>
       <c r="N22" t="n">
-        <v>281</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0365</v>
+        <v>0.9603</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2259</v>
+        <v>0.2093</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1524</v>
+        <v>-0.1683</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0365</v>
+        <v>0.9603</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4628</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4977</v>
+        <v>0.4975</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.4628</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5669</v>
+        <v>0.4878</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4977</v>
+        <v>0.4975</v>
       </c>
       <c r="K23" t="n">
         <v>111</v>
@@ -1495,7 +1495,7 @@
         <v>170</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0646</v>
+        <v>0.9853000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>281</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6903</v>
+        <v>0.7483</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1504</v>
+        <v>0.1631</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.31</v>
+        <v>-0.2649</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6903</v>
+        <v>0.7483</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1853</v>
+        <v>1.2182</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.495</v>
+        <v>-0.4699</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1853</v>
+        <v>1.2182</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2472</v>
+        <v>1.2842</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.495</v>
+        <v>-0.4699</v>
       </c>
       <c r="K24" t="n">
         <v>118</v>
@@ -1541,7 +1541,7 @@
         <v>55</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7522000000000001</v>
+        <v>0.8143</v>
       </c>
       <c r="N24" t="n">
         <v>173</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.65</v>
+        <v>0.5715</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1416</v>
+        <v>0.1245</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3283</v>
+        <v>-0.3454</v>
       </c>
       <c r="E25" t="n">
-        <v>0.65</v>
+        <v>0.5715</v>
       </c>
       <c r="F25" t="n">
-        <v>0.65</v>
+        <v>0.5715</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.65</v>
+        <v>0.5715</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.5868</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.5868</v>
       </c>
       <c r="N25" t="n">
         <v>119</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.443</v>
+        <v>0.3344</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0965</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4225</v>
+        <v>-0.4535</v>
       </c>
       <c r="E26" t="n">
-        <v>0.443</v>
+        <v>0.3344</v>
       </c>
       <c r="F26" t="n">
-        <v>0.443</v>
+        <v>0.3344</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.443</v>
+        <v>0.3344</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4544</v>
+        <v>0.3433</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4544</v>
+        <v>0.3433</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.254</v>
+        <v>0.1892</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0553</v>
+        <v>0.0412</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5196</v>
       </c>
       <c r="E27" t="n">
-        <v>0.254</v>
+        <v>0.1892</v>
       </c>
       <c r="F27" t="n">
-        <v>0.254</v>
+        <v>0.1892</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.254</v>
+        <v>0.1892</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2605</v>
+        <v>0.1942</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2605</v>
+        <v>0.1942</v>
       </c>
       <c r="N27" t="n">
         <v>119</v>
@@ -1688,231 +1688,231 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0373</v>
       </c>
       <c r="C28" t="n">
-        <v>0.014</v>
+        <v>0.0081</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.595</v>
+        <v>-0.5888</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0373</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.0851</v>
+        <v>0.5144</v>
       </c>
       <c r="G28" t="n">
-        <v>1.1493</v>
+        <v>-0.4771</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.0851</v>
+        <v>0.5144</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.1712</v>
+        <v>0.5423</v>
       </c>
       <c r="J28" t="n">
-        <v>1.1493</v>
+        <v>-0.4771</v>
       </c>
       <c r="K28" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="L28" t="n">
-        <v>196</v>
+        <v>55</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02190000000000003</v>
+        <v>0.06519999999999998</v>
       </c>
       <c r="N28" t="n">
-        <v>328</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0453</v>
+        <v>0.0064</v>
       </c>
       <c r="C29" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0014</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6036</v>
+        <v>-0.6029</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0453</v>
+        <v>0.0064</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5611</v>
+        <v>-1.0459</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5158</v>
+        <v>1.0523</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5611</v>
+        <v>-1.0459</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5904</v>
+        <v>-1.132</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5158</v>
+        <v>1.0523</v>
       </c>
       <c r="K29" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="L29" t="n">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0746</v>
+        <v>-0.07969999999999988</v>
       </c>
       <c r="N29" t="n">
-        <v>173</v>
+        <v>328</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0421</v>
+        <v>-0.0211</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0092</v>
+        <v>-0.0046</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.605</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0421</v>
+        <v>-0.0211</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0421</v>
+        <v>0.2864</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.3075</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0421</v>
+        <v>0.2864</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0432</v>
+        <v>0.3019</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.3075</v>
       </c>
       <c r="K30" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0432</v>
+        <v>-0.005599999999999994</v>
       </c>
       <c r="N30" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0897</v>
+        <v>-0.0994</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0195</v>
+        <v>-0.0217</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.665</v>
+        <v>-0.6511</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0897</v>
+        <v>-0.0994</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2057</v>
+        <v>0.3843</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2954</v>
+        <v>-0.4837</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2057</v>
+        <v>0.3843</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2164</v>
+        <v>0.4051</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2954</v>
+        <v>-0.4837</v>
       </c>
       <c r="K31" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L31" t="n">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.07899999999999999</v>
+        <v>-0.0786</v>
       </c>
       <c r="N31" t="n">
-        <v>173</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1275</v>
+        <v>-0.1471</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0278</v>
+        <v>-0.0321</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6822</v>
+        <v>-0.6728</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1275</v>
+        <v>-0.1471</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4001</v>
+        <v>-0.1471</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5276</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4001</v>
+        <v>-0.1471</v>
       </c>
       <c r="I32" t="n">
-        <v>0.421</v>
+        <v>-0.151</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5276</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="L32" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1066</v>
+        <v>-0.151</v>
       </c>
       <c r="N32" t="n">
-        <v>281</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1977</v>
+        <v>-0.1997</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0431</v>
+        <v>-0.0435</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6968</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1977</v>
+        <v>-0.1997</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1977</v>
+        <v>-0.1997</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1977</v>
+        <v>-0.1997</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2028</v>
+        <v>-0.205</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.2028</v>
+        <v>-0.205</v>
       </c>
       <c r="N33" t="n">
         <v>119</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.24</v>
+        <v>-0.2504</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0523</v>
+        <v>-0.0546</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7335</v>
+        <v>-0.7199</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.24</v>
+        <v>-0.2504</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.24</v>
+        <v>-0.2504</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.24</v>
+        <v>-0.2504</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2525</v>
+        <v>-0.264</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2525</v>
+        <v>-0.264</v>
       </c>
       <c r="N34" t="n">
         <v>144</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3292</v>
+        <v>-0.3955</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0717</v>
+        <v>-0.0862</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7741</v>
+        <v>-0.786</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3292</v>
+        <v>-0.3955</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3292</v>
+        <v>-0.3955</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3292</v>
+        <v>-0.3955</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3377</v>
+        <v>-0.4061</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3377</v>
+        <v>-0.4061</v>
       </c>
       <c r="N35" t="n">
         <v>119</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>SANJI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5347</v>
+        <v>-0.4989</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1165</v>
+        <v>-0.1087</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8676</v>
+        <v>-0.8331</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5347</v>
+        <v>-0.4989</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5347</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
+        <v>-0.4989</v>
+      </c>
+      <c r="H36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="n">
-        <v>-0.5347</v>
-      </c>
       <c r="I36" t="n">
-        <v>-0.5485</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
+        <v>-0.4989</v>
+      </c>
+      <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="K36" t="n">
-        <v>119</v>
-      </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5485</v>
+        <v>-0.4989</v>
       </c>
       <c r="N36" t="n">
-        <v>119</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SANJI</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.5594</v>
+        <v>-0.5511</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1219</v>
+        <v>-0.1201</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8789</v>
+        <v>-0.8568</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5594</v>
+        <v>-0.5511</v>
       </c>
       <c r="F37" t="n">
+        <v>-0.5511</v>
+      </c>
+      <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="n">
-        <v>-0.5594</v>
-      </c>
       <c r="H37" t="n">
+        <v>-0.5511</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.5658</v>
+      </c>
+      <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
+        <v>119</v>
+      </c>
+      <c r="L37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" t="n">
-        <v>-0.5594</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>87</v>
-      </c>
       <c r="M37" t="n">
-        <v>-0.5594</v>
+        <v>-0.5658</v>
       </c>
       <c r="N37" t="n">
-        <v>87</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.5877</v>
+        <v>-0.6427</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1281</v>
+        <v>-0.14</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8917</v>
+        <v>-0.8986</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.5877</v>
+        <v>-0.6427</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.1718</v>
+        <v>-0.1712</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4159</v>
+        <v>-0.4715</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1718</v>
+        <v>-0.1712</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1854</v>
+        <v>-0.1853</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4159</v>
+        <v>-0.4715</v>
       </c>
       <c r="K38" t="n">
         <v>132</v>
@@ -2185,7 +2185,7 @@
         <v>196</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.6567999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>328</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1049</v>
+        <v>-1.0134</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2408</v>
+        <v>-0.2208</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1272</v>
+        <v>-1.0674</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1049</v>
+        <v>-1.0134</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1049</v>
+        <v>-1.0134</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1049</v>
+        <v>-1.0134</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1334</v>
+        <v>-1.0405</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1334</v>
+        <v>-1.0405</v>
       </c>
       <c r="N39" t="n">
         <v>138</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1606</v>
+        <v>-1.1334</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2529</v>
+        <v>-0.247</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1525</v>
+        <v>-1.1221</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1606</v>
+        <v>-1.1334</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.494</v>
+        <v>-0.4845</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6666</v>
+        <v>-0.6489</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.494</v>
+        <v>-0.4845</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5198</v>
+        <v>-0.5107</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6666</v>
+        <v>-0.6489</v>
       </c>
       <c r="K40" t="n">
         <v>144</v>
@@ -2277,7 +2277,7 @@
         <v>87</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.1864</v>
+        <v>-1.1596</v>
       </c>
       <c r="N40" t="n">
         <v>231</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7797</v>
+        <v>-1.7661</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3878</v>
+        <v>-0.3848</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4344</v>
+        <v>-1.4103</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7797</v>
+        <v>-1.7661</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7797</v>
+        <v>-1.7661</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7797</v>
+        <v>-1.7661</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8256</v>
+        <v>-1.8133</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8256</v>
+        <v>-1.8133</v>
       </c>
       <c r="N41" t="n">
         <v>138</v>
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.5012</v>
+        <v>-2.3003</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.545</v>
+        <v>-0.5013</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.7628</v>
+        <v>-1.6537</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.5012</v>
+        <v>-2.3003</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.2037</v>
+        <v>-2.0031</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.2975</v>
+        <v>-0.2972</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.2037</v>
+        <v>-2.0031</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.19</v>
+        <v>-1.1247</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.2975</v>
+        <v>-0.2972</v>
       </c>
       <c r="K42" t="n">
         <v>112</v>
@@ -2369,7 +2369,7 @@
         <v>88</v>
       </c>
       <c r="M42" t="n">
-        <v>-1.4875</v>
+        <v>-1.4219</v>
       </c>
       <c r="N42" t="n">
         <v>200</v>
@@ -2475,10 +2475,10 @@
         <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4414</v>
+        <v>0.3884</v>
       </c>
       <c r="J2" t="n">
-        <v>11.4764</v>
+        <v>10.0984</v>
       </c>
     </row>
     <row r="3">
@@ -2515,10 +2515,10 @@
         <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1991</v>
+        <v>-0.1806</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.1766</v>
+        <v>-4.6956</v>
       </c>
     </row>
     <row r="4">
@@ -2555,10 +2555,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2289</v>
+        <v>-0.2099</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.9514</v>
+        <v>-5.4574</v>
       </c>
     </row>
     <row r="5">
@@ -2595,10 +2595,10 @@
         <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2485</v>
+        <v>-0.2295</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.461</v>
+        <v>-5.967</v>
       </c>
     </row>
     <row r="6">
@@ -2635,10 +2635,10 @@
         <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3702</v>
+        <v>-0.3564</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.6252</v>
+        <v>-9.266400000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2675,10 +2675,10 @@
         <v>1.38</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9044</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>23.5144</v>
+        <v>23.1036</v>
       </c>
     </row>
     <row r="8">
@@ -2715,10 +2715,10 @@
         <v>1.35</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8462</v>
+        <v>0.826</v>
       </c>
       <c r="J8" t="n">
-        <v>22.0012</v>
+        <v>21.476</v>
       </c>
     </row>
     <row r="9">
@@ -2755,10 +2755,10 @@
         <v>1.17</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4752</v>
+        <v>0.442</v>
       </c>
       <c r="J9" t="n">
-        <v>12.3552</v>
+        <v>11.492</v>
       </c>
     </row>
     <row r="10">
@@ -2795,10 +2795,10 @@
         <v>1.16</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4522</v>
+        <v>0.4189</v>
       </c>
       <c r="J10" t="n">
-        <v>11.7572</v>
+        <v>10.8914</v>
       </c>
     </row>
     <row r="11">
@@ -2835,10 +2835,10 @@
         <v>1.1</v>
       </c>
       <c r="I11" t="n">
-        <v>0.305</v>
+        <v>0.2729</v>
       </c>
       <c r="J11" t="n">
-        <v>7.93</v>
+        <v>7.0954</v>
       </c>
     </row>
     <row r="12">
@@ -2875,10 +2875,10 @@
         <v>1.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7059</v>
+        <v>0.6582</v>
       </c>
       <c r="J12" t="n">
-        <v>19.0593</v>
+        <v>17.7714</v>
       </c>
     </row>
     <row r="13">
@@ -2915,10 +2915,10 @@
         <v>0.89</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1488</v>
+        <v>-0.1315</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.0176</v>
+        <v>-3.5505</v>
       </c>
     </row>
     <row r="14">
@@ -2955,10 +2955,10 @@
         <v>0.78</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.26</v>
+        <v>-0.2408</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.02</v>
+        <v>-6.5016</v>
       </c>
     </row>
     <row r="15">
@@ -2995,10 +2995,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2887</v>
+        <v>-0.2704</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.7949</v>
+        <v>-7.3008</v>
       </c>
     </row>
     <row r="16">
@@ -3035,10 +3035,10 @@
         <v>0.61</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4169</v>
+        <v>-0.4072</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.2563</v>
+        <v>-10.9944</v>
       </c>
     </row>
     <row r="17">
@@ -3075,10 +3075,10 @@
         <v>1.36</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8786</v>
+        <v>0.8592</v>
       </c>
       <c r="J17" t="n">
-        <v>23.7222</v>
+        <v>23.1984</v>
       </c>
     </row>
     <row r="18">
@@ -3115,10 +3115,10 @@
         <v>1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7988</v>
+        <v>0.7735</v>
       </c>
       <c r="J18" t="n">
-        <v>21.5676</v>
+        <v>20.8845</v>
       </c>
     </row>
     <row r="19">
@@ -3155,10 +3155,10 @@
         <v>1.18</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5043</v>
+        <v>0.4684</v>
       </c>
       <c r="J19" t="n">
-        <v>13.6161</v>
+        <v>12.6468</v>
       </c>
     </row>
     <row r="20">
@@ -3195,10 +3195,10 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0308</v>
+        <v>0.0209</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8316</v>
+        <v>0.5643</v>
       </c>
     </row>
     <row r="21">
@@ -3235,10 +3235,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.029</v>
+        <v>-0.0234</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.783</v>
+        <v>-0.6318</v>
       </c>
     </row>
     <row r="22">
@@ -3275,10 +3275,10 @@
         <v>1.59</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6212</v>
+        <v>0.583</v>
       </c>
       <c r="J22" t="n">
-        <v>13.6664</v>
+        <v>12.826</v>
       </c>
     </row>
     <row r="23">
@@ -3315,10 +3315,10 @@
         <v>1.56</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6002</v>
+        <v>0.5642</v>
       </c>
       <c r="J23" t="n">
-        <v>13.2044</v>
+        <v>12.4124</v>
       </c>
     </row>
     <row r="24">
@@ -3355,10 +3355,10 @@
         <v>1.47</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5361</v>
+        <v>0.501</v>
       </c>
       <c r="J24" t="n">
-        <v>11.7942</v>
+        <v>11.022</v>
       </c>
     </row>
     <row r="25">
@@ -3395,10 +3395,10 @@
         <v>1.34</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4377</v>
+        <v>0.3811</v>
       </c>
       <c r="J25" t="n">
-        <v>9.6294</v>
+        <v>8.3842</v>
       </c>
     </row>
     <row r="26">
@@ -3435,10 +3435,10 @@
         <v>1.12</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1795</v>
+        <v>0.1422</v>
       </c>
       <c r="J26" t="n">
-        <v>3.949</v>
+        <v>3.1284</v>
       </c>
     </row>
     <row r="27">
@@ -3475,10 +3475,10 @@
         <v>1.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3377</v>
+        <v>0.3421</v>
       </c>
       <c r="J27" t="n">
-        <v>7.4294</v>
+        <v>7.5262</v>
       </c>
     </row>
     <row r="28">
@@ -3515,10 +3515,10 @@
         <v>0.8</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2297</v>
+        <v>-0.2139</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.0534</v>
+        <v>-4.7058</v>
       </c>
     </row>
     <row r="29">
@@ -3555,10 +3555,10 @@
         <v>0.7</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3221</v>
+        <v>-0.3068</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.0862</v>
+        <v>-6.7496</v>
       </c>
     </row>
     <row r="30">
@@ -3595,10 +3595,10 @@
         <v>0.64</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3763</v>
+        <v>-0.3633</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.278600000000001</v>
+        <v>-7.9926</v>
       </c>
     </row>
     <row r="31">
@@ -3635,10 +3635,10 @@
         <v>0.46</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5381</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.7656</v>
+        <v>-11.8382</v>
       </c>
     </row>
     <row r="32">
@@ -3675,10 +3675,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5599</v>
+        <v>0.5343</v>
       </c>
       <c r="J32" t="n">
-        <v>20.1564</v>
+        <v>19.2348</v>
       </c>
     </row>
     <row r="33">
@@ -3715,10 +3715,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2156</v>
+        <v>0.1725</v>
       </c>
       <c r="J33" t="n">
-        <v>7.7616</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="34">
@@ -3755,10 +3755,10 @@
         <v>1.03</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1024</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6864</v>
+        <v>2.7144</v>
       </c>
     </row>
     <row r="35">
@@ -3795,10 +3795,10 @@
         <v>0.76</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2898</v>
+        <v>-0.2713</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.4328</v>
+        <v>-9.7668</v>
       </c>
     </row>
     <row r="36">
@@ -3835,10 +3835,10 @@
         <v>0.74</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3088</v>
+        <v>-0.2913</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.1168</v>
+        <v>-10.4868</v>
       </c>
     </row>
     <row r="37">
@@ -3875,10 +3875,10 @@
         <v>1.47</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9382</v>
+        <v>0.9248</v>
       </c>
       <c r="J37" t="n">
-        <v>33.7752</v>
+        <v>33.2928</v>
       </c>
     </row>
     <row r="38">
@@ -3915,10 +3915,10 @@
         <v>1.12</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3733</v>
+        <v>0.3349</v>
       </c>
       <c r="J38" t="n">
-        <v>13.4388</v>
+        <v>12.0564</v>
       </c>
     </row>
     <row r="39">
@@ -3955,10 +3955,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3488</v>
+        <v>0.311</v>
       </c>
       <c r="J39" t="n">
-        <v>12.5568</v>
+        <v>11.196</v>
       </c>
     </row>
     <row r="40">
@@ -3995,10 +3995,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1857</v>
+        <v>0.1571</v>
       </c>
       <c r="J40" t="n">
-        <v>6.6852</v>
+        <v>5.6556</v>
       </c>
     </row>
     <row r="41">
@@ -4035,10 +4035,10 @@
         <v>0.77</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6764</v>
+        <v>-0.6435</v>
       </c>
       <c r="J41" t="n">
-        <v>-24.3504</v>
+        <v>-23.166</v>
       </c>
     </row>
     <row r="42">
@@ -4075,10 +4075,10 @@
         <v>1.52</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7343</v>
       </c>
       <c r="J42" t="n">
-        <v>23.151</v>
+        <v>22.029</v>
       </c>
     </row>
     <row r="43">
@@ -4115,10 +4115,10 @@
         <v>1.14</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3098</v>
+        <v>0.2615</v>
       </c>
       <c r="J43" t="n">
-        <v>9.294</v>
+        <v>7.845</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4155,10 @@
         <v>1.07</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1787</v>
+        <v>0.1441</v>
       </c>
       <c r="J44" t="n">
-        <v>5.361</v>
+        <v>4.323</v>
       </c>
     </row>
     <row r="45">
@@ -4195,10 +4195,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0673</v>
+        <v>-0.0531</v>
       </c>
       <c r="J45" t="n">
-        <v>-2.019</v>
+        <v>-1.593</v>
       </c>
     </row>
     <row r="46">
@@ -4235,10 +4235,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1682</v>
+        <v>-0.1481</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.046</v>
+        <v>-4.443</v>
       </c>
     </row>
     <row r="47">
@@ -4275,10 +4275,10 @@
         <v>1.57</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1271</v>
+        <v>1.1328</v>
       </c>
       <c r="J47" t="n">
-        <v>33.813</v>
+        <v>33.984</v>
       </c>
     </row>
     <row r="48">
@@ -4315,10 +4315,10 @@
         <v>0.95</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1953</v>
+        <v>-0.1626</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.859</v>
+        <v>-4.878</v>
       </c>
     </row>
     <row r="49">
@@ -4355,10 +4355,10 @@
         <v>0.89</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3622</v>
+        <v>-0.3205</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.866</v>
+        <v>-9.615</v>
       </c>
     </row>
     <row r="50">
@@ -4395,10 +4395,10 @@
         <v>0.73</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7379</v>
+        <v>-0.7071</v>
       </c>
       <c r="J50" t="n">
-        <v>-22.137</v>
+        <v>-21.213</v>
       </c>
     </row>
     <row r="51">
@@ -4435,10 +4435,10 @@
         <v>0.71</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.7813</v>
+        <v>-0.7539</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.439</v>
+        <v>-22.617</v>
       </c>
     </row>
     <row r="52">
@@ -4475,10 +4475,10 @@
         <v>1.17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3012</v>
+        <v>0.2891</v>
       </c>
       <c r="J52" t="n">
-        <v>9.036</v>
+        <v>8.673</v>
       </c>
     </row>
     <row r="53">
@@ -4515,10 +4515,10 @@
         <v>1.16</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2872</v>
+        <v>0.2742</v>
       </c>
       <c r="J53" t="n">
-        <v>8.616</v>
+        <v>8.226000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4555,10 +4555,10 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1682</v>
+        <v>-0.1481</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.046</v>
+        <v>-4.443</v>
       </c>
     </row>
     <row r="55">
@@ -4595,10 +4595,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1682</v>
+        <v>-0.1481</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.046</v>
+        <v>-4.443</v>
       </c>
     </row>
     <row r="56">
@@ -4635,10 +4635,10 @@
         <v>0.85</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2004</v>
+        <v>-0.1798</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.012</v>
+        <v>-5.394</v>
       </c>
     </row>
     <row r="57">
@@ -4675,10 +4675,10 @@
         <v>1.55</v>
       </c>
       <c r="I57" t="n">
-        <v>0.64</v>
+        <v>0.6021</v>
       </c>
       <c r="J57" t="n">
-        <v>19.2</v>
+        <v>18.063</v>
       </c>
     </row>
     <row r="58">
@@ -4715,10 +4715,10 @@
         <v>0.97</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0608</v>
+        <v>-0.0475</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.824</v>
+        <v>-1.425</v>
       </c>
     </row>
     <row r="59">
@@ -4755,10 +4755,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1266</v>
+        <v>-0.1077</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.798</v>
+        <v>-3.231</v>
       </c>
     </row>
     <row r="60">
@@ -4795,10 +4795,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1614</v>
+        <v>-0.1411</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.842</v>
+        <v>-4.233</v>
       </c>
     </row>
     <row r="61">
@@ -4835,10 +4835,10 @@
         <v>0.85</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2047</v>
+        <v>-0.184</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.141</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="62">
@@ -4875,10 +4875,10 @@
         <v>1.34</v>
       </c>
       <c r="I62" t="n">
-        <v>0.751</v>
+        <v>0.735</v>
       </c>
       <c r="J62" t="n">
-        <v>20.277</v>
+        <v>19.845</v>
       </c>
     </row>
     <row r="63">
@@ -4915,10 +4915,10 @@
         <v>1.25</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6116</v>
+        <v>0.5986</v>
       </c>
       <c r="J63" t="n">
-        <v>16.5132</v>
+        <v>16.1622</v>
       </c>
     </row>
     <row r="64">
@@ -4955,10 +4955,10 @@
         <v>1.04</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1562</v>
+        <v>0.1299</v>
       </c>
       <c r="J64" t="n">
-        <v>4.2174</v>
+        <v>3.5073</v>
       </c>
     </row>
     <row r="65">
@@ -4995,10 +4995,10 @@
         <v>0.98</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1153</v>
+        <v>-0.0887</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.1131</v>
+        <v>-2.3949</v>
       </c>
     </row>
     <row r="66">
@@ -5035,10 +5035,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4875</v>
+        <v>-0.4456</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.1625</v>
+        <v>-12.0312</v>
       </c>
     </row>
     <row r="67">
@@ -5075,10 +5075,10 @@
         <v>1.32</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5653</v>
+        <v>0.5386</v>
       </c>
       <c r="J67" t="n">
-        <v>15.2631</v>
+        <v>14.5422</v>
       </c>
     </row>
     <row r="68">
@@ -5115,10 +5115,10 @@
         <v>1.18</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3852</v>
+        <v>0.3303</v>
       </c>
       <c r="J68" t="n">
-        <v>10.4004</v>
+        <v>8.918100000000001</v>
       </c>
     </row>
     <row r="69">
@@ -5155,10 +5155,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0664</v>
+        <v>0.0488</v>
       </c>
       <c r="J69" t="n">
-        <v>1.7928</v>
+        <v>1.3176</v>
       </c>
     </row>
     <row r="70">
@@ -5195,10 +5195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1049</v>
+        <v>-0.0872</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.8323</v>
+        <v>-2.3544</v>
       </c>
     </row>
     <row r="71">
@@ -5235,10 +5235,10 @@
         <v>0.9</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1531</v>
+        <v>-0.1331</v>
       </c>
       <c r="J71" t="n">
-        <v>-4.1337</v>
+        <v>-3.5937</v>
       </c>
     </row>
     <row r="72">
@@ -5275,10 +5275,10 @@
         <v>1.22</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5619</v>
+        <v>0.5512</v>
       </c>
       <c r="J72" t="n">
-        <v>14.6094</v>
+        <v>14.3312</v>
       </c>
     </row>
     <row r="73">
@@ -5315,10 +5315,10 @@
         <v>1.14</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4212</v>
+        <v>0.3827</v>
       </c>
       <c r="J73" t="n">
-        <v>10.9512</v>
+        <v>9.950200000000001</v>
       </c>
     </row>
     <row r="74">
@@ -5355,10 +5355,10 @@
         <v>1.1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3243</v>
+        <v>0.2872</v>
       </c>
       <c r="J74" t="n">
-        <v>8.431800000000001</v>
+        <v>7.4672</v>
       </c>
     </row>
     <row r="75">
@@ -5395,10 +5395,10 @@
         <v>1.09</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2988</v>
+        <v>0.2628</v>
       </c>
       <c r="J75" t="n">
-        <v>7.7688</v>
+        <v>6.8328</v>
       </c>
     </row>
     <row r="76">
@@ -5435,10 +5435,10 @@
         <v>0.95</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.219</v>
+        <v>-0.182</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.694</v>
+        <v>-4.732</v>
       </c>
     </row>
     <row r="77">
@@ -5475,10 +5475,10 @@
         <v>1.08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2273</v>
+        <v>0.1829</v>
       </c>
       <c r="J77" t="n">
-        <v>5.9098</v>
+        <v>4.7554</v>
       </c>
     </row>
     <row r="78">
@@ -5515,10 +5515,10 @@
         <v>1.01</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0542</v>
+        <v>0.0367</v>
       </c>
       <c r="J78" t="n">
-        <v>1.4092</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="79">
@@ -5555,10 +5555,10 @@
         <v>1.01</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0542</v>
+        <v>0.0367</v>
       </c>
       <c r="J79" t="n">
-        <v>1.4092</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="80">
@@ -5595,10 +5595,10 @@
         <v>0.86</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1843</v>
+        <v>-0.1645</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.7918</v>
+        <v>-4.277</v>
       </c>
     </row>
     <row r="81">
@@ -5635,10 +5635,10 @@
         <v>0.67</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3682</v>
+        <v>-0.3545</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.5732</v>
+        <v>-9.217000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5675,10 +5675,10 @@
         <v>1.08</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2317</v>
+        <v>0.1871</v>
       </c>
       <c r="J82" t="n">
-        <v>6.0242</v>
+        <v>4.8646</v>
       </c>
     </row>
     <row r="83">
@@ -5715,10 +5715,10 @@
         <v>1.02</v>
       </c>
       <c r="I83" t="n">
-        <v>0.0886</v>
+        <v>0.0639</v>
       </c>
       <c r="J83" t="n">
-        <v>2.3036</v>
+        <v>1.6614</v>
       </c>
     </row>
     <row r="84">
@@ -5755,10 +5755,10 @@
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0133</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J84" t="n">
-        <v>0.3458</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="85">
@@ -5795,10 +5795,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2338</v>
+        <v>-0.2139</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.0788</v>
+        <v>-5.5614</v>
       </c>
     </row>
     <row r="86">
@@ -5835,10 +5835,10 @@
         <v>0.63</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4025</v>
+        <v>-0.3917</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.465</v>
+        <v>-10.1842</v>
       </c>
     </row>
     <row r="87">
@@ -5875,10 +5875,10 @@
         <v>1.61</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0838</v>
+        <v>1.0743</v>
       </c>
       <c r="J87" t="n">
-        <v>28.1788</v>
+        <v>27.9318</v>
       </c>
     </row>
     <row r="88">
@@ -5915,10 +5915,10 @@
         <v>1.5</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9384</v>
+        <v>0.925</v>
       </c>
       <c r="J88" t="n">
-        <v>24.3984</v>
+        <v>24.05</v>
       </c>
     </row>
     <row r="89">
@@ -5955,10 +5955,10 @@
         <v>1.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5082</v>
+        <v>0.5004</v>
       </c>
       <c r="J89" t="n">
-        <v>13.2132</v>
+        <v>13.0104</v>
       </c>
     </row>
     <row r="90">
@@ -5995,10 +5995,10 @@
         <v>1.19</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4918</v>
+        <v>0.4795</v>
       </c>
       <c r="J90" t="n">
-        <v>12.7868</v>
+        <v>12.467</v>
       </c>
     </row>
     <row r="91">
@@ -6035,10 +6035,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.11</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.86</v>
+        <v>-2.3478</v>
       </c>
     </row>
     <row r="92">
@@ -6075,10 +6075,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.468</v>
+        <v>0.4226</v>
       </c>
       <c r="J92" t="n">
-        <v>13.572</v>
+        <v>12.2554</v>
       </c>
     </row>
     <row r="93">
@@ -6115,10 +6115,10 @@
         <v>0.95</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0794</v>
+        <v>-0.0664</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.3026</v>
+        <v>-1.9256</v>
       </c>
     </row>
     <row r="94">
@@ -6155,10 +6155,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0925</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.6825</v>
+        <v>-2.2678</v>
       </c>
     </row>
     <row r="95">
@@ -6195,10 +6195,10 @@
         <v>0.76</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.282</v>
+        <v>-0.2632</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.178000000000001</v>
+        <v>-7.6328</v>
       </c>
     </row>
     <row r="96">
@@ -6235,10 +6235,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.384</v>
+        <v>-0.3714</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.136</v>
+        <v>-10.7706</v>
       </c>
     </row>
     <row r="97">
@@ -6275,10 +6275,10 @@
         <v>1.52</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9804</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>28.4316</v>
+        <v>28.0488</v>
       </c>
     </row>
     <row r="98">
@@ -6315,10 +6315,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6085</v>
+        <v>0.5988</v>
       </c>
       <c r="J98" t="n">
-        <v>17.6465</v>
+        <v>17.3652</v>
       </c>
     </row>
     <row r="99">
@@ -6355,10 +6355,10 @@
         <v>1.23</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5627</v>
+        <v>0.5556</v>
       </c>
       <c r="J99" t="n">
-        <v>16.3183</v>
+        <v>16.1124</v>
       </c>
     </row>
     <row r="100">
@@ -6395,10 +6395,10 @@
         <v>1.12</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3583</v>
+        <v>0.325</v>
       </c>
       <c r="J100" t="n">
-        <v>10.3907</v>
+        <v>9.425000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6435,10 +6435,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2085</v>
+        <v>-0.1744</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.0465</v>
+        <v>-5.0576</v>
       </c>
     </row>
     <row r="102">
@@ -6475,10 +6475,10 @@
         <v>1.45</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6071</v>
+        <v>0.6474</v>
       </c>
       <c r="J102" t="n">
-        <v>15.1775</v>
+        <v>16.185</v>
       </c>
     </row>
     <row r="103">
@@ -6515,10 +6515,10 @@
         <v>1.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1928</v>
+        <v>0.1757</v>
       </c>
       <c r="J103" t="n">
-        <v>4.82</v>
+        <v>4.3925</v>
       </c>
     </row>
     <row r="104">
@@ -6555,10 +6555,10 @@
         <v>0.75</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.2947</v>
+        <v>-0.2764</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.3675</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="105">
@@ -6595,10 +6595,10 @@
         <v>0.73</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3136</v>
+        <v>-0.2963</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.84</v>
+        <v>-7.4075</v>
       </c>
     </row>
     <row r="106">
@@ -6635,10 +6635,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3871</v>
+        <v>-0.375</v>
       </c>
       <c r="J106" t="n">
-        <v>-9.6775</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="107">
@@ -6675,10 +6675,10 @@
         <v>1.56</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6306</v>
+        <v>0.5914</v>
       </c>
       <c r="J107" t="n">
-        <v>15.765</v>
+        <v>14.785</v>
       </c>
     </row>
     <row r="108">
@@ -6715,10 +6715,10 @@
         <v>1.14</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2292</v>
+        <v>0.1834</v>
       </c>
       <c r="J108" t="n">
-        <v>5.73</v>
+        <v>4.585</v>
       </c>
     </row>
     <row r="109">
@@ -6755,10 +6755,10 @@
         <v>1.08</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1467</v>
+        <v>0.1131</v>
       </c>
       <c r="J109" t="n">
-        <v>3.6675</v>
+        <v>2.8275</v>
       </c>
     </row>
     <row r="110">
@@ -6795,10 +6795,10 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0094</v>
+        <v>-0.007</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.235</v>
+        <v>-0.175</v>
       </c>
     </row>
     <row r="111">
@@ -6835,10 +6835,10 @@
         <v>0.89</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.1695</v>
+        <v>-0.1494</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.2375</v>
+        <v>-3.735</v>
       </c>
     </row>
     <row r="112">
@@ -6875,10 +6875,10 @@
         <v>1.37</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8045</v>
+        <v>0.789</v>
       </c>
       <c r="J112" t="n">
-        <v>22.526</v>
+        <v>22.092</v>
       </c>
     </row>
     <row r="113">
@@ -6915,10 +6915,10 @@
         <v>1.15</v>
       </c>
       <c r="I113" t="n">
-        <v>0.449</v>
+        <v>0.4128</v>
       </c>
       <c r="J113" t="n">
-        <v>12.572</v>
+        <v>11.5584</v>
       </c>
     </row>
     <row r="114">
@@ -6955,10 +6955,10 @@
         <v>1.03</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1282</v>
+        <v>0.1038</v>
       </c>
       <c r="J114" t="n">
-        <v>3.5896</v>
+        <v>2.9064</v>
       </c>
     </row>
     <row r="115">
@@ -6995,10 +6995,10 @@
         <v>0.91</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3266</v>
+        <v>-0.2846</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.1448</v>
+        <v>-7.9688</v>
       </c>
     </row>
     <row r="116">
@@ -7035,10 +7035,10 @@
         <v>0.83</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.529</v>
+        <v>-0.4879</v>
       </c>
       <c r="J116" t="n">
-        <v>-14.812</v>
+        <v>-13.6612</v>
       </c>
     </row>
     <row r="117">
@@ -7075,10 +7075,10 @@
         <v>1.46</v>
       </c>
       <c r="I117" t="n">
-        <v>0.731</v>
+        <v>0.6973</v>
       </c>
       <c r="J117" t="n">
-        <v>20.468</v>
+        <v>19.5244</v>
       </c>
     </row>
     <row r="118">
@@ -7115,10 +7115,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0421</v>
+        <v>0.0289</v>
       </c>
       <c r="J118" t="n">
-        <v>1.1788</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="119">
@@ -7155,10 +7155,10 @@
         <v>0.91</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1369</v>
+        <v>-0.1176</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.8332</v>
+        <v>-3.2928</v>
       </c>
     </row>
     <row r="120">
@@ -7195,10 +7195,10 @@
         <v>0.88</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1709</v>
+        <v>-0.1505</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.7852</v>
+        <v>-4.214</v>
       </c>
     </row>
     <row r="121">
@@ -7235,10 +7235,10 @@
         <v>0.83</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2238</v>
+        <v>-0.2033</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.2664</v>
+        <v>-5.6924</v>
       </c>
     </row>
     <row r="122">
@@ -7275,10 +7275,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5442</v>
+        <v>0.5337</v>
       </c>
       <c r="J122" t="n">
-        <v>18.5028</v>
+        <v>18.1458</v>
       </c>
     </row>
     <row r="123">
@@ -7315,10 +7315,10 @@
         <v>1.18</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4944</v>
+        <v>0.4746</v>
       </c>
       <c r="J123" t="n">
-        <v>16.8096</v>
+        <v>16.1364</v>
       </c>
     </row>
     <row r="124">
@@ -7355,10 +7355,10 @@
         <v>1.12</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3729</v>
+        <v>0.3347</v>
       </c>
       <c r="J124" t="n">
-        <v>12.6786</v>
+        <v>11.3798</v>
       </c>
     </row>
     <row r="125">
@@ -7395,10 +7395,10 @@
         <v>1.05</v>
       </c>
       <c r="I125" t="n">
-        <v>0.185</v>
+        <v>0.1566</v>
       </c>
       <c r="J125" t="n">
-        <v>6.29</v>
+        <v>5.3244</v>
       </c>
     </row>
     <row r="126">
@@ -7435,10 +7435,10 @@
         <v>0.98</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1182</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.0188</v>
+        <v>-3.1042</v>
       </c>
     </row>
     <row r="127">
@@ -7475,10 +7475,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5521</v>
+        <v>0.5266</v>
       </c>
       <c r="J127" t="n">
-        <v>18.7714</v>
+        <v>17.9044</v>
       </c>
     </row>
     <row r="128">
@@ -7515,10 +7515,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4793</v>
+        <v>0.4354</v>
       </c>
       <c r="J128" t="n">
-        <v>16.2962</v>
+        <v>14.8036</v>
       </c>
     </row>
     <row r="129">
@@ -7555,10 +7555,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1207</v>
+        <v>-0.1029</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.1038</v>
+        <v>-3.4986</v>
       </c>
     </row>
     <row r="130">
@@ -7595,10 +7595,10 @@
         <v>0.88</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1661</v>
+        <v>-0.1462</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.6474</v>
+        <v>-4.9708</v>
       </c>
     </row>
     <row r="131">
@@ -7635,10 +7635,10 @@
         <v>0.5</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5203</v>
+        <v>-0.5243</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.6902</v>
+        <v>-17.8262</v>
       </c>
     </row>
     <row r="132">
@@ -7675,10 +7675,10 @@
         <v>1.48</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6178</v>
+        <v>0.5467</v>
       </c>
       <c r="J132" t="n">
-        <v>22.2408</v>
+        <v>19.6812</v>
       </c>
     </row>
     <row r="133">
@@ -7715,10 +7715,10 @@
         <v>1.36</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4893</v>
+        <v>0.4213</v>
       </c>
       <c r="J133" t="n">
-        <v>17.6148</v>
+        <v>15.1668</v>
       </c>
     </row>
     <row r="134">
@@ -7755,10 +7755,10 @@
         <v>1.26</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3765</v>
+        <v>0.3151</v>
       </c>
       <c r="J134" t="n">
-        <v>13.554</v>
+        <v>11.3436</v>
       </c>
     </row>
     <row r="135">
@@ -7795,10 +7795,10 @@
         <v>0.79</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2728</v>
+        <v>-0.2545</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.8208</v>
+        <v>-9.162000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7835,10 +7835,10 @@
         <v>0.73</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3301</v>
+        <v>-0.3152</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.8836</v>
+        <v>-11.3472</v>
       </c>
     </row>
     <row r="137">
@@ -7875,10 +7875,10 @@
         <v>1.18</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3263</v>
+        <v>0.317</v>
       </c>
       <c r="J137" t="n">
-        <v>11.7468</v>
+        <v>11.412</v>
       </c>
     </row>
     <row r="138">
@@ -7915,10 +7915,10 @@
         <v>1.05</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1253</v>
+        <v>0.1085</v>
       </c>
       <c r="J138" t="n">
-        <v>4.5108</v>
+        <v>3.906</v>
       </c>
     </row>
     <row r="139">
@@ -7955,10 +7955,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1742</v>
+        <v>-0.1545</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.2712</v>
+        <v>-5.562</v>
       </c>
     </row>
     <row r="140">
@@ -7995,10 +7995,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2261</v>
+        <v>-0.2059</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.1396</v>
+        <v>-7.4124</v>
       </c>
     </row>
     <row r="141">
@@ -8035,10 +8035,10 @@
         <v>0.74</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.304</v>
+        <v>-0.2861</v>
       </c>
       <c r="J141" t="n">
-        <v>-10.944</v>
+        <v>-10.2996</v>
       </c>
     </row>
     <row r="142">
@@ -8075,10 +8075,10 @@
         <v>1.2</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4861</v>
+        <v>0.4347</v>
       </c>
       <c r="J142" t="n">
-        <v>13.6108</v>
+        <v>12.1716</v>
       </c>
     </row>
     <row r="143">
@@ -8115,10 +8115,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0595</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.9992</v>
+        <v>-1.666</v>
       </c>
     </row>
     <row r="144">
@@ -8155,10 +8155,10 @@
         <v>0.84</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1979</v>
+        <v>-0.18</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.5412</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="145">
@@ -8195,10 +8195,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3679</v>
+        <v>-0.3539</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.3012</v>
+        <v>-9.9092</v>
       </c>
     </row>
     <row r="146">
@@ -8235,10 +8235,10 @@
         <v>0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4917</v>
+        <v>-0.4902</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.7676</v>
+        <v>-13.7256</v>
       </c>
     </row>
     <row r="147">
@@ -8275,10 +8275,10 @@
         <v>1.55</v>
       </c>
       <c r="I147" t="n">
-        <v>1.167</v>
+        <v>1.1806</v>
       </c>
       <c r="J147" t="n">
-        <v>32.676</v>
+        <v>33.0568</v>
       </c>
     </row>
     <row r="148">
@@ -8315,10 +8315,10 @@
         <v>1.45</v>
       </c>
       <c r="I148" t="n">
-        <v>1.0276</v>
+        <v>1.0297</v>
       </c>
       <c r="J148" t="n">
-        <v>28.7728</v>
+        <v>28.8316</v>
       </c>
     </row>
     <row r="149">
@@ -8355,10 +8355,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6675</v>
+        <v>0.6377</v>
       </c>
       <c r="J149" t="n">
-        <v>18.69</v>
+        <v>17.8556</v>
       </c>
     </row>
     <row r="150">
@@ -8395,10 +8395,10 @@
         <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0221</v>
+        <v>0.0122</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6188</v>
+        <v>0.3416</v>
       </c>
     </row>
     <row r="151">
@@ -8435,10 +8435,10 @@
         <v>0.85</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5113</v>
+        <v>-0.4728</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.3164</v>
+        <v>-13.2384</v>
       </c>
     </row>
     <row r="152">
@@ -8475,10 +8475,10 @@
         <v>1.06</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2003</v>
+        <v>0.1602</v>
       </c>
       <c r="J152" t="n">
-        <v>5.2078</v>
+        <v>4.1652</v>
       </c>
     </row>
     <row r="153">
@@ -8515,10 +8515,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1771</v>
+        <v>0.1397</v>
       </c>
       <c r="J153" t="n">
-        <v>4.6046</v>
+        <v>3.6322</v>
       </c>
     </row>
     <row r="154">
@@ -8555,10 +8555,10 @@
         <v>0.93</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.101</v>
+        <v>-0.0868</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.626</v>
+        <v>-2.2568</v>
       </c>
     </row>
     <row r="155">
@@ -8595,10 +8595,10 @@
         <v>0.85</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1895</v>
+        <v>-0.171</v>
       </c>
       <c r="J155" t="n">
-        <v>-4.927</v>
+        <v>-4.446</v>
       </c>
     </row>
     <row r="156">
@@ -8635,10 +8635,10 @@
         <v>0.42</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5796</v>
+        <v>-0.5914</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.0696</v>
+        <v>-15.3764</v>
       </c>
     </row>
     <row r="157">
@@ -8675,10 +8675,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8269</v>
+        <v>0.8054</v>
       </c>
       <c r="J157" t="n">
-        <v>21.4994</v>
+        <v>20.9404</v>
       </c>
     </row>
     <row r="158">
@@ -8715,10 +8715,10 @@
         <v>1.29</v>
       </c>
       <c r="I158" t="n">
-        <v>0.7275</v>
+        <v>0.7005</v>
       </c>
       <c r="J158" t="n">
-        <v>18.915</v>
+        <v>18.213</v>
       </c>
     </row>
     <row r="159">
@@ -8755,10 +8755,10 @@
         <v>1.24</v>
       </c>
       <c r="I159" t="n">
-        <v>0.6258</v>
+        <v>0.5951</v>
       </c>
       <c r="J159" t="n">
-        <v>16.2708</v>
+        <v>15.4726</v>
       </c>
     </row>
     <row r="160">
@@ -8795,10 +8795,10 @@
         <v>1.17</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4755</v>
+        <v>0.4422</v>
       </c>
       <c r="J160" t="n">
-        <v>12.363</v>
+        <v>11.4972</v>
       </c>
     </row>
     <row r="161">
@@ -8835,10 +8835,10 @@
         <v>1.11</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3312</v>
+        <v>0.2985</v>
       </c>
       <c r="J161" t="n">
-        <v>8.6112</v>
+        <v>7.761</v>
       </c>
     </row>
     <row r="162">
@@ -8875,10 +8875,10 @@
         <v>1.69</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3355</v>
+        <v>1.3567</v>
       </c>
       <c r="J162" t="n">
-        <v>32.052</v>
+        <v>32.5608</v>
       </c>
     </row>
     <row r="163">
@@ -8915,10 +8915,10 @@
         <v>1.22</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.548</v>
       </c>
       <c r="J163" t="n">
-        <v>13.8504</v>
+        <v>13.152</v>
       </c>
     </row>
     <row r="164">
@@ -8955,10 +8955,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5556</v>
+        <v>0.5258</v>
       </c>
       <c r="J164" t="n">
-        <v>13.3344</v>
+        <v>12.6192</v>
       </c>
     </row>
     <row r="165">
@@ -8995,10 +8995,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4663</v>
+        <v>0.4347</v>
       </c>
       <c r="J165" t="n">
-        <v>11.1912</v>
+        <v>10.4328</v>
       </c>
     </row>
     <row r="166">
@@ -9035,10 +9035,10 @@
         <v>1.17</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4663</v>
+        <v>0.4347</v>
       </c>
       <c r="J166" t="n">
-        <v>11.1912</v>
+        <v>10.4328</v>
       </c>
     </row>
     <row r="167">
@@ -9075,10 +9075,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8531</v>
+        <v>0.8268</v>
       </c>
       <c r="J167" t="n">
-        <v>20.4744</v>
+        <v>19.8432</v>
       </c>
     </row>
     <row r="168">
@@ -9115,10 +9115,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2629</v>
+        <v>-0.2452</v>
       </c>
       <c r="J168" t="n">
-        <v>-6.3096</v>
+        <v>-5.8848</v>
       </c>
     </row>
     <row r="169">
@@ -9155,10 +9155,10 @@
         <v>0.72</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3097</v>
+        <v>-0.2929</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.4328</v>
+        <v>-7.0296</v>
       </c>
     </row>
     <row r="170">
@@ -9195,10 +9195,10 @@
         <v>0.67</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3557</v>
+        <v>-0.341</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.536799999999999</v>
+        <v>-8.183999999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9235,10 +9235,10 @@
         <v>0.46</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5406</v>
+        <v>-0.5455</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.9744</v>
+        <v>-13.092</v>
       </c>
     </row>
     <row r="172">
@@ -9275,10 +9275,10 @@
         <v>1.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.147</v>
+        <v>0.1299</v>
       </c>
       <c r="J172" t="n">
-        <v>3.969</v>
+        <v>3.5073</v>
       </c>
     </row>
     <row r="173">
@@ -9315,10 +9315,10 @@
         <v>1.05</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1291</v>
+        <v>0.1123</v>
       </c>
       <c r="J173" t="n">
-        <v>3.4857</v>
+        <v>3.0321</v>
       </c>
     </row>
     <row r="174">
@@ -9355,10 +9355,10 @@
         <v>0.88</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1616</v>
+        <v>-0.1428</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.3632</v>
+        <v>-3.8556</v>
       </c>
     </row>
     <row r="175">
@@ -9395,10 +9395,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1723</v>
+        <v>-0.1531</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.6521</v>
+        <v>-4.1337</v>
       </c>
     </row>
     <row r="176">
@@ -9435,10 +9435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3484</v>
+        <v>-0.3331</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.4068</v>
+        <v>-8.9937</v>
       </c>
     </row>
     <row r="177">
@@ -9475,10 +9475,10 @@
         <v>1.32</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4444</v>
+        <v>0.3786</v>
       </c>
       <c r="J177" t="n">
-        <v>11.9988</v>
+        <v>10.2222</v>
       </c>
     </row>
     <row r="178">
@@ -9515,10 +9515,10 @@
         <v>1.25</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3643</v>
+        <v>0.3039</v>
       </c>
       <c r="J178" t="n">
-        <v>9.8361</v>
+        <v>8.205299999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9555,10 +9555,10 @@
         <v>1.09</v>
       </c>
       <c r="I179" t="n">
-        <v>0.1619</v>
+        <v>0.1258</v>
       </c>
       <c r="J179" t="n">
-        <v>4.3713</v>
+        <v>3.3966</v>
       </c>
     </row>
     <row r="180">
@@ -9595,10 +9595,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1162</v>
+        <v>0.0878</v>
       </c>
       <c r="J180" t="n">
-        <v>3.1374</v>
+        <v>2.3706</v>
       </c>
     </row>
     <row r="181">
@@ -9635,10 +9635,10 @@
         <v>0.92</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1343</v>
+        <v>-0.1151</v>
       </c>
       <c r="J181" t="n">
-        <v>-3.6261</v>
+        <v>-3.1077</v>
       </c>
     </row>
     <row r="182">
@@ -9675,10 +9675,10 @@
         <v>1.29</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7659</v>
+        <v>0.7366</v>
       </c>
       <c r="J182" t="n">
-        <v>20.6793</v>
+        <v>19.8882</v>
       </c>
     </row>
     <row r="183">
@@ -9715,10 +9715,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7018</v>
+        <v>0.6683</v>
       </c>
       <c r="J183" t="n">
-        <v>18.9486</v>
+        <v>18.0441</v>
       </c>
     </row>
     <row r="184">
@@ -9755,10 +9755,10 @@
         <v>1.04</v>
       </c>
       <c r="I184" t="n">
-        <v>0.1604</v>
+        <v>0.1327</v>
       </c>
       <c r="J184" t="n">
-        <v>4.3308</v>
+        <v>3.5829</v>
       </c>
     </row>
     <row r="185">
@@ -9795,10 +9795,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0689</v>
+        <v>-0.0497</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.8603</v>
+        <v>-1.3419</v>
       </c>
     </row>
     <row r="186">
@@ -9835,10 +9835,10 @@
         <v>0.74</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7353</v>
+        <v>-0.7058</v>
       </c>
       <c r="J186" t="n">
-        <v>-19.8531</v>
+        <v>-19.0566</v>
       </c>
     </row>
     <row r="187">
@@ -9875,10 +9875,10 @@
         <v>1.39</v>
       </c>
       <c r="I187" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6654</v>
       </c>
       <c r="J187" t="n">
-        <v>19.5021</v>
+        <v>17.9658</v>
       </c>
     </row>
     <row r="188">
@@ -9915,10 +9915,10 @@
         <v>1.13</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3014</v>
+        <v>0.2515</v>
       </c>
       <c r="J188" t="n">
-        <v>8.1378</v>
+        <v>6.7905</v>
       </c>
     </row>
     <row r="189">
@@ -9955,10 +9955,10 @@
         <v>1.12</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2829</v>
+        <v>0.2346</v>
       </c>
       <c r="J189" t="n">
-        <v>7.6383</v>
+        <v>6.3342</v>
       </c>
     </row>
     <row r="190">
@@ -9995,10 +9995,10 @@
         <v>0.99</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0283</v>
+        <v>-0.0201</v>
       </c>
       <c r="J190" t="n">
-        <v>-0.7641</v>
+        <v>-0.5427</v>
       </c>
     </row>
     <row r="191">
@@ -10035,10 +10035,10 @@
         <v>0.6</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4408</v>
+        <v>-0.4356</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.9016</v>
+        <v>-11.7612</v>
       </c>
     </row>
     <row r="192">
@@ -10075,10 +10075,10 @@
         <v>1.77</v>
       </c>
       <c r="I192" t="n">
-        <v>0.85</v>
+        <v>0.7794</v>
       </c>
       <c r="J192" t="n">
-        <v>17.85</v>
+        <v>16.3674</v>
       </c>
     </row>
     <row r="193">
@@ -10115,10 +10115,10 @@
         <v>1.48</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5789</v>
+        <v>0.5119</v>
       </c>
       <c r="J193" t="n">
-        <v>12.1569</v>
+        <v>10.7499</v>
       </c>
     </row>
     <row r="194">
@@ -10155,10 +10155,10 @@
         <v>1.45</v>
       </c>
       <c r="I194" t="n">
-        <v>0.55</v>
+        <v>0.4843</v>
       </c>
       <c r="J194" t="n">
-        <v>11.55</v>
+        <v>10.1703</v>
       </c>
     </row>
     <row r="195">
@@ -10195,10 +10195,10 @@
         <v>1.25</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3403</v>
+        <v>0.2879</v>
       </c>
       <c r="J195" t="n">
-        <v>7.1463</v>
+        <v>6.0459</v>
       </c>
     </row>
     <row r="196">
@@ -10235,10 +10235,10 @@
         <v>1.22</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3053</v>
+        <v>0.2556</v>
       </c>
       <c r="J196" t="n">
-        <v>6.4113</v>
+        <v>5.3676</v>
       </c>
     </row>
     <row r="197">
@@ -10275,10 +10275,10 @@
         <v>0.85</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.1561</v>
+        <v>-0.1387</v>
       </c>
       <c r="J197" t="n">
-        <v>-3.2781</v>
+        <v>-2.9127</v>
       </c>
     </row>
     <row r="198">
@@ -10315,10 +10315,10 @@
         <v>0.73</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2825</v>
+        <v>-0.2699</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.9325</v>
+        <v>-5.6679</v>
       </c>
     </row>
     <row r="199">
@@ -10355,10 +10355,10 @@
         <v>0.6</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3986</v>
+        <v>-0.389</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.3706</v>
+        <v>-8.169</v>
       </c>
     </row>
     <row r="200">
@@ -10395,10 +10395,10 @@
         <v>0.58</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4161</v>
+        <v>-0.4073</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.738099999999999</v>
+        <v>-8.5533</v>
       </c>
     </row>
     <row r="201">
@@ -10435,10 +10435,10 @@
         <v>0.46</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.5223</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.9557</v>
+        <v>-10.9683</v>
       </c>
     </row>
     <row r="202">
@@ -10475,10 +10475,10 @@
         <v>0.92</v>
       </c>
       <c r="I202" t="n">
-        <v>-0.0993</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>-2.0853</v>
+        <v>-1.785</v>
       </c>
     </row>
     <row r="203">
@@ -10515,10 +10515,10 @@
         <v>0.8</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2313</v>
+        <v>-0.2151</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.8573</v>
+        <v>-4.5171</v>
       </c>
     </row>
     <row r="204">
@@ -10555,10 +10555,10 @@
         <v>0.74</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.287</v>
+        <v>-0.2707</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.027</v>
+        <v>-5.6847</v>
       </c>
     </row>
     <row r="205">
@@ -10595,10 +10595,10 @@
         <v>0.71</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3145</v>
+        <v>-0.2986</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.6045</v>
+        <v>-6.2706</v>
       </c>
     </row>
     <row r="206">
@@ -10635,10 +10635,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.369</v>
+        <v>-0.3554</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.749</v>
+        <v>-7.4634</v>
       </c>
     </row>
     <row r="207">
@@ -10675,10 +10675,10 @@
         <v>1.91</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5931</v>
+        <v>1.6328</v>
       </c>
       <c r="J207" t="n">
-        <v>33.4551</v>
+        <v>34.2888</v>
       </c>
     </row>
     <row r="208">
@@ -10715,10 +10715,10 @@
         <v>1.45</v>
       </c>
       <c r="I208" t="n">
-        <v>1.0047</v>
+        <v>1.007</v>
       </c>
       <c r="J208" t="n">
-        <v>21.0987</v>
+        <v>21.147</v>
       </c>
     </row>
     <row r="209">
@@ -10755,10 +10755,10 @@
         <v>1.35</v>
       </c>
       <c r="I209" t="n">
-        <v>0.8289</v>
+        <v>0.8138</v>
       </c>
       <c r="J209" t="n">
-        <v>17.4069</v>
+        <v>17.0898</v>
       </c>
     </row>
     <row r="210">
@@ -10795,10 +10795,10 @@
         <v>1.17</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4561</v>
+        <v>0.4254</v>
       </c>
       <c r="J210" t="n">
-        <v>9.578099999999999</v>
+        <v>8.933400000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10835,10 +10835,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3787</v>
+        <v>-0.3423</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.9527</v>
+        <v>-7.1883</v>
       </c>
     </row>
     <row r="212">
@@ -10875,10 +10875,10 @@
         <v>0.88</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.141</v>
+        <v>-0.1255</v>
       </c>
       <c r="J212" t="n">
-        <v>-2.961</v>
+        <v>-2.6355</v>
       </c>
     </row>
     <row r="213">
@@ -10915,10 +10915,10 @@
         <v>0.87</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1524</v>
+        <v>-0.1369</v>
       </c>
       <c r="J213" t="n">
-        <v>-3.2004</v>
+        <v>-2.8749</v>
       </c>
     </row>
     <row r="214">
@@ -10955,10 +10955,10 @@
         <v>0.86</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1637</v>
+        <v>-0.1481</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.4377</v>
+        <v>-3.1101</v>
       </c>
     </row>
     <row r="215">
@@ -10995,10 +10995,10 @@
         <v>0.61</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4007</v>
+        <v>-0.3895</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.4147</v>
+        <v>-8.179500000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11035,10 +11035,10 @@
         <v>0.43</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5585</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.7285</v>
+        <v>-11.865</v>
       </c>
     </row>
     <row r="217">
@@ -11075,10 +11075,10 @@
         <v>1.91</v>
       </c>
       <c r="I217" t="n">
-        <v>1.5636</v>
+        <v>1.5998</v>
       </c>
       <c r="J217" t="n">
-        <v>32.8356</v>
+        <v>33.5958</v>
       </c>
     </row>
     <row r="218">
@@ -11115,10 +11115,10 @@
         <v>1.6</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1884</v>
+        <v>1.207</v>
       </c>
       <c r="J218" t="n">
-        <v>24.9564</v>
+        <v>25.347</v>
       </c>
     </row>
     <row r="219">
@@ -11155,10 +11155,10 @@
         <v>1.52</v>
       </c>
       <c r="I219" t="n">
-        <v>1.088</v>
+        <v>1.1051</v>
       </c>
       <c r="J219" t="n">
-        <v>22.848</v>
+        <v>23.2071</v>
       </c>
     </row>
     <row r="220">
@@ -11195,10 +11195,10 @@
         <v>1.4</v>
       </c>
       <c r="I220" t="n">
-        <v>0.9062</v>
+        <v>0.9028</v>
       </c>
       <c r="J220" t="n">
-        <v>19.0302</v>
+        <v>18.9588</v>
       </c>
     </row>
     <row r="221">
@@ -11235,10 +11235,10 @@
         <v>1.06</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1531</v>
+        <v>0.1219</v>
       </c>
       <c r="J221" t="n">
-        <v>3.2151</v>
+        <v>2.5599</v>
       </c>
     </row>
     <row r="222">
@@ -11275,10 +11275,10 @@
         <v>1.33</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8431</v>
+        <v>0.8199</v>
       </c>
       <c r="J222" t="n">
-        <v>23.6068</v>
+        <v>22.9572</v>
       </c>
     </row>
     <row r="223">
@@ -11315,10 +11315,10 @@
         <v>1.21</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5869</v>
+        <v>0.5484</v>
       </c>
       <c r="J223" t="n">
-        <v>16.4332</v>
+        <v>15.3552</v>
       </c>
     </row>
     <row r="224">
@@ -11355,10 +11355,10 @@
         <v>1.14</v>
       </c>
       <c r="I224" t="n">
-        <v>0.425</v>
+        <v>0.3846</v>
       </c>
       <c r="J224" t="n">
-        <v>11.9</v>
+        <v>10.7688</v>
       </c>
     </row>
     <row r="225">
@@ -11395,10 +11395,10 @@
         <v>1.05</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1888</v>
+        <v>0.1592</v>
       </c>
       <c r="J225" t="n">
-        <v>5.2864</v>
+        <v>4.4576</v>
       </c>
     </row>
     <row r="226">
@@ -11435,10 +11435,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8466</v>
+        <v>-0.8276</v>
       </c>
       <c r="J226" t="n">
-        <v>-23.7048</v>
+        <v>-23.1728</v>
       </c>
     </row>
     <row r="227">
@@ -11475,10 +11475,10 @@
         <v>1.48</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8501</v>
+        <v>0.799</v>
       </c>
       <c r="J227" t="n">
-        <v>23.8028</v>
+        <v>22.372</v>
       </c>
     </row>
     <row r="228">
@@ -11515,10 +11515,10 @@
         <v>1.01</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0378</v>
+        <v>0.0264</v>
       </c>
       <c r="J228" t="n">
-        <v>1.0584</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="229">
@@ -11555,10 +11555,10 @@
         <v>0.98</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.0469</v>
+        <v>-0.0354</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.3132</v>
+        <v>-0.9912</v>
       </c>
     </row>
     <row r="230">
@@ -11595,10 +11595,10 @@
         <v>0.93</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1163</v>
+        <v>-0.0979</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.2564</v>
+        <v>-2.7412</v>
       </c>
     </row>
     <row r="231">
@@ -11635,10 +11635,10 @@
         <v>0.89</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1632</v>
+        <v>-0.1429</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.5696</v>
+        <v>-4.0012</v>
       </c>
     </row>
     <row r="232">
@@ -11675,10 +11675,10 @@
         <v>1.8</v>
       </c>
       <c r="I232" t="n">
-        <v>1.4952</v>
+        <v>1.5302</v>
       </c>
       <c r="J232" t="n">
-        <v>41.8656</v>
+        <v>42.8456</v>
       </c>
     </row>
     <row r="233">
@@ -11715,10 +11715,10 @@
         <v>1.29</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7298</v>
+        <v>0.7022</v>
       </c>
       <c r="J233" t="n">
-        <v>20.4344</v>
+        <v>19.6616</v>
       </c>
     </row>
     <row r="234">
@@ -11755,10 +11755,10 @@
         <v>1.17</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4775</v>
+        <v>0.4436</v>
       </c>
       <c r="J234" t="n">
-        <v>13.37</v>
+        <v>12.4208</v>
       </c>
     </row>
     <row r="235">
@@ -11795,10 +11795,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2706</v>
+        <v>-0.2326</v>
       </c>
       <c r="J235" t="n">
-        <v>-7.5768</v>
+        <v>-6.5128</v>
       </c>
     </row>
     <row r="236">
@@ -11835,10 +11835,10 @@
         <v>0.88</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4351</v>
+        <v>-0.3947</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.1828</v>
+        <v>-11.0516</v>
       </c>
     </row>
     <row r="237">
@@ -11875,10 +11875,10 @@
         <v>1.04</v>
       </c>
       <c r="I237" t="n">
-        <v>0.1396</v>
+        <v>0.106</v>
       </c>
       <c r="J237" t="n">
-        <v>3.9088</v>
+        <v>2.968</v>
       </c>
     </row>
     <row r="238">
@@ -11915,10 +11915,10 @@
         <v>1.02</v>
       </c>
       <c r="I238" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="J238" t="n">
-        <v>2.436</v>
+        <v>1.7472</v>
       </c>
     </row>
     <row r="239">
@@ -11955,10 +11955,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1512</v>
+        <v>-0.1327</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.2336</v>
+        <v>-3.7156</v>
       </c>
     </row>
     <row r="240">
@@ -11995,10 +11995,10 @@
         <v>0.84</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2042</v>
+        <v>-0.1842</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.7176</v>
+        <v>-5.1576</v>
       </c>
     </row>
     <row r="241">
@@ -12035,10 +12035,10 @@
         <v>0.79</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2544</v>
+        <v>-0.2347</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.1232</v>
+        <v>-6.5716</v>
       </c>
     </row>
     <row r="242">
@@ -12075,10 +12075,10 @@
         <v>1.1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.2571</v>
+        <v>0.2098</v>
       </c>
       <c r="J242" t="n">
-        <v>6.9417</v>
+        <v>5.6646</v>
       </c>
     </row>
     <row r="243">
@@ -12115,10 +12115,10 @@
         <v>1.05</v>
       </c>
       <c r="I243" t="n">
-        <v>0.1516</v>
+        <v>0.1166</v>
       </c>
       <c r="J243" t="n">
-        <v>4.0932</v>
+        <v>3.1482</v>
       </c>
     </row>
     <row r="244">
@@ -12155,10 +12155,10 @@
         <v>1.04</v>
       </c>
       <c r="I244" t="n">
-        <v>0.1282</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>3.4614</v>
+        <v>2.6109</v>
       </c>
     </row>
     <row r="245">
@@ -12195,10 +12195,10 @@
         <v>1.03</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1033</v>
+        <v>0.076</v>
       </c>
       <c r="J245" t="n">
-        <v>2.7891</v>
+        <v>2.052</v>
       </c>
     </row>
     <row r="246">
@@ -12235,10 +12235,10 @@
         <v>0.66</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3819</v>
+        <v>-0.3698</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.3113</v>
+        <v>-9.9846</v>
       </c>
     </row>
     <row r="247">
@@ -12275,10 +12275,10 @@
         <v>1.7</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4109</v>
+        <v>1.4456</v>
       </c>
       <c r="J247" t="n">
-        <v>38.0943</v>
+        <v>39.0312</v>
       </c>
     </row>
     <row r="248">
@@ -12315,10 +12315,10 @@
         <v>1.09</v>
       </c>
       <c r="I248" t="n">
-        <v>0.3008</v>
+        <v>0.2636</v>
       </c>
       <c r="J248" t="n">
-        <v>8.121600000000001</v>
+        <v>7.1172</v>
       </c>
     </row>
     <row r="249">
@@ -12355,10 +12355,10 @@
         <v>0.9</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3575</v>
+        <v>-0.3148</v>
       </c>
       <c r="J249" t="n">
-        <v>-9.6525</v>
+        <v>-8.499599999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12395,10 +12395,10 @@
         <v>0.87</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4351</v>
+        <v>-0.3922</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.7477</v>
+        <v>-10.5894</v>
       </c>
     </row>
     <row r="251">
@@ -12435,10 +12435,10 @@
         <v>0.83</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.533</v>
+        <v>-0.4922</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.391</v>
+        <v>-13.2894</v>
       </c>
     </row>
     <row r="252">
@@ -12475,10 +12475,10 @@
         <v>1.21</v>
       </c>
       <c r="I252" t="n">
-        <v>0.4567</v>
+        <v>0.3988</v>
       </c>
       <c r="J252" t="n">
-        <v>12.3309</v>
+        <v>10.7676</v>
       </c>
     </row>
     <row r="253">
@@ -12515,10 +12515,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>0.0022</v>
+        <v>0.001</v>
       </c>
       <c r="J253" t="n">
-        <v>0.0594</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="254">
@@ -12555,10 +12555,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0416</v>
+        <v>-0.0319</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.1232</v>
+        <v>-0.8613</v>
       </c>
     </row>
     <row r="255">
@@ -12595,10 +12595,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0843</v>
+        <v>-0.0692</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.2761</v>
+        <v>-1.8684</v>
       </c>
     </row>
     <row r="256">
@@ -12635,10 +12635,10 @@
         <v>0.74</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3082</v>
+        <v>-0.2907</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.321400000000001</v>
+        <v>-7.8489</v>
       </c>
     </row>
     <row r="257">
@@ -12675,10 +12675,10 @@
         <v>1.35</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8833</v>
+        <v>0.8637</v>
       </c>
       <c r="J257" t="n">
-        <v>23.8491</v>
+        <v>23.3199</v>
       </c>
     </row>
     <row r="258">
@@ -12715,10 +12715,10 @@
         <v>1.14</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4247</v>
+        <v>0.3844</v>
       </c>
       <c r="J258" t="n">
-        <v>11.4669</v>
+        <v>10.3788</v>
       </c>
     </row>
     <row r="259">
@@ -12755,10 +12755,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1885</v>
+        <v>0.159</v>
       </c>
       <c r="J259" t="n">
-        <v>5.0895</v>
+        <v>4.293</v>
       </c>
     </row>
     <row r="260">
@@ -12795,10 +12795,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1142</v>
+        <v>-0.0877</v>
       </c>
       <c r="J260" t="n">
-        <v>-3.0834</v>
+        <v>-2.3679</v>
       </c>
     </row>
     <row r="261">
@@ -12835,10 +12835,10 @@
         <v>0.91</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3321</v>
+        <v>-0.2899</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.966699999999999</v>
+        <v>-7.8273</v>
       </c>
     </row>
     <row r="262">
@@ -12875,10 +12875,10 @@
         <v>1.09</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3103</v>
+        <v>0.27</v>
       </c>
       <c r="J262" t="n">
-        <v>8.998699999999999</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="263">
@@ -12915,10 +12915,10 @@
         <v>1.04</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1652</v>
+        <v>0.135</v>
       </c>
       <c r="J263" t="n">
-        <v>4.7908</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="264">
@@ -12955,10 +12955,10 @@
         <v>1.01</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0565</v>
+        <v>0.0418</v>
       </c>
       <c r="J264" t="n">
-        <v>1.6385</v>
+        <v>1.2122</v>
       </c>
     </row>
     <row r="265">
@@ -12995,10 +12995,10 @@
         <v>0.99</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0618</v>
+        <v>-0.0445</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.7922</v>
+        <v>-1.2905</v>
       </c>
     </row>
     <row r="266">
@@ -13035,10 +13035,10 @@
         <v>0.98</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.1028</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-2.9812</v>
+        <v>-2.2823</v>
       </c>
     </row>
     <row r="267">
@@ -13075,10 +13075,10 @@
         <v>1.4</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7332</v>
+        <v>0.6764</v>
       </c>
       <c r="J267" t="n">
-        <v>21.2628</v>
+        <v>19.6156</v>
       </c>
     </row>
     <row r="268">
@@ -13115,10 +13115,10 @@
         <v>1.37</v>
       </c>
       <c r="I268" t="n">
-        <v>0.6886</v>
+        <v>0.6303</v>
       </c>
       <c r="J268" t="n">
-        <v>19.9694</v>
+        <v>18.2787</v>
       </c>
     </row>
     <row r="269">
@@ -13155,10 +13155,10 @@
         <v>0.92</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1287</v>
+        <v>-0.1096</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.7323</v>
+        <v>-3.1784</v>
       </c>
     </row>
     <row r="270">
@@ -13195,10 +13195,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2478</v>
+        <v>-0.228</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.1862</v>
+        <v>-6.612</v>
       </c>
     </row>
     <row r="271">
@@ -13235,10 +13235,10 @@
         <v>0.8</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2577</v>
+        <v>-0.2382</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.4733</v>
+        <v>-6.9078</v>
       </c>
     </row>
     <row r="272">
@@ -13275,10 +13275,10 @@
         <v>1.8</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4302</v>
+        <v>1.4579</v>
       </c>
       <c r="J272" t="n">
-        <v>27.1738</v>
+        <v>27.7001</v>
       </c>
     </row>
     <row r="273">
@@ -13315,10 +13315,10 @@
         <v>1.7</v>
       </c>
       <c r="I273" t="n">
-        <v>1.3095</v>
+        <v>1.3318</v>
       </c>
       <c r="J273" t="n">
-        <v>24.8805</v>
+        <v>25.3042</v>
       </c>
     </row>
     <row r="274">
@@ -13355,10 +13355,10 @@
         <v>1.67</v>
       </c>
       <c r="I274" t="n">
-        <v>1.2729</v>
+        <v>1.294</v>
       </c>
       <c r="J274" t="n">
-        <v>24.1851</v>
+        <v>24.586</v>
       </c>
     </row>
     <row r="275">
@@ -13395,10 +13395,10 @@
         <v>1.61</v>
       </c>
       <c r="I275" t="n">
-        <v>1.1989</v>
+        <v>1.2183</v>
       </c>
       <c r="J275" t="n">
-        <v>22.7791</v>
+        <v>23.1477</v>
       </c>
     </row>
     <row r="276">
@@ -13435,10 +13435,10 @@
         <v>0.8</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6693</v>
+        <v>-0.6478</v>
       </c>
       <c r="J276" t="n">
-        <v>-12.7167</v>
+        <v>-12.3082</v>
       </c>
     </row>
     <row r="277">
@@ -13475,10 +13475,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2342</v>
+        <v>0.2586</v>
       </c>
       <c r="J277" t="n">
-        <v>4.4498</v>
+        <v>4.9134</v>
       </c>
     </row>
     <row r="278">
@@ -13515,10 +13515,10 @@
         <v>0.77</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2155</v>
+        <v>-0.1968</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.0945</v>
+        <v>-3.7392</v>
       </c>
     </row>
     <row r="279">
@@ -13555,10 +13555,10 @@
         <v>0.38</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.5778</v>
+        <v>-0.5853</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.9782</v>
+        <v>-11.1207</v>
       </c>
     </row>
     <row r="280">
@@ -13595,10 +13595,10 @@
         <v>0.36</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.5957</v>
+        <v>-0.6057</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.3183</v>
+        <v>-11.5083</v>
       </c>
     </row>
     <row r="281">
@@ -13635,10 +13635,10 @@
         <v>0.21</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7305</v>
+        <v>-0.7664</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.8795</v>
+        <v>-14.5616</v>
       </c>
     </row>
     <row r="282">
@@ -13675,10 +13675,10 @@
         <v>1.01</v>
       </c>
       <c r="I282" t="n">
-        <v>0.0553</v>
+        <v>0.0376</v>
       </c>
       <c r="J282" t="n">
-        <v>1.6037</v>
+        <v>1.0904</v>
       </c>
     </row>
     <row r="283">
@@ -13715,10 +13715,10 @@
         <v>0.99</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0194</v>
+        <v>-0.0144</v>
       </c>
       <c r="J283" t="n">
-        <v>-0.5626</v>
+        <v>-0.4176</v>
       </c>
     </row>
     <row r="284">
@@ -13755,10 +13755,10 @@
         <v>0.95</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.081</v>
+        <v>-0.0675</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.349</v>
+        <v>-1.9575</v>
       </c>
     </row>
     <row r="285">
@@ -13795,10 +13795,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J285" t="n">
-        <v>-5.3302</v>
+        <v>-4.756</v>
       </c>
     </row>
     <row r="286">
@@ -13835,10 +13835,10 @@
         <v>0.79</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2547</v>
+        <v>-0.2351</v>
       </c>
       <c r="J286" t="n">
-        <v>-7.3863</v>
+        <v>-6.8179</v>
       </c>
     </row>
     <row r="287">
@@ -13875,10 +13875,10 @@
         <v>1.53</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1553</v>
+        <v>1.1691</v>
       </c>
       <c r="J287" t="n">
-        <v>33.5037</v>
+        <v>33.9039</v>
       </c>
     </row>
     <row r="288">
@@ -13915,10 +13915,10 @@
         <v>1.2</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5502</v>
+        <v>0.5139</v>
       </c>
       <c r="J288" t="n">
-        <v>15.9558</v>
+        <v>14.9031</v>
       </c>
     </row>
     <row r="289">
@@ -13955,10 +13955,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2906</v>
+        <v>0.2574</v>
       </c>
       <c r="J289" t="n">
-        <v>8.4274</v>
+        <v>7.4646</v>
       </c>
     </row>
     <row r="290">
@@ -13995,10 +13995,10 @@
         <v>1.02</v>
       </c>
       <c r="I290" t="n">
-        <v>0.075</v>
+        <v>0.0585</v>
       </c>
       <c r="J290" t="n">
-        <v>2.175</v>
+        <v>1.6965</v>
       </c>
     </row>
     <row r="291">
@@ -14035,10 +14035,10 @@
         <v>0.95</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2297</v>
+        <v>-0.1928</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.6613</v>
+        <v>-5.5912</v>
       </c>
     </row>
     <row r="292">
@@ -14075,10 +14075,10 @@
         <v>1.05</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1697</v>
+        <v>0.1323</v>
       </c>
       <c r="J292" t="n">
-        <v>4.4122</v>
+        <v>3.4398</v>
       </c>
     </row>
     <row r="293">
@@ -14115,10 +14115,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1456</v>
+        <v>0.1116</v>
       </c>
       <c r="J293" t="n">
-        <v>3.7856</v>
+        <v>2.9016</v>
       </c>
     </row>
     <row r="294">
@@ -14155,10 +14155,10 @@
         <v>0.88</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1602</v>
+        <v>-0.142</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.1652</v>
+        <v>-3.692</v>
       </c>
     </row>
     <row r="295">
@@ -14195,10 +14195,10 @@
         <v>0.88</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1602</v>
+        <v>-0.142</v>
       </c>
       <c r="J295" t="n">
-        <v>-4.1652</v>
+        <v>-3.692</v>
       </c>
     </row>
     <row r="296">
@@ -14235,10 +14235,10 @@
         <v>0.6</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4274</v>
+        <v>-0.4189</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.1124</v>
+        <v>-10.8914</v>
       </c>
     </row>
     <row r="297">
@@ -14275,10 +14275,10 @@
         <v>1.38</v>
       </c>
       <c r="I297" t="n">
-        <v>0.9064</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>23.5664</v>
+        <v>23.1556</v>
       </c>
     </row>
     <row r="298">
@@ -14315,10 +14315,10 @@
         <v>1.33</v>
       </c>
       <c r="I298" t="n">
-        <v>0.8088</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J298" t="n">
-        <v>21.0288</v>
+        <v>20.4308</v>
       </c>
     </row>
     <row r="299">
@@ -14355,10 +14355,10 @@
         <v>1.25</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6473</v>
+        <v>0.6167</v>
       </c>
       <c r="J299" t="n">
-        <v>16.8298</v>
+        <v>16.0342</v>
       </c>
     </row>
     <row r="300">
@@ -14395,10 +14395,10 @@
         <v>1.08</v>
       </c>
       <c r="I300" t="n">
-        <v>0.253</v>
+        <v>0.2224</v>
       </c>
       <c r="J300" t="n">
-        <v>6.578</v>
+        <v>5.7824</v>
       </c>
     </row>
     <row r="301">
@@ -14435,10 +14435,10 @@
         <v>1.07</v>
       </c>
       <c r="I301" t="n">
-        <v>0.225</v>
+        <v>0.1956</v>
       </c>
       <c r="J301" t="n">
-        <v>5.85</v>
+        <v>5.0856</v>
       </c>
     </row>
     <row r="302">
@@ -14475,10 +14475,10 @@
         <v>1.12</v>
       </c>
       <c r="I302" t="n">
-        <v>0.2984</v>
+        <v>0.2478</v>
       </c>
       <c r="J302" t="n">
-        <v>8.952</v>
+        <v>7.434</v>
       </c>
     </row>
     <row r="303">
@@ -14515,10 +14515,10 @@
         <v>0.95</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0688</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.508</v>
+        <v>-2.064</v>
       </c>
     </row>
     <row r="304">
@@ -14555,10 +14555,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0963</v>
+        <v>-0.0803</v>
       </c>
       <c r="J304" t="n">
-        <v>-2.889</v>
+        <v>-2.409</v>
       </c>
     </row>
     <row r="305">
@@ -14595,10 +14595,10 @@
         <v>0.92</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.1207</v>
+        <v>-0.1029</v>
       </c>
       <c r="J305" t="n">
-        <v>-3.621</v>
+        <v>-3.087</v>
       </c>
     </row>
     <row r="306">
@@ -14635,10 +14635,10 @@
         <v>0.89</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1551</v>
+        <v>-0.1356</v>
       </c>
       <c r="J306" t="n">
-        <v>-4.653</v>
+        <v>-4.068</v>
       </c>
     </row>
     <row r="307">
@@ -14675,10 +14675,10 @@
         <v>1.31</v>
       </c>
       <c r="I307" t="n">
-        <v>0.7982</v>
+        <v>0.7715</v>
       </c>
       <c r="J307" t="n">
-        <v>23.946</v>
+        <v>23.145</v>
       </c>
     </row>
     <row r="308">
@@ -14715,10 +14715,10 @@
         <v>1.17</v>
       </c>
       <c r="I308" t="n">
-        <v>0.4935</v>
+        <v>0.4536</v>
       </c>
       <c r="J308" t="n">
-        <v>14.805</v>
+        <v>13.608</v>
       </c>
     </row>
     <row r="309">
@@ -14755,10 +14755,10 @@
         <v>1.13</v>
       </c>
       <c r="I309" t="n">
-        <v>0.3988</v>
+        <v>0.3594</v>
       </c>
       <c r="J309" t="n">
-        <v>11.964</v>
+        <v>10.782</v>
       </c>
     </row>
     <row r="310">
@@ -14795,10 +14795,10 @@
         <v>1.07</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2453</v>
+        <v>0.2121</v>
       </c>
       <c r="J310" t="n">
-        <v>7.359</v>
+        <v>6.363</v>
       </c>
     </row>
     <row r="311">
@@ -14835,10 +14835,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6068</v>
+        <v>-0.5695</v>
       </c>
       <c r="J311" t="n">
-        <v>-18.204</v>
+        <v>-17.085</v>
       </c>
     </row>
     <row r="312">
@@ -14875,10 +14875,10 @@
         <v>1.22</v>
       </c>
       <c r="I312" t="n">
-        <v>0.482</v>
+        <v>0.4243</v>
       </c>
       <c r="J312" t="n">
-        <v>12.532</v>
+        <v>11.0318</v>
       </c>
     </row>
     <row r="313">
@@ -14915,10 +14915,10 @@
         <v>1.16</v>
       </c>
       <c r="I313" t="n">
-        <v>0.3769</v>
+        <v>0.322</v>
       </c>
       <c r="J313" t="n">
-        <v>9.7994</v>
+        <v>8.372</v>
       </c>
     </row>
     <row r="314">
@@ -14955,10 +14955,10 @@
         <v>0.89</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1536</v>
+        <v>-0.1344</v>
       </c>
       <c r="J314" t="n">
-        <v>-3.9936</v>
+        <v>-3.4944</v>
       </c>
     </row>
     <row r="315">
@@ -14995,10 +14995,10 @@
         <v>0.87</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1754</v>
+        <v>-0.1555</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.5604</v>
+        <v>-4.043</v>
       </c>
     </row>
     <row r="316">
@@ -15035,10 +15035,10 @@
         <v>0.59</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4414</v>
+        <v>-0.435</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.4764</v>
+        <v>-11.31</v>
       </c>
     </row>
     <row r="317">
@@ -15075,10 +15075,10 @@
         <v>1.33</v>
       </c>
       <c r="I317" t="n">
-        <v>0.8212</v>
+        <v>0.7972</v>
       </c>
       <c r="J317" t="n">
-        <v>21.3512</v>
+        <v>20.7272</v>
       </c>
     </row>
     <row r="318">
@@ -15115,10 +15115,10 @@
         <v>1.27</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6985</v>
+        <v>0.6671</v>
       </c>
       <c r="J318" t="n">
-        <v>18.161</v>
+        <v>17.3446</v>
       </c>
     </row>
     <row r="319">
@@ -15155,10 +15155,10 @@
         <v>1.21</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5354</v>
       </c>
       <c r="J319" t="n">
-        <v>14.8486</v>
+        <v>13.9204</v>
       </c>
     </row>
     <row r="320">
@@ -15195,10 +15195,10 @@
         <v>1.17</v>
       </c>
       <c r="I320" t="n">
-        <v>0.4831</v>
+        <v>0.4466</v>
       </c>
       <c r="J320" t="n">
-        <v>12.5606</v>
+        <v>11.6116</v>
       </c>
     </row>
     <row r="321">
@@ -15235,10 +15235,10 @@
         <v>0.84</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5252</v>
+        <v>-0.4857</v>
       </c>
       <c r="J321" t="n">
-        <v>-13.6552</v>
+        <v>-12.6282</v>
       </c>
     </row>
   </sheetData>
